--- a/JO12-1/JO12-1_matchesDB.xlsx
+++ b/JO12-1/JO12-1_matchesDB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yasif\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE79DF21-45CD-41F8-A994-F55E0896770E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927513B8-3486-44BB-B3E2-F34BBC5B1A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,8 +36,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="76">
   <si>
     <t>Matches</t>
   </si>
@@ -249,6 +271,24 @@
   </si>
   <si>
     <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,4</t>
+  </si>
+  <si>
+    <t>1,1,4,1</t>
+  </si>
+  <si>
+    <t>1,0,2,0</t>
+  </si>
+  <si>
+    <t>1,1,1,1</t>
+  </si>
+  <si>
+    <t>1,1,2,0</t>
+  </si>
+  <si>
+    <t>1,1,2,1</t>
   </si>
 </sst>
 </file>
@@ -792,7 +832,7 @@
       </c>
       <c r="B1" s="5">
         <f>SUM(COUNTIF(J11:J40,"W"),COUNTIF(J11:J40,"D"),COUNTIF(J11:J40,"L"))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="7">
@@ -831,7 +871,7 @@
       </c>
       <c r="B2" s="9">
         <f>COUNTIF(J11:J40,"W")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -942,7 +982,7 @@
       </c>
       <c r="B5" s="9">
         <f>B2*3+B4</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -979,7 +1019,7 @@
       </c>
       <c r="B6" s="9">
         <f>B7-B8</f>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -1016,7 +1056,7 @@
       </c>
       <c r="B7" s="9">
         <f>SUM(K11:K40)</f>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -1053,7 +1093,7 @@
       </c>
       <c r="B8" s="12">
         <f>SUM(L11:L40)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -1169,24 +1209,21 @@
         <v>4</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="W10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="X10" s="16" t="s">
+      <c r="W10" s="16" t="s">
         <v>32</v>
       </c>
       <c r="AD10" s="6"/>
@@ -1224,16 +1261,16 @@
         <f t="shared" ref="J11:J40" si="0">IF(AND(NOT(ISBLANK(K11)),NOT(ISBLANK(L11))),IF(K11&gt;L11,"W",IF(K11&lt;L11,"L","D")),"")</f>
         <v>L</v>
       </c>
-      <c r="K11" s="23">
-        <f t="array" ref="K11">IF(L11&lt;&gt;"", SUMPRODUCT(MID(N11:X11,5,1)*1), "")</f>
+      <c r="K11" s="23" cm="1">
+        <f t="array" ref="K11">IF(L11&lt;&gt;"", SUMPRODUCT(MID(N11:W11,5,1)*1), "")</f>
         <v>1</v>
       </c>
       <c r="L11" s="18">
         <v>2</v>
       </c>
-      <c r="M11" s="23">
-        <f t="array" ref="M11">IF(L11&lt;&gt;"", SUMPRODUCT(LEFT(N11:X11,1)*1), "")</f>
-        <v>10</v>
+      <c r="M11" s="23" cm="1">
+        <f t="array" ref="M11">IF(L11&lt;&gt;"", SUMPRODUCT(LEFT(N11:W11,1)*1), "")</f>
+        <v>9</v>
       </c>
       <c r="N11" s="16" t="s">
         <v>38</v>
@@ -1248,10 +1285,10 @@
         <v>39</v>
       </c>
       <c r="R11" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="S11" s="16" t="s">
         <v>39</v>
-      </c>
-      <c r="S11" s="16" t="s">
-        <v>40</v>
       </c>
       <c r="T11" s="16" t="s">
         <v>39</v>
@@ -1263,9 +1300,6 @@
         <v>39</v>
       </c>
       <c r="W11" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="X11" s="16" t="s">
         <v>69</v>
       </c>
       <c r="AD11" s="6"/>
@@ -1303,16 +1337,16 @@
         <f t="shared" si="0"/>
         <v>L</v>
       </c>
-      <c r="K12" s="23">
-        <f t="array" ref="K12">IF(L12&lt;&gt;"", SUMPRODUCT(MID(N12:X12,5,1)*1), "")</f>
+      <c r="K12" s="23" cm="1">
+        <f t="array" ref="K12">IF(L12&lt;&gt;"", SUMPRODUCT(MID(N12:W12,5,1)*1), "")</f>
         <v>0</v>
       </c>
       <c r="L12" s="18">
         <v>1</v>
       </c>
-      <c r="M12" s="23">
-        <f t="array" ref="M12">IF(L12&lt;&gt;"", SUMPRODUCT(LEFT(N12:X12,1)*1), "")</f>
-        <v>10</v>
+      <c r="M12" s="23" cm="1">
+        <f t="array" ref="M12">IF(L12&lt;&gt;"", SUMPRODUCT(LEFT(N12:W12,1)*1), "")</f>
+        <v>9</v>
       </c>
       <c r="N12" s="16" t="s">
         <v>39</v>
@@ -1336,15 +1370,12 @@
         <v>39</v>
       </c>
       <c r="U12" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="V12" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="V12" s="16" t="s">
-        <v>38</v>
-      </c>
       <c r="W12" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="X12" s="16" t="s">
         <v>69</v>
       </c>
       <c r="AD12" s="6"/>
@@ -1382,16 +1413,16 @@
         <f t="shared" si="0"/>
         <v>L</v>
       </c>
-      <c r="K13" s="23">
-        <f t="array" ref="K13">IF(L13&lt;&gt;"", SUMPRODUCT(MID(N13:X13,5,1)*1), "")</f>
+      <c r="K13" s="23" cm="1">
+        <f t="array" ref="K13">IF(L13&lt;&gt;"", SUMPRODUCT(MID(N13:W13,5,1)*1), "")</f>
         <v>1</v>
       </c>
       <c r="L13" s="18">
         <v>3</v>
       </c>
-      <c r="M13" s="23">
-        <f t="array" ref="M13">IF(L13&lt;&gt;"", SUMPRODUCT(LEFT(N13:X13,1)*1), "")</f>
-        <v>10</v>
+      <c r="M13" s="23" cm="1">
+        <f t="array" ref="M13">IF(L13&lt;&gt;"", SUMPRODUCT(LEFT(N13:W13,1)*1), "")</f>
+        <v>9</v>
       </c>
       <c r="N13" s="16" t="s">
         <v>39</v>
@@ -1406,10 +1437,10 @@
         <v>39</v>
       </c>
       <c r="R13" s="16" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="S13" s="16" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="T13" s="16" t="s">
         <v>39</v>
@@ -1421,9 +1452,6 @@
         <v>39</v>
       </c>
       <c r="W13" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="X13" s="16" t="s">
         <v>69</v>
       </c>
       <c r="AD13" s="6"/>
@@ -1459,16 +1487,16 @@
         <f t="shared" si="0"/>
         <v>W</v>
       </c>
-      <c r="K14" s="23">
-        <f t="array" ref="K14">IF(L14&lt;&gt;"", SUMPRODUCT(MID(N14:X14,5,1)*1), "")</f>
+      <c r="K14" s="23" cm="1">
+        <f t="array" ref="K14">IF(L14&lt;&gt;"", SUMPRODUCT(MID(N14:W14,5,1)*1), "")</f>
         <v>12</v>
       </c>
       <c r="L14" s="26">
         <v>5</v>
       </c>
-      <c r="M14" s="23">
-        <f t="array" ref="M14">IF(L14&lt;&gt;"", SUMPRODUCT(LEFT(N14:X14,1)*1), "")</f>
-        <v>10</v>
+      <c r="M14" s="23" cm="1">
+        <f t="array" ref="M14">IF(L14&lt;&gt;"", SUMPRODUCT(LEFT(N14:W14,1)*1), "")</f>
+        <v>9</v>
       </c>
       <c r="N14" s="16" t="s">
         <v>39</v>
@@ -1483,24 +1511,21 @@
         <v>39</v>
       </c>
       <c r="R14" s="16" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="S14" s="16" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="T14" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U14" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="V14" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="V14" s="16" t="s">
-        <v>68</v>
-      </c>
       <c r="W14" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="X14" s="16" t="s">
         <v>69</v>
       </c>
       <c r="AD14" s="6"/>
@@ -1532,28 +1557,49 @@
       </c>
       <c r="J15" s="17" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K15" s="23" t="str">
-        <f t="array" ref="K15">IF(L15&lt;&gt;"", SUMPRODUCT(MID(N15:X15,5,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="L15" s="26"/>
-      <c r="M15" s="23" t="str">
-        <f t="array" ref="M15">IF(L15&lt;&gt;"", SUMPRODUCT(LEFT(N15:X15,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
+        <v>W</v>
+      </c>
+      <c r="K15" s="23" cm="1">
+        <f t="array" ref="K15">IF(L15&lt;&gt;"", SUMPRODUCT(MID(N15:W15,5,1)*1), "")</f>
+        <v>14</v>
+      </c>
+      <c r="L15" s="26">
+        <v>3</v>
+      </c>
+      <c r="M15" s="23" cm="1">
+        <f t="array" ref="M15">IF(L15&lt;&gt;"", SUMPRODUCT(LEFT(N15:W15,1)*1), "")</f>
+        <v>9</v>
+      </c>
+      <c r="N15" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="O15" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="P15" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q15" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="R15" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="S15" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T15" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="U15" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="V15" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="W15" s="16" t="s">
+        <v>74</v>
+      </c>
       <c r="AD15" s="6"/>
     </row>
     <row r="16" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1587,13 +1633,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K16" s="23" t="str">
-        <f t="array" ref="K16">IF(L16&lt;&gt;"", SUMPRODUCT(MID(N16:X16,5,1)*1), "")</f>
+      <c r="K16" s="23" t="str" cm="1">
+        <f t="array" ref="K16">IF(L16&lt;&gt;"", SUMPRODUCT(MID(N16:W16,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L16" s="26"/>
-      <c r="M16" s="23" t="str">
-        <f t="array" ref="M16">IF(L16&lt;&gt;"", SUMPRODUCT(LEFT(N16:X16,1)*1), "")</f>
+      <c r="M16" s="23" t="str" cm="1">
+        <f t="array" ref="M16">IF(L16&lt;&gt;"", SUMPRODUCT(LEFT(N16:W16,1)*1), "")</f>
         <v/>
       </c>
       <c r="N16" s="16"/>
@@ -1606,7 +1652,6 @@
       <c r="U16" s="16"/>
       <c r="V16" s="16"/>
       <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
       <c r="AD16" s="6"/>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -1638,13 +1683,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K17" s="23" t="str">
-        <f t="array" ref="K17">IF(L17&lt;&gt;"", SUMPRODUCT(MID(N17:X17,5,1)*1), "")</f>
+      <c r="K17" s="23" t="str" cm="1">
+        <f t="array" ref="K17">IF(L17&lt;&gt;"", SUMPRODUCT(MID(N17:W17,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L17" s="26"/>
-      <c r="M17" s="23" t="str">
-        <f t="array" ref="M17">IF(L17&lt;&gt;"", SUMPRODUCT(LEFT(N17:X17,1)*1), "")</f>
+      <c r="M17" s="23" t="str" cm="1">
+        <f t="array" ref="M17">IF(L17&lt;&gt;"", SUMPRODUCT(LEFT(N17:W17,1)*1), "")</f>
         <v/>
       </c>
       <c r="N17" s="16"/>
@@ -1657,7 +1702,6 @@
       <c r="U17" s="16"/>
       <c r="V17" s="16"/>
       <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
       <c r="AD17" s="6"/>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -1689,13 +1733,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K18" s="23" t="str">
-        <f t="array" ref="K18">IF(L18&lt;&gt;"", SUMPRODUCT(MID(N18:X18,5,1)*1), "")</f>
+      <c r="K18" s="23" t="str" cm="1">
+        <f t="array" ref="K18">IF(L18&lt;&gt;"", SUMPRODUCT(MID(N18:W18,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L18" s="26"/>
-      <c r="M18" s="23" t="str">
-        <f t="array" ref="M18">IF(L18&lt;&gt;"", SUMPRODUCT(LEFT(N18:X18,1)*1), "")</f>
+      <c r="M18" s="23" t="str" cm="1">
+        <f t="array" ref="M18">IF(L18&lt;&gt;"", SUMPRODUCT(LEFT(N18:W18,1)*1), "")</f>
         <v/>
       </c>
       <c r="N18" s="16"/>
@@ -1708,7 +1752,6 @@
       <c r="U18" s="16"/>
       <c r="V18" s="16"/>
       <c r="W18" s="16"/>
-      <c r="X18" s="16"/>
       <c r="AD18" s="6"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -1728,13 +1771,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K19" s="23" t="str">
-        <f t="array" ref="K19">IF(L19&lt;&gt;"", SUMPRODUCT(MID(N19:X19,5,1)*1), "")</f>
+      <c r="K19" s="23" t="str" cm="1">
+        <f t="array" ref="K19">IF(L19&lt;&gt;"", SUMPRODUCT(MID(N19:W19,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L19" s="26"/>
-      <c r="M19" s="23" t="str">
-        <f t="array" ref="M19">IF(L19&lt;&gt;"", SUMPRODUCT(LEFT(N19:X19,1)*1), "")</f>
+      <c r="M19" s="23" t="str" cm="1">
+        <f t="array" ref="M19">IF(L19&lt;&gt;"", SUMPRODUCT(LEFT(N19:W19,1)*1), "")</f>
         <v/>
       </c>
       <c r="N19" s="16"/>
@@ -1747,7 +1790,6 @@
       <c r="U19" s="16"/>
       <c r="V19" s="16"/>
       <c r="W19" s="16"/>
-      <c r="X19" s="16"/>
       <c r="AD19" s="6"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
@@ -1767,13 +1809,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K20" s="23" t="str">
-        <f t="array" ref="K20">IF(L20&lt;&gt;"", SUMPRODUCT(MID(N20:X20,5,1)*1), "")</f>
+      <c r="K20" s="23" t="str" cm="1">
+        <f t="array" ref="K20">IF(L20&lt;&gt;"", SUMPRODUCT(MID(N20:W20,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L20" s="26"/>
-      <c r="M20" s="23" t="str">
-        <f t="array" ref="M20">IF(L20&lt;&gt;"", SUMPRODUCT(LEFT(N20:X20,1)*1), "")</f>
+      <c r="M20" s="23" t="str" cm="1">
+        <f t="array" ref="M20">IF(L20&lt;&gt;"", SUMPRODUCT(LEFT(N20:W20,1)*1), "")</f>
         <v/>
       </c>
       <c r="N20" s="16"/>
@@ -1786,7 +1828,6 @@
       <c r="U20" s="16"/>
       <c r="V20" s="16"/>
       <c r="W20" s="16"/>
-      <c r="X20" s="16"/>
       <c r="AD20" s="6"/>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -1806,13 +1847,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K21" s="23" t="str">
-        <f t="array" ref="K21">IF(L21&lt;&gt;"", SUMPRODUCT(MID(N21:X21,5,1)*1), "")</f>
+      <c r="K21" s="23" t="str" cm="1">
+        <f t="array" ref="K21">IF(L21&lt;&gt;"", SUMPRODUCT(MID(N21:W21,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L21" s="26"/>
-      <c r="M21" s="23" t="str">
-        <f t="array" ref="M21">IF(L21&lt;&gt;"", SUMPRODUCT(LEFT(N21:X21,1)*1), "")</f>
+      <c r="M21" s="23" t="str" cm="1">
+        <f t="array" ref="M21">IF(L21&lt;&gt;"", SUMPRODUCT(LEFT(N21:W21,1)*1), "")</f>
         <v/>
       </c>
       <c r="N21" s="16"/>
@@ -1825,7 +1866,6 @@
       <c r="U21" s="16"/>
       <c r="V21" s="16"/>
       <c r="W21" s="16"/>
-      <c r="X21" s="16"/>
       <c r="AD21" s="6"/>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -1845,13 +1885,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K22" s="23" t="str">
-        <f t="array" ref="K22">IF(L22&lt;&gt;"", SUMPRODUCT(MID(N22:X22,5,1)*1), "")</f>
+      <c r="K22" s="23" t="str" cm="1">
+        <f t="array" ref="K22">IF(L22&lt;&gt;"", SUMPRODUCT(MID(N22:W22,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L22" s="26"/>
-      <c r="M22" s="23" t="str">
-        <f t="array" ref="M22">IF(L22&lt;&gt;"", SUMPRODUCT(LEFT(N22:X22,1)*1), "")</f>
+      <c r="M22" s="23" t="str" cm="1">
+        <f t="array" ref="M22">IF(L22&lt;&gt;"", SUMPRODUCT(LEFT(N22:W22,1)*1), "")</f>
         <v/>
       </c>
       <c r="N22" s="16"/>
@@ -1864,7 +1904,6 @@
       <c r="U22" s="16"/>
       <c r="V22" s="16"/>
       <c r="W22" s="16"/>
-      <c r="X22" s="16"/>
       <c r="AD22" s="6"/>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -1884,13 +1923,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K23" s="23" t="str">
-        <f t="array" ref="K23">IF(L23&lt;&gt;"", SUMPRODUCT(MID(N23:X23,5,1)*1), "")</f>
+      <c r="K23" s="23" t="str" cm="1">
+        <f t="array" ref="K23">IF(L23&lt;&gt;"", SUMPRODUCT(MID(N23:W23,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L23" s="26"/>
-      <c r="M23" s="23" t="str">
-        <f t="array" ref="M23">IF(L23&lt;&gt;"", SUMPRODUCT(LEFT(N23:X23,1)*1), "")</f>
+      <c r="M23" s="23" t="str" cm="1">
+        <f t="array" ref="M23">IF(L23&lt;&gt;"", SUMPRODUCT(LEFT(N23:W23,1)*1), "")</f>
         <v/>
       </c>
       <c r="N23" s="16"/>
@@ -1903,7 +1942,6 @@
       <c r="U23" s="16"/>
       <c r="V23" s="16"/>
       <c r="W23" s="16"/>
-      <c r="X23" s="16"/>
       <c r="AD23" s="6"/>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -1923,13 +1961,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K24" s="23" t="str">
-        <f t="array" ref="K24">IF(L24&lt;&gt;"", SUMPRODUCT(MID(N24:X24,5,1)*1), "")</f>
+      <c r="K24" s="23" t="str" cm="1">
+        <f t="array" ref="K24">IF(L24&lt;&gt;"", SUMPRODUCT(MID(N24:W24,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L24" s="26"/>
-      <c r="M24" s="23" t="str">
-        <f t="array" ref="M24">IF(L24&lt;&gt;"", SUMPRODUCT(LEFT(N24:X24,1)*1), "")</f>
+      <c r="M24" s="23" t="str" cm="1">
+        <f t="array" ref="M24">IF(L24&lt;&gt;"", SUMPRODUCT(LEFT(N24:W24,1)*1), "")</f>
         <v/>
       </c>
       <c r="N24" s="16"/>
@@ -1942,7 +1980,6 @@
       <c r="U24" s="16"/>
       <c r="V24" s="16"/>
       <c r="W24" s="16"/>
-      <c r="X24" s="16"/>
       <c r="AD24" s="6"/>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -1962,13 +1999,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K25" s="23" t="str">
-        <f t="array" ref="K25">IF(L25&lt;&gt;"", SUMPRODUCT(MID(N25:X25,5,1)*1), "")</f>
+      <c r="K25" s="23" t="str" cm="1">
+        <f t="array" ref="K25">IF(L25&lt;&gt;"", SUMPRODUCT(MID(N25:W25,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L25" s="26"/>
-      <c r="M25" s="23" t="str">
-        <f t="array" ref="M25">IF(L25&lt;&gt;"", SUMPRODUCT(LEFT(N25:X25,1)*1), "")</f>
+      <c r="M25" s="23" t="str" cm="1">
+        <f t="array" ref="M25">IF(L25&lt;&gt;"", SUMPRODUCT(LEFT(N25:W25,1)*1), "")</f>
         <v/>
       </c>
       <c r="N25" s="16"/>
@@ -1981,7 +2018,6 @@
       <c r="U25" s="16"/>
       <c r="V25" s="16"/>
       <c r="W25" s="16"/>
-      <c r="X25" s="16"/>
       <c r="AD25" s="6"/>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
@@ -2001,13 +2037,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K26" s="23" t="str">
-        <f t="array" ref="K26">IF(L26&lt;&gt;"", SUMPRODUCT(MID(N26:X26,5,1)*1), "")</f>
+      <c r="K26" s="23" t="str" cm="1">
+        <f t="array" ref="K26">IF(L26&lt;&gt;"", SUMPRODUCT(MID(N26:W26,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L26" s="26"/>
-      <c r="M26" s="23" t="str">
-        <f t="array" ref="M26">IF(L26&lt;&gt;"", SUMPRODUCT(LEFT(N26:X26,1)*1), "")</f>
+      <c r="M26" s="23" t="str" cm="1">
+        <f t="array" ref="M26">IF(L26&lt;&gt;"", SUMPRODUCT(LEFT(N26:W26,1)*1), "")</f>
         <v/>
       </c>
       <c r="N26" s="16"/>
@@ -2020,7 +2056,6 @@
       <c r="U26" s="16"/>
       <c r="V26" s="16"/>
       <c r="W26" s="16"/>
-      <c r="X26" s="16"/>
       <c r="AD26" s="6"/>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -2040,13 +2075,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K27" s="23" t="str">
-        <f t="array" ref="K27">IF(L27&lt;&gt;"", SUMPRODUCT(MID(N27:X27,5,1)*1), "")</f>
+      <c r="K27" s="23" t="str" cm="1">
+        <f t="array" ref="K27">IF(L27&lt;&gt;"", SUMPRODUCT(MID(N27:W27,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L27" s="18"/>
-      <c r="M27" s="23" t="str">
-        <f t="array" ref="M27">IF(L27&lt;&gt;"", SUMPRODUCT(LEFT(N27:X27,1)*1), "")</f>
+      <c r="M27" s="23" t="str" cm="1">
+        <f t="array" ref="M27">IF(L27&lt;&gt;"", SUMPRODUCT(LEFT(N27:W27,1)*1), "")</f>
         <v/>
       </c>
       <c r="N27" s="16"/>
@@ -2059,7 +2094,6 @@
       <c r="U27" s="16"/>
       <c r="V27" s="16"/>
       <c r="W27" s="16"/>
-      <c r="X27" s="16"/>
       <c r="AD27" s="6"/>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -2079,13 +2113,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K28" s="23" t="str">
-        <f t="array" ref="K28">IF(L28&lt;&gt;"", SUMPRODUCT(MID(N28:X28,5,1)*1), "")</f>
+      <c r="K28" s="23" t="str" cm="1">
+        <f t="array" ref="K28">IF(L28&lt;&gt;"", SUMPRODUCT(MID(N28:W28,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L28" s="18"/>
-      <c r="M28" s="23" t="str">
-        <f t="array" ref="M28">IF(L28&lt;&gt;"", SUMPRODUCT(LEFT(N28:X28,1)*1), "")</f>
+      <c r="M28" s="23" t="str" cm="1">
+        <f t="array" ref="M28">IF(L28&lt;&gt;"", SUMPRODUCT(LEFT(N28:W28,1)*1), "")</f>
         <v/>
       </c>
       <c r="N28" s="16"/>
@@ -2098,7 +2132,6 @@
       <c r="U28" s="16"/>
       <c r="V28" s="16"/>
       <c r="W28" s="16"/>
-      <c r="X28" s="16"/>
       <c r="AD28" s="6"/>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -2118,13 +2151,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K29" s="23" t="str">
-        <f t="array" ref="K29">IF(L29&lt;&gt;"", SUMPRODUCT(MID(N29:X29,5,1)*1), "")</f>
+      <c r="K29" s="23" t="str" cm="1">
+        <f t="array" ref="K29">IF(L29&lt;&gt;"", SUMPRODUCT(MID(N29:W29,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L29" s="18"/>
-      <c r="M29" s="23" t="str">
-        <f t="array" ref="M29">IF(L29&lt;&gt;"", SUMPRODUCT(LEFT(N29:X29,1)*1), "")</f>
+      <c r="M29" s="23" t="str" cm="1">
+        <f t="array" ref="M29">IF(L29&lt;&gt;"", SUMPRODUCT(LEFT(N29:W29,1)*1), "")</f>
         <v/>
       </c>
       <c r="N29" s="16"/>
@@ -2137,7 +2170,6 @@
       <c r="U29" s="16"/>
       <c r="V29" s="16"/>
       <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
       <c r="AD29" s="6"/>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -2157,13 +2189,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K30" s="23" t="str">
-        <f t="array" ref="K30">IF(L30&lt;&gt;"", SUMPRODUCT(MID(N30:X30,5,1)*1), "")</f>
+      <c r="K30" s="23" t="str" cm="1">
+        <f t="array" ref="K30">IF(L30&lt;&gt;"", SUMPRODUCT(MID(N30:W30,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L30" s="18"/>
-      <c r="M30" s="23" t="str">
-        <f t="array" ref="M30">IF(L30&lt;&gt;"", SUMPRODUCT(LEFT(N30:X30,1)*1), "")</f>
+      <c r="M30" s="23" t="str" cm="1">
+        <f t="array" ref="M30">IF(L30&lt;&gt;"", SUMPRODUCT(LEFT(N30:W30,1)*1), "")</f>
         <v/>
       </c>
       <c r="N30" s="16"/>
@@ -2176,7 +2208,6 @@
       <c r="U30" s="16"/>
       <c r="V30" s="16"/>
       <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
       <c r="AD30" s="6"/>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -2196,13 +2227,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K31" s="23" t="str">
-        <f t="array" ref="K31">IF(L31&lt;&gt;"", SUMPRODUCT(MID(N31:X31,5,1)*1), "")</f>
+      <c r="K31" s="23" t="str" cm="1">
+        <f t="array" ref="K31">IF(L31&lt;&gt;"", SUMPRODUCT(MID(N31:W31,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L31" s="18"/>
-      <c r="M31" s="23" t="str">
-        <f t="array" ref="M31">IF(L31&lt;&gt;"", SUMPRODUCT(LEFT(N31:X31,1)*1), "")</f>
+      <c r="M31" s="23" t="str" cm="1">
+        <f t="array" ref="M31">IF(L31&lt;&gt;"", SUMPRODUCT(LEFT(N31:W31,1)*1), "")</f>
         <v/>
       </c>
       <c r="N31" s="16"/>
@@ -2215,7 +2246,6 @@
       <c r="U31" s="16"/>
       <c r="V31" s="16"/>
       <c r="W31" s="16"/>
-      <c r="X31" s="16"/>
       <c r="AD31" s="6"/>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
@@ -2235,13 +2265,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K32" s="23" t="str">
-        <f t="array" ref="K32">IF(L32&lt;&gt;"", SUMPRODUCT(MID(N32:X32,5,1)*1), "")</f>
+      <c r="K32" s="23" t="str" cm="1">
+        <f t="array" ref="K32">IF(L32&lt;&gt;"", SUMPRODUCT(MID(N32:W32,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L32" s="18"/>
-      <c r="M32" s="23" t="str">
-        <f t="array" ref="M32">IF(L32&lt;&gt;"", SUMPRODUCT(LEFT(N32:X32,1)*1), "")</f>
+      <c r="M32" s="23" t="str" cm="1">
+        <f t="array" ref="M32">IF(L32&lt;&gt;"", SUMPRODUCT(LEFT(N32:W32,1)*1), "")</f>
         <v/>
       </c>
       <c r="N32" s="16"/>
@@ -2254,7 +2284,6 @@
       <c r="U32" s="16"/>
       <c r="V32" s="16"/>
       <c r="W32" s="16"/>
-      <c r="X32" s="16"/>
       <c r="AD32" s="6"/>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -2274,13 +2303,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K33" s="23" t="str">
-        <f t="array" ref="K33">IF(L33&lt;&gt;"", SUMPRODUCT(MID(N33:X33,5,1)*1), "")</f>
+      <c r="K33" s="23" t="str" cm="1">
+        <f t="array" ref="K33">IF(L33&lt;&gt;"", SUMPRODUCT(MID(N33:W33,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L33" s="18"/>
-      <c r="M33" s="23" t="str">
-        <f t="array" ref="M33">IF(L33&lt;&gt;"", SUMPRODUCT(LEFT(N33:X33,1)*1), "")</f>
+      <c r="M33" s="23" t="str" cm="1">
+        <f t="array" ref="M33">IF(L33&lt;&gt;"", SUMPRODUCT(LEFT(N33:W33,1)*1), "")</f>
         <v/>
       </c>
       <c r="N33" s="16"/>
@@ -2293,7 +2322,6 @@
       <c r="U33" s="16"/>
       <c r="V33" s="16"/>
       <c r="W33" s="16"/>
-      <c r="X33" s="16"/>
       <c r="AD33" s="6"/>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
@@ -2313,13 +2341,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K34" s="23" t="str">
-        <f t="array" ref="K34">IF(L34&lt;&gt;"", SUMPRODUCT(MID(N34:X34,5,1)*1), "")</f>
+      <c r="K34" s="23" t="str" cm="1">
+        <f t="array" ref="K34">IF(L34&lt;&gt;"", SUMPRODUCT(MID(N34:W34,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L34" s="18"/>
-      <c r="M34" s="23" t="str">
-        <f t="array" ref="M34">IF(L34&lt;&gt;"", SUMPRODUCT(LEFT(N34:X34,1)*1), "")</f>
+      <c r="M34" s="23" t="str" cm="1">
+        <f t="array" ref="M34">IF(L34&lt;&gt;"", SUMPRODUCT(LEFT(N34:W34,1)*1), "")</f>
         <v/>
       </c>
       <c r="N34" s="16"/>
@@ -2332,7 +2360,6 @@
       <c r="U34" s="16"/>
       <c r="V34" s="16"/>
       <c r="W34" s="16"/>
-      <c r="X34" s="16"/>
       <c r="AD34" s="6"/>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -2352,13 +2379,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K35" s="23" t="str">
-        <f t="array" ref="K35">IF(L35&lt;&gt;"", SUMPRODUCT(MID(N35:X35,5,1)*1), "")</f>
+      <c r="K35" s="23" t="str" cm="1">
+        <f t="array" ref="K35">IF(L35&lt;&gt;"", SUMPRODUCT(MID(N35:W35,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L35" s="18"/>
-      <c r="M35" s="23" t="str">
-        <f t="array" ref="M35">IF(L35&lt;&gt;"", SUMPRODUCT(LEFT(N35:X35,1)*1), "")</f>
+      <c r="M35" s="23" t="str" cm="1">
+        <f t="array" ref="M35">IF(L35&lt;&gt;"", SUMPRODUCT(LEFT(N35:W35,1)*1), "")</f>
         <v/>
       </c>
       <c r="N35" s="16"/>
@@ -2371,7 +2398,6 @@
       <c r="U35" s="16"/>
       <c r="V35" s="16"/>
       <c r="W35" s="16"/>
-      <c r="X35" s="16"/>
       <c r="AD35" s="6"/>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
@@ -2391,13 +2417,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K36" s="23" t="str">
-        <f t="array" ref="K36">IF(L36&lt;&gt;"", SUMPRODUCT(MID(N36:X36,5,1)*1), "")</f>
+      <c r="K36" s="23" t="str" cm="1">
+        <f t="array" ref="K36">IF(L36&lt;&gt;"", SUMPRODUCT(MID(N36:W36,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L36" s="26"/>
-      <c r="M36" s="23" t="str">
-        <f t="array" ref="M36">IF(L36&lt;&gt;"", SUMPRODUCT(LEFT(N36:X36,1)*1), "")</f>
+      <c r="M36" s="23" t="str" cm="1">
+        <f t="array" ref="M36">IF(L36&lt;&gt;"", SUMPRODUCT(LEFT(N36:W36,1)*1), "")</f>
         <v/>
       </c>
       <c r="N36" s="16"/>
@@ -2410,7 +2436,6 @@
       <c r="U36" s="16"/>
       <c r="V36" s="16"/>
       <c r="W36" s="16"/>
-      <c r="X36" s="16"/>
       <c r="AD36" s="6"/>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
@@ -2430,13 +2455,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K37" s="23" t="str">
-        <f t="array" ref="K37">IF(L37&lt;&gt;"", SUMPRODUCT(MID(N37:X37,5,1)*1), "")</f>
+      <c r="K37" s="23" t="str" cm="1">
+        <f t="array" ref="K37">IF(L37&lt;&gt;"", SUMPRODUCT(MID(N37:W37,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L37" s="18"/>
-      <c r="M37" s="23" t="str">
-        <f t="array" ref="M37">IF(L37&lt;&gt;"", SUMPRODUCT(LEFT(N37:X37,1)*1), "")</f>
+      <c r="M37" s="23" t="str" cm="1">
+        <f t="array" ref="M37">IF(L37&lt;&gt;"", SUMPRODUCT(LEFT(N37:W37,1)*1), "")</f>
         <v/>
       </c>
       <c r="N37" s="16"/>
@@ -2449,7 +2474,6 @@
       <c r="U37" s="16"/>
       <c r="V37" s="16"/>
       <c r="W37" s="16"/>
-      <c r="X37" s="16"/>
       <c r="AD37" s="6"/>
     </row>
     <row r="38" spans="1:30" x14ac:dyDescent="0.25">
@@ -2469,13 +2493,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K38" s="23" t="str">
-        <f t="array" ref="K38">IF(L38&lt;&gt;"", SUMPRODUCT(MID(N38:X38,5,1)*1), "")</f>
+      <c r="K38" s="23" t="str" cm="1">
+        <f t="array" ref="K38">IF(L38&lt;&gt;"", SUMPRODUCT(MID(N38:W38,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L38" s="18"/>
-      <c r="M38" s="23" t="str">
-        <f t="array" ref="M38">IF(L38&lt;&gt;"", SUMPRODUCT(LEFT(N38:X38,1)*1), "")</f>
+      <c r="M38" s="23" t="str" cm="1">
+        <f t="array" ref="M38">IF(L38&lt;&gt;"", SUMPRODUCT(LEFT(N38:W38,1)*1), "")</f>
         <v/>
       </c>
       <c r="N38" s="16"/>
@@ -2488,7 +2512,6 @@
       <c r="U38" s="16"/>
       <c r="V38" s="16"/>
       <c r="W38" s="16"/>
-      <c r="X38" s="16"/>
       <c r="AD38" s="6"/>
     </row>
     <row r="39" spans="1:30" x14ac:dyDescent="0.25">
@@ -2508,13 +2531,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K39" s="23" t="str">
-        <f t="array" ref="K39">IF(L39&lt;&gt;"", SUMPRODUCT(MID(N39:X39,5,1)*1), "")</f>
+      <c r="K39" s="23" t="str" cm="1">
+        <f t="array" ref="K39">IF(L39&lt;&gt;"", SUMPRODUCT(MID(N39:W39,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L39" s="18"/>
-      <c r="M39" s="23" t="str">
-        <f t="array" ref="M39">IF(L39&lt;&gt;"", SUMPRODUCT(LEFT(N39:X39,1)*1), "")</f>
+      <c r="M39" s="23" t="str" cm="1">
+        <f t="array" ref="M39">IF(L39&lt;&gt;"", SUMPRODUCT(LEFT(N39:W39,1)*1), "")</f>
         <v/>
       </c>
       <c r="N39" s="16"/>
@@ -2527,7 +2550,6 @@
       <c r="U39" s="16"/>
       <c r="V39" s="16"/>
       <c r="W39" s="16"/>
-      <c r="X39" s="16"/>
       <c r="AD39" s="6"/>
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.25">
@@ -2547,13 +2569,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K40" s="23" t="str">
-        <f t="array" ref="K40">IF(L40&lt;&gt;"", SUMPRODUCT(MID(N40:X40,5,1)*1), "")</f>
+      <c r="K40" s="23" t="str" cm="1">
+        <f t="array" ref="K40">IF(L40&lt;&gt;"", SUMPRODUCT(MID(N40:W40,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L40" s="18"/>
-      <c r="M40" s="23" t="str">
-        <f t="array" ref="M40">IF(L40&lt;&gt;"", SUMPRODUCT(LEFT(N40:X40,1)*1), "")</f>
+      <c r="M40" s="23" t="str" cm="1">
+        <f t="array" ref="M40">IF(L40&lt;&gt;"", SUMPRODUCT(LEFT(N40:W40,1)*1), "")</f>
         <v/>
       </c>
       <c r="N40" s="16"/>
@@ -2566,7 +2588,6 @@
       <c r="U40" s="16"/>
       <c r="V40" s="16"/>
       <c r="W40" s="16"/>
-      <c r="X40" s="16"/>
       <c r="AD40" s="6"/>
     </row>
     <row r="41" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
@@ -2680,36 +2701,33 @@
         <v>4</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="K44" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="K44" s="16" t="s">
+        <v>32</v>
+      </c>
       <c r="L44" s="16" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="M44" s="16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N44" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="O44" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="P44" s="6"/>
+      <c r="O44" s="6"/>
       <c r="T44" s="6"/>
       <c r="U44" s="6"/>
       <c r="V44" s="6"/>
@@ -2745,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" s="6">
         <v>1</v>
@@ -2759,10 +2777,9 @@
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
-      <c r="O45" s="6"/>
-      <c r="P45" s="28">
-        <f t="shared" ref="P45:P48" si="2">SUM(B45:O45)</f>
-        <v>10</v>
+      <c r="O45" s="28">
+        <f t="shared" ref="O45:O48" si="2">SUM(A45:N45)</f>
+        <v>9</v>
       </c>
       <c r="T45" s="6"/>
       <c r="U45" s="6"/>
@@ -2793,13 +2810,13 @@
         <v>1</v>
       </c>
       <c r="F46" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="6">
         <v>1</v>
       </c>
       <c r="H46" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="6">
         <v>1</v>
@@ -2813,8 +2830,7 @@
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="28">
+      <c r="O46" s="28">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
@@ -2838,39 +2854,38 @@
         <v>0</v>
       </c>
       <c r="C47" s="6">
+        <v>4</v>
+      </c>
+      <c r="D47" s="6">
+        <v>2</v>
+      </c>
+      <c r="E47" s="6">
         <v>1</v>
       </c>
-      <c r="D47" s="6">
+      <c r="F47" s="6">
+        <v>1</v>
+      </c>
+      <c r="G47" s="6">
         <v>0</v>
       </c>
-      <c r="E47" s="6">
+      <c r="H47" s="6">
         <v>0</v>
       </c>
-      <c r="F47" s="6">
-        <v>0</v>
-      </c>
-      <c r="G47" s="6">
-        <v>8</v>
-      </c>
-      <c r="H47" s="6">
-        <v>1</v>
-      </c>
       <c r="I47" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J47" s="6">
         <v>2</v>
       </c>
       <c r="K47" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
-      <c r="O47" s="6"/>
-      <c r="P47" s="28">
+      <c r="O47" s="28">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T47" s="6"/>
       <c r="U47" s="6"/>
@@ -2889,22 +2904,22 @@
         <v>64</v>
       </c>
       <c r="B48" s="6">
+        <v>4</v>
+      </c>
+      <c r="C48" s="6">
+        <v>1</v>
+      </c>
+      <c r="D48" s="6">
         <v>0</v>
       </c>
-      <c r="C48" s="6">
-        <v>3</v>
-      </c>
-      <c r="D48" s="6">
+      <c r="E48" s="6">
         <v>1</v>
-      </c>
-      <c r="E48" s="6">
-        <v>0</v>
       </c>
       <c r="F48" s="6">
         <v>0</v>
       </c>
       <c r="G48" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="6">
         <v>0</v>
@@ -2913,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K48" s="6">
         <v>0</v>
@@ -2921,8 +2936,7 @@
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
-      <c r="O48" s="6"/>
-      <c r="P48" s="28">
+      <c r="O48" s="28">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
@@ -2942,61 +2956,57 @@
       <c r="A49" s="6"/>
       <c r="B49" s="6" t="str">
         <f t="shared" ref="B49:O49" si="3">B45&amp;","&amp;B46&amp;","&amp;B47&amp;","&amp;B48</f>
-        <v>1,1,0,0</v>
+        <v>1,1,0,4</v>
       </c>
       <c r="C49" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>1,1,1,3</v>
+        <v>1,1,4,1</v>
       </c>
       <c r="D49" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>1,0,0,1</v>
+        <v>1,0,2,0</v>
       </c>
       <c r="E49" s="6" t="str">
         <f t="shared" si="3"/>
+        <v>1,1,1,1</v>
+      </c>
+      <c r="F49" s="6" t="str">
+        <f t="shared" ref="F49:Q49" si="4">F45&amp;","&amp;F46&amp;","&amp;F47&amp;","&amp;F48</f>
+        <v>1,1,1,0</v>
+      </c>
+      <c r="G49" s="6" t="str">
+        <f t="shared" si="4"/>
         <v>1,1,0,0</v>
       </c>
-      <c r="F49" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>1,0,0,0</v>
-      </c>
-      <c r="G49" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>1,1,8,1</v>
-      </c>
       <c r="H49" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>1,1,1,0</v>
+        <f t="shared" si="4"/>
+        <v>0,0,0,0</v>
       </c>
       <c r="I49" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>1,1,0,0</v>
+        <f t="shared" si="4"/>
+        <v>1,1,2,0</v>
       </c>
       <c r="J49" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>1,1,2,2</v>
+        <f t="shared" si="4"/>
+        <v>1,1,2,1</v>
       </c>
       <c r="K49" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>1,1,0,0</v>
+        <f t="shared" si="4"/>
+        <v>1,1,2,0</v>
       </c>
       <c r="L49" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>,,,</v>
       </c>
       <c r="M49" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>,,,</v>
       </c>
       <c r="N49" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>,,,</v>
       </c>
-      <c r="O49" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>,,,</v>
-      </c>
-      <c r="P49" s="6"/>
+      <c r="O49" s="6"/>
       <c r="T49" s="6"/>
       <c r="U49" s="6"/>
       <c r="V49" s="6"/>
@@ -33128,31 +33138,31 @@
       </c>
       <c r="C2" s="10">
         <f t="array" ref="C2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="10">
         <f t="array" ref="D2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z42, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="10">
         <f t="array" ref="E2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="10">
         <f t="array" ref="F2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="10">
+        <v>5</v>
+      </c>
+      <c r="G2" s="10" t="e">
         <f t="array" ref="G2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>#N/A</v>
       </c>
       <c r="H2" s="10">
         <f t="array" ref="H2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" s="10">
         <f t="array" ref="I2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" s="10">
         <f t="array" ref="J2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
@@ -33160,11 +33170,11 @@
       </c>
       <c r="K2" s="10">
         <f t="array" ref="K2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" s="10">
         <f t="array" ref="L2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(L$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -33198,9 +33208,9 @@
         <f>F2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="24" t="e">
         <f>G2/MatchesDB!$B$1</f>
-        <v>1</v>
+        <v>#N/A</v>
       </c>
       <c r="H3" s="24">
         <f>H2/MatchesDB!$B$1</f>
@@ -33210,9 +33220,9 @@
         <f>I2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="J3" s="24" t="e">
+      <c r="J3" s="24">
         <f>J2/(MatchesDB!$B$1-4)</f>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
       <c r="K3" s="24">
         <f>K2/MatchesDB!$B$1</f>
@@ -33242,11 +33252,11 @@
       </c>
       <c r="C4" s="25">
         <f t="array" ref="C4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="25">
         <f t="array" ref="D4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" s="25">
         <f t="array" ref="E4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
@@ -33254,19 +33264,19 @@
       </c>
       <c r="F4" s="25">
         <f t="array" ref="F4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="G4" s="25">
+        <v>4</v>
+      </c>
+      <c r="G4" s="25" t="e">
         <f t="array" ref="G4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>2</v>
+        <v>#N/A</v>
       </c>
       <c r="H4" s="25">
         <f t="array" ref="H4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I4" s="25">
         <f t="array" ref="I4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" s="25">
         <f t="array" ref="J4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
@@ -33274,11 +33284,11 @@
       </c>
       <c r="K4" s="25">
         <f t="array" ref="K4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4" s="25">
         <f t="array" ref="L4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(L$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
@@ -33298,7 +33308,7 @@
       </c>
       <c r="C5" s="24">
         <f t="shared" ref="C5:L5" si="0">C4/C2</f>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D5" s="24">
         <f t="shared" si="0"/>
@@ -33306,19 +33316,19 @@
       </c>
       <c r="E5" s="24">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F5" s="24">
         <f t="shared" si="0"/>
-        <v>0.75</v>
-      </c>
-      <c r="G5" s="24">
+        <v>0.8</v>
+      </c>
+      <c r="G5" s="24" t="e">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>#N/A</v>
       </c>
       <c r="H5" s="24">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="I5" s="24">
         <f t="shared" si="0"/>
@@ -33330,7 +33340,7 @@
       </c>
       <c r="K5" s="24">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="L5" s="24">
         <f t="shared" si="0"/>
@@ -33360,15 +33370,15 @@
       </c>
       <c r="D6" s="10">
         <f t="array" ref="D6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E6" s="10">
         <f t="array" ref="E6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="10">
         <f t="array" ref="F6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="10">
         <f t="array" ref="G6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
@@ -33376,7 +33386,7 @@
       </c>
       <c r="H6" s="10">
         <f t="array" ref="H6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" s="10">
         <f t="array" ref="I6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
@@ -33388,11 +33398,11 @@
       </c>
       <c r="K6" s="10">
         <f t="array" ref="K6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L6" s="10">
         <f t="array" ref="L6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(L$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
@@ -33416,27 +33426,27 @@
       </c>
       <c r="D7" s="27">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="E7" s="27">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F7" s="27">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="27" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="H7" s="27">
         <f t="shared" si="1"/>
-        <v>2.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I7" s="27">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J7" s="27">
         <f t="shared" si="1"/>
@@ -33444,11 +33454,11 @@
       </c>
       <c r="K7" s="27">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L7" s="27">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
@@ -33470,11 +33480,11 @@
       </c>
       <c r="C8" s="25">
         <f t="array" ref="C8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D8" s="25">
         <f t="array" ref="D8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="25">
         <f t="array" ref="E8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
@@ -33482,7 +33492,7 @@
       </c>
       <c r="F8" s="25">
         <f t="array" ref="F8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="25">
         <f t="array" ref="G8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
@@ -33506,7 +33516,7 @@
       </c>
       <c r="L8" s="25">
         <f t="array" ref="L8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(L$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
@@ -33526,7 +33536,7 @@
       </c>
       <c r="C9" s="27">
         <f t="shared" ref="C9:L9" si="2">C8/C2</f>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D9" s="27">
         <f t="shared" si="2"/>
@@ -33534,19 +33544,19 @@
       </c>
       <c r="E9" s="27">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F9" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="27" t="e">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="H9" s="27">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="I9" s="27">
         <f t="shared" si="2"/>
@@ -33558,11 +33568,11 @@
       </c>
       <c r="K9" s="27">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L9" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
@@ -33584,19 +33594,19 @@
       </c>
       <c r="C10" s="10">
         <f t="shared" ref="C10:L10" si="3">C6+C8</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D10" s="10">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E10" s="10">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="10">
         <f t="shared" si="3"/>
@@ -33604,7 +33614,7 @@
       </c>
       <c r="H10" s="10">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I10" s="10">
         <f t="shared" si="3"/>
@@ -33616,11 +33626,11 @@
       </c>
       <c r="K10" s="10">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L10" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
@@ -33640,31 +33650,31 @@
       </c>
       <c r="C11" s="27">
         <f t="shared" ref="C11:L11" si="4">C10/C2</f>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D11" s="27">
         <f t="shared" si="4"/>
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="E11" s="27">
         <f t="shared" si="4"/>
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="F11" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="27">
+        <v>0.4</v>
+      </c>
+      <c r="G11" s="27" t="e">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="H11" s="27">
         <f t="shared" si="4"/>
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="I11" s="27">
         <f t="shared" si="4"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J11" s="27">
         <f t="shared" si="4"/>
@@ -33672,11 +33682,11 @@
       </c>
       <c r="K11" s="27">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L11" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>

--- a/JO12-1/JO12-1_matchesDB.xlsx
+++ b/JO12-1/JO12-1_matchesDB.xlsx
@@ -10,14 +10,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="aHSKc9kpOFk2TJvwiUrvHIbgmoLibm6Va0T7UVBaHFs="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="jYPGeq9R/EaEgA2pODhYN+9vkUgVoQKAkVagaeyIflw="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="81">
   <si>
     <t>Matches</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>Hugo</t>
-  </si>
-  <si>
-    <t>Micah</t>
   </si>
   <si>
     <t>Miron</t>
@@ -121,6 +118,9 @@
     <t>Antek</t>
   </si>
   <si>
+    <t>Ilay</t>
+  </si>
+  <si>
     <t>NVC Givaudan Kick-off Zomertornooi</t>
   </si>
   <si>
@@ -148,7 +148,13 @@
     <t>KFC</t>
   </si>
   <si>
+    <t>%</t>
+  </si>
+  <si>
     <t>SDO JO 12-1</t>
+  </si>
+  <si>
+    <t>1st lineup</t>
   </si>
   <si>
     <t>1,1,0,1</t>
@@ -222,13 +228,16 @@
     <t>Sporting Martinus O12-2</t>
   </si>
   <si>
-    <t>Amstelveen/Heemraad O12-1</t>
+    <t>1,1,3,1</t>
   </si>
   <si>
-    <t>%</t>
+    <t>1,1,3,2</t>
   </si>
   <si>
-    <t>1st lineup</t>
+    <t>1,0,0,2</t>
+  </si>
+  <si>
+    <t>Amstelveen/Heemraad O12-1</t>
   </si>
   <si>
     <t>Scorers</t>
@@ -240,7 +249,7 @@
     <t>Assists</t>
   </si>
   <si>
-    <t>Player2</t>
+    <t>Goal contribution</t>
   </si>
   <si>
     <t>Player3</t>
@@ -253,9 +262,6 @@
   </si>
   <si>
     <t>assist</t>
-  </si>
-  <si>
-    <t>Goal contribution</t>
   </si>
 </sst>
 </file>
@@ -273,12 +279,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -347,6 +353,20 @@
   <borders count="11">
     <border/>
     <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -354,20 +374,6 @@
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
@@ -386,17 +392,6 @@
       </bottom>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color rgb="FF000000"/>
@@ -407,6 +402,17 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
     </border>
     <border>
       <left style="medium">
@@ -467,86 +473,89 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="5" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="6" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="7" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="8" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="9" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="16" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="16" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -774,15 +783,15 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7">
+      <c r="B1" s="6">
         <f>SUM(COUNTIF(J11:J40,"W"),COUNTIF(J11:J40,"D"),COUNTIF(J11:J40,"L"))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C1" s="5"/>
-      <c r="D1" s="8">
+      <c r="D1" s="7">
         <v>123.0</v>
       </c>
       <c r="E1" s="5"/>
@@ -814,11 +823,11 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="10">
         <f>COUNTIF(J11:J40,"W")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -851,7 +860,7 @@
     </row>
     <row r="3">
       <c r="A3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="10">
         <f>COUNTIF(J11:J40,"L")</f>
@@ -888,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="10">
         <f>COUNTIF(J11:J40,"D")</f>
@@ -925,11 +934,11 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="10">
         <f>B2*3+B4</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -962,11 +971,11 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="10">
         <f>B7-B8</f>
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -999,11 +1008,11 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="10">
         <f>SUM(K11:K40)</f>
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1035,12 +1044,12 @@
       <c r="AD7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="12">
+      <c r="A8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="13">
         <f>SUM(L11:L40)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1085,18 +1094,18 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
       <c r="V9" s="5"/>
-      <c r="W9" s="13"/>
+      <c r="W9" s="14"/>
       <c r="X9" s="5"/>
-      <c r="Y9" s="13"/>
+      <c r="Y9" s="5"/>
       <c r="Z9" s="5"/>
       <c r="AA9" s="5"/>
       <c r="AB9" s="5"/>
@@ -1104,44 +1113,44 @@
       <c r="AD9" s="5"/>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="C10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="D10" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="E10" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="F10" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="G10" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="H10" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="I10" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="J10" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="K10" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="L10" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="L10" s="15" t="s">
+      <c r="M10" s="16" t="s">
         <v>30</v>
-      </c>
-      <c r="M10" s="15" t="s">
-        <v>31</v>
       </c>
       <c r="N10" s="4" t="s">
         <v>1</v>
@@ -1156,1452 +1165,1523 @@
         <v>4</v>
       </c>
       <c r="R10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="S10" s="4" t="s">
+      <c r="T10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="T10" s="4" t="s">
+      <c r="U10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="U10" s="4" t="s">
+      <c r="V10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="V10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="W10" s="16" t="s">
+      <c r="W10" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="X10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="X10" s="4" t="s">
+      <c r="Y10" s="18" t="s">
         <v>33</v>
       </c>
       <c r="AD10" s="5"/>
     </row>
     <row r="11">
-      <c r="A11" s="18">
+      <c r="A11" s="19">
         <f>IF(ISBLANK(B11),"",1)</f>
         <v>1</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="20">
         <v>1.0</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="21">
         <v>46256.0</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="22">
         <v>0.5555555555555556</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="18" t="str">
+      <c r="J11" s="19" t="str">
         <f t="shared" ref="J11:J40" si="1">IF(AND(NOT(ISBLANK(K11)),NOT(ISBLANK(L11))),IF(K11&gt;L11,"W",IF(K11&lt;L11,"L","D")),"")</f>
         <v>L</v>
       </c>
-      <c r="K11" s="23">
-        <f t="array" ref="K11">IF(L11&lt;&gt;"", SUMPRODUCT(MID(N11:X11,5,1)*1), "")</f>
+      <c r="K11" s="24">
+        <f t="array" ref="K11">IF(L11&lt;&gt;"", SUMPRODUCT(MID(N11:Y11,5,1)*1), "")</f>
         <v>1</v>
       </c>
-      <c r="L11" s="19">
+      <c r="L11" s="20">
         <v>2.0</v>
       </c>
-      <c r="M11" s="23">
-        <f t="array" ref="M11">IF(L11&lt;&gt;"", SUMPRODUCT(LEFT(N11:X11,1)*1), "")</f>
+      <c r="M11" s="24">
+        <f t="array" ref="M11">IF(L11&lt;&gt;"", SUMPRODUCT(LEFT(N11:Y11,1)*1), "")</f>
         <v>9</v>
       </c>
-      <c r="N11" s="16" t="s">
+      <c r="N11" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O11" s="16" t="s">
+      <c r="O11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="P11" s="16" t="s">
+      <c r="P11" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="Q11" s="16" t="s">
+      <c r="Q11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="R11" s="16" t="s">
+      <c r="R11" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="S11" s="16" t="s">
+      <c r="S11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="T11" s="16" t="s">
+      <c r="T11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="U11" s="16" t="s">
+      <c r="U11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="V11" s="16" t="s">
+      <c r="V11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="W11" s="16" t="s">
+      <c r="W11" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="X11" s="16" t="s">
+      <c r="X11" s="17" t="s">
         <v>41</v>
       </c>
+      <c r="Y11" s="17" t="s">
+        <v>41</v>
+      </c>
       <c r="AD11" s="5"/>
     </row>
     <row r="12">
-      <c r="A12" s="18">
+      <c r="A12" s="19">
         <f t="shared" ref="A12:A40" si="2">IF(ISBLANK(B12),"",A11+1)</f>
         <v>2</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="20">
         <v>1.0</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="21">
         <v>46256.0</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="22">
         <v>0.5972222222222222</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="H12" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="19" t="s">
+      <c r="I12" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="J12" s="18" t="str">
+      <c r="J12" s="19" t="str">
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="K12" s="23">
-        <f t="array" ref="K12">IF(L12&lt;&gt;"", SUMPRODUCT(MID(N12:X12,5,1)*1), "")</f>
+      <c r="K12" s="24">
+        <f t="array" ref="K12">IF(L12&lt;&gt;"", SUMPRODUCT(MID(N12:Y12,5,1)*1), "")</f>
         <v>0</v>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="20">
         <v>1.0</v>
       </c>
-      <c r="M12" s="23">
-        <f t="array" ref="M12">IF(L12&lt;&gt;"", SUMPRODUCT(LEFT(N12:X12,1)*1), "")</f>
+      <c r="M12" s="24">
+        <f t="array" ref="M12">IF(L12&lt;&gt;"", SUMPRODUCT(LEFT(N12:Y12,1)*1), "")</f>
         <v>9</v>
       </c>
-      <c r="N12" s="16" t="s">
+      <c r="N12" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O12" s="16" t="s">
+      <c r="O12" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="P12" s="16" t="s">
+      <c r="P12" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="Q12" s="16" t="s">
+      <c r="Q12" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="R12" s="16" t="s">
+      <c r="R12" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="S12" s="16" t="s">
+      <c r="S12" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="T12" s="16" t="s">
+      <c r="T12" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="U12" s="16" t="s">
+      <c r="U12" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="V12" s="16" t="s">
+      <c r="V12" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="W12" s="16" t="s">
+      <c r="W12" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="X12" s="16" t="s">
+      <c r="X12" s="17" t="s">
         <v>41</v>
       </c>
+      <c r="Y12" s="17" t="s">
+        <v>41</v>
+      </c>
       <c r="AD12" s="5"/>
     </row>
     <row r="13">
-      <c r="A13" s="18">
+      <c r="A13" s="19">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="20">
         <v>1.0</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <v>46256.0</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="22">
         <v>0.6388888888888888</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="H13" s="19" t="s">
+      <c r="G13" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="19" t="s">
+      <c r="I13" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="18" t="str">
+      <c r="J13" s="19" t="str">
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="K13" s="23">
-        <f t="array" ref="K13">IF(L13&lt;&gt;"", SUMPRODUCT(MID(N13:X13,5,1)*1), "")</f>
+      <c r="K13" s="24">
+        <f t="array" ref="K13">IF(L13&lt;&gt;"", SUMPRODUCT(MID(N13:Y13,5,1)*1), "")</f>
         <v>1</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="20">
         <v>3.0</v>
       </c>
-      <c r="M13" s="23">
-        <f t="array" ref="M13">IF(L13&lt;&gt;"", SUMPRODUCT(LEFT(N13:X13,1)*1), "")</f>
+      <c r="M13" s="24">
+        <f t="array" ref="M13">IF(L13&lt;&gt;"", SUMPRODUCT(LEFT(N13:Y13,1)*1), "")</f>
         <v>9</v>
       </c>
-      <c r="N13" s="16" t="s">
+      <c r="N13" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="P13" s="16" t="s">
+      <c r="O13" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="P13" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="Q13" s="16" t="s">
+      <c r="Q13" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="R13" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="S13" s="16" t="s">
+      <c r="R13" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="S13" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="T13" s="16" t="s">
+      <c r="T13" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="U13" s="16" t="s">
+      <c r="U13" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="V13" s="16" t="s">
+      <c r="V13" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="W13" s="16" t="s">
+      <c r="W13" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="X13" s="16" t="s">
+      <c r="X13" s="17" t="s">
         <v>41</v>
       </c>
+      <c r="Y13" s="17" t="s">
+        <v>41</v>
+      </c>
       <c r="AD13" s="5"/>
     </row>
     <row r="14">
-      <c r="A14" s="18">
+      <c r="A14" s="19">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="20">
         <v>1.0</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="20">
+      <c r="C14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="21">
         <v>46270.0</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="22">
         <v>0.4166666666666667</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="I14" s="19" t="s">
+      <c r="F14" s="20"/>
+      <c r="G14" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="J14" s="18" t="str">
+      <c r="J14" s="19" t="str">
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="K14" s="23">
-        <f t="array" ref="K14">IF(L14&lt;&gt;"", SUMPRODUCT(MID(N14:X14,5,1)*1), "")</f>
+      <c r="K14" s="24">
+        <f t="array" ref="K14">IF(L14&lt;&gt;"", SUMPRODUCT(MID(N14:Y14,5,1)*1), "")</f>
         <v>12</v>
       </c>
-      <c r="L14" s="24">
+      <c r="L14" s="28">
         <v>5.0</v>
       </c>
-      <c r="M14" s="23">
-        <f t="array" ref="M14">IF(L14&lt;&gt;"", SUMPRODUCT(LEFT(N14:X14,1)*1), "")</f>
+      <c r="M14" s="24">
+        <f t="array" ref="M14">IF(L14&lt;&gt;"", SUMPRODUCT(LEFT(N14:Y14,1)*1), "")</f>
         <v>9</v>
       </c>
-      <c r="N14" s="16" t="s">
+      <c r="N14" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O14" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="P14" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q14" s="16" t="s">
+      <c r="O14" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="P14" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q14" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="R14" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="S14" s="16" t="s">
+      <c r="R14" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="S14" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="T14" s="16" t="s">
+      <c r="T14" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="U14" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="V14" s="16" t="s">
+      <c r="U14" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="V14" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="W14" s="16" t="s">
+      <c r="W14" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="X14" s="16" t="s">
+      <c r="X14" s="17" t="s">
         <v>41</v>
       </c>
+      <c r="Y14" s="17" t="s">
+        <v>41</v>
+      </c>
       <c r="AD14" s="5"/>
     </row>
     <row r="15">
-      <c r="A15" s="18">
+      <c r="A15" s="19">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="20">
         <v>1.0</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="20">
+      <c r="C15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="21">
         <v>46277.0</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="22">
         <v>0.375</v>
       </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="J15" s="18" t="str">
+      <c r="F15" s="20"/>
+      <c r="G15" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="J15" s="19" t="str">
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="K15" s="23">
-        <f t="array" ref="K15">IF(L15&lt;&gt;"", SUMPRODUCT(MID(N15:X15,5,1)*1), "")</f>
+      <c r="K15" s="24">
+        <f t="array" ref="K15">IF(L15&lt;&gt;"", SUMPRODUCT(MID(N15:Y15,5,1)*1), "")</f>
         <v>14</v>
       </c>
-      <c r="L15" s="24">
+      <c r="L15" s="28">
         <v>3.0</v>
       </c>
-      <c r="M15" s="23">
-        <f t="array" ref="M15">IF(L15&lt;&gt;"", SUMPRODUCT(LEFT(N15:X15,1)*1), "")</f>
+      <c r="M15" s="24">
+        <f t="array" ref="M15">IF(L15&lt;&gt;"", SUMPRODUCT(LEFT(N15:Y15,1)*1), "")</f>
         <v>9</v>
       </c>
-      <c r="N15" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="O15" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="P15" s="16" t="s">
+      <c r="N15" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="Q15" s="16" t="s">
+      <c r="O15" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="R15" s="16" t="s">
+      <c r="P15" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q15" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="R15" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="S15" s="16" t="s">
+      <c r="S15" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="T15" s="16" t="s">
+      <c r="T15" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="U15" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="V15" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="W15" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="X15" s="16" t="s">
+      <c r="U15" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="V15" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="W15" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="X15" s="17" t="s">
         <v>41</v>
       </c>
+      <c r="Y15" s="17" t="s">
+        <v>41</v>
+      </c>
       <c r="AD15" s="5"/>
     </row>
     <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="18">
+      <c r="A16" s="19">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <v>1.0</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="20">
+      <c r="C16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="21">
         <v>46284.0</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="22">
         <v>0.4375</v>
       </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="I16" s="19" t="s">
+      <c r="F16" s="20"/>
+      <c r="G16" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="J16" s="18" t="str">
+      <c r="J16" s="19" t="str">
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="K16" s="23">
-        <f t="array" ref="K16">IF(L16&lt;&gt;"", SUMPRODUCT(MID(N16:X16,5,1)*1), "")</f>
+      <c r="K16" s="24">
+        <f t="array" ref="K16">IF(L16&lt;&gt;"", SUMPRODUCT(MID(N16:Y16,5,1)*1), "")</f>
         <v>8</v>
       </c>
-      <c r="L16" s="25">
+      <c r="L16" s="29">
         <v>1.0</v>
       </c>
-      <c r="M16" s="23">
-        <f t="array" ref="M16">IF(L16&lt;&gt;"", SUMPRODUCT(LEFT(N16:X16,1)*1), "")</f>
+      <c r="M16" s="24">
+        <f t="array" ref="M16">IF(L16&lt;&gt;"", SUMPRODUCT(LEFT(N16:Y16,1)*1), "")</f>
         <v>10</v>
       </c>
-      <c r="N16" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="O16" s="16" t="s">
+      <c r="N16" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="P16" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q16" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="R16" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="S16" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="T16" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="U16" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="V16" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q16" s="16" t="s">
+      <c r="W16" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="X16" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y16" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="R16" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="S16" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="T16" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="U16" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="V16" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="W16" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="X16" s="16" t="s">
-        <v>65</v>
-      </c>
       <c r="AD16" s="5"/>
     </row>
     <row r="17">
-      <c r="A17" s="18">
+      <c r="A17" s="19">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="20">
         <v>1.0</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="21">
+        <v>46291.0</v>
+      </c>
+      <c r="E17" s="22">
+        <v>0.375</v>
+      </c>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="J17" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>W</v>
+      </c>
+      <c r="K17" s="24">
+        <f t="array" ref="K17">IF(L17&lt;&gt;"", SUMPRODUCT(MID(N17:Y17,5,1)*1), "")</f>
+        <v>15</v>
+      </c>
+      <c r="L17" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="M17" s="24">
+        <f t="array" ref="M17">IF(L17&lt;&gt;"", SUMPRODUCT(LEFT(N17:Y17,1)*1), "")</f>
+        <v>10</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="O17" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="P17" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q17" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="20">
-        <v>46291.0</v>
-      </c>
-      <c r="E17" s="21">
+      <c r="R17" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="S17" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="T17" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="U17" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="V17" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="W17" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="X17" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y17" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD17" s="5"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="19">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="B18" s="20">
+        <v>1.0</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="21">
+        <v>46298.0</v>
+      </c>
+      <c r="E18" s="22">
         <v>0.375</v>
       </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="J17" s="18" t="str">
+      <c r="F18" s="20"/>
+      <c r="G18" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="J18" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K17" s="23" t="str">
-        <f t="array" ref="K17">IF(L17&lt;&gt;"", SUMPRODUCT(MID(N17:X17,5,1)*1), "")</f>
+      <c r="K18" s="24" t="str">
+        <f t="array" ref="K18">IF(L18&lt;&gt;"", SUMPRODUCT(MID(N18:Y18,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L17" s="24"/>
-      <c r="M17" s="23" t="str">
-        <f t="array" ref="M17">IF(L17&lt;&gt;"", SUMPRODUCT(LEFT(N17:X17,1)*1), "")</f>
+      <c r="L18" s="28"/>
+      <c r="M18" s="24" t="str">
+        <f t="array" ref="M18">IF(L18&lt;&gt;"", SUMPRODUCT(LEFT(N18:Y18,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="16"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="AD17" s="5"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="18">
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="17"/>
+      <c r="V18" s="17"/>
+      <c r="W18" s="17"/>
+      <c r="X18" s="17"/>
+      <c r="Y18" s="17"/>
+      <c r="AD18" s="5"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="str">
         <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="B18" s="19">
-        <v>1.0</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="20">
-        <v>46298.0</v>
-      </c>
-      <c r="E18" s="21">
-        <v>0.375</v>
-      </c>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="J18" s="18" t="str">
+        <v/>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K18" s="23" t="str">
-        <f t="array" ref="K18">IF(L18&lt;&gt;"", SUMPRODUCT(MID(N18:X18,5,1)*1), "")</f>
+      <c r="K19" s="24" t="str">
+        <f t="array" ref="K19">IF(L19&lt;&gt;"", SUMPRODUCT(MID(N19:Y19,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L18" s="24"/>
-      <c r="M18" s="23" t="str">
-        <f t="array" ref="M18">IF(L18&lt;&gt;"", SUMPRODUCT(LEFT(N18:X18,1)*1), "")</f>
+      <c r="L19" s="28"/>
+      <c r="M19" s="24" t="str">
+        <f t="array" ref="M19">IF(L19&lt;&gt;"", SUMPRODUCT(LEFT(N19:Y19,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="16"/>
-      <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
-      <c r="X18" s="16"/>
-      <c r="AD18" s="5"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="str">
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="17"/>
+      <c r="V19" s="17"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="17"/>
+      <c r="Y19" s="17"/>
+      <c r="AD19" s="5"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="18" t="str">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K19" s="23" t="str">
-        <f t="array" ref="K19">IF(L19&lt;&gt;"", SUMPRODUCT(MID(N19:X19,5,1)*1), "")</f>
+      <c r="K20" s="24" t="str">
+        <f t="array" ref="K20">IF(L20&lt;&gt;"", SUMPRODUCT(MID(N20:Y20,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L19" s="24"/>
-      <c r="M19" s="23" t="str">
-        <f t="array" ref="M19">IF(L19&lt;&gt;"", SUMPRODUCT(LEFT(N19:X19,1)*1), "")</f>
+      <c r="L20" s="28"/>
+      <c r="M20" s="24" t="str">
+        <f t="array" ref="M20">IF(L20&lt;&gt;"", SUMPRODUCT(LEFT(N20:Y20,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="16"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="16"/>
-      <c r="AD19" s="5"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="str">
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="17"/>
+      <c r="Y20" s="17"/>
+      <c r="AD20" s="5"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="18" t="str">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K20" s="23" t="str">
-        <f t="array" ref="K20">IF(L20&lt;&gt;"", SUMPRODUCT(MID(N20:X20,5,1)*1), "")</f>
+      <c r="K21" s="24" t="str">
+        <f t="array" ref="K21">IF(L21&lt;&gt;"", SUMPRODUCT(MID(N21:Y21,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L20" s="24"/>
-      <c r="M20" s="23" t="str">
-        <f t="array" ref="M20">IF(L20&lt;&gt;"", SUMPRODUCT(LEFT(N20:X20,1)*1), "")</f>
+      <c r="L21" s="28"/>
+      <c r="M21" s="24" t="str">
+        <f t="array" ref="M21">IF(L21&lt;&gt;"", SUMPRODUCT(LEFT(N21:Y21,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="16"/>
-      <c r="T20" s="16"/>
-      <c r="U20" s="16"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-      <c r="X20" s="16"/>
-      <c r="AD20" s="5"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="str">
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17"/>
+      <c r="V21" s="17"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="17"/>
+      <c r="Y21" s="17"/>
+      <c r="AD21" s="5"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="18" t="str">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K21" s="23" t="str">
-        <f t="array" ref="K21">IF(L21&lt;&gt;"", SUMPRODUCT(MID(N21:X21,5,1)*1), "")</f>
+      <c r="K22" s="24" t="str">
+        <f t="array" ref="K22">IF(L22&lt;&gt;"", SUMPRODUCT(MID(N22:Y22,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L21" s="24"/>
-      <c r="M21" s="23" t="str">
-        <f t="array" ref="M21">IF(L21&lt;&gt;"", SUMPRODUCT(LEFT(N21:X21,1)*1), "")</f>
+      <c r="L22" s="28"/>
+      <c r="M22" s="24" t="str">
+        <f t="array" ref="M22">IF(L22&lt;&gt;"", SUMPRODUCT(LEFT(N22:Y22,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="16"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="16"/>
-      <c r="V21" s="16"/>
-      <c r="W21" s="16"/>
-      <c r="X21" s="16"/>
-      <c r="AD21" s="5"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="str">
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="17"/>
+      <c r="V22" s="17"/>
+      <c r="W22" s="17"/>
+      <c r="X22" s="17"/>
+      <c r="Y22" s="17"/>
+      <c r="AD22" s="5"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="18" t="str">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K22" s="23" t="str">
-        <f t="array" ref="K22">IF(L22&lt;&gt;"", SUMPRODUCT(MID(N22:X22,5,1)*1), "")</f>
+      <c r="K23" s="24" t="str">
+        <f t="array" ref="K23">IF(L23&lt;&gt;"", SUMPRODUCT(MID(N23:Y23,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L22" s="24"/>
-      <c r="M22" s="23" t="str">
-        <f t="array" ref="M22">IF(L22&lt;&gt;"", SUMPRODUCT(LEFT(N22:X22,1)*1), "")</f>
+      <c r="L23" s="28"/>
+      <c r="M23" s="24" t="str">
+        <f t="array" ref="M23">IF(L23&lt;&gt;"", SUMPRODUCT(LEFT(N23:Y23,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="16"/>
-      <c r="S22" s="16"/>
-      <c r="T22" s="16"/>
-      <c r="U22" s="16"/>
-      <c r="V22" s="16"/>
-      <c r="W22" s="16"/>
-      <c r="X22" s="16"/>
-      <c r="AD22" s="5"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="18" t="str">
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="17"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="17"/>
+      <c r="U23" s="17"/>
+      <c r="V23" s="17"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="17"/>
+      <c r="Y23" s="17"/>
+      <c r="AD23" s="5"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="18" t="str">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K23" s="23" t="str">
-        <f t="array" ref="K23">IF(L23&lt;&gt;"", SUMPRODUCT(MID(N23:X23,5,1)*1), "")</f>
+      <c r="K24" s="24" t="str">
+        <f t="array" ref="K24">IF(L24&lt;&gt;"", SUMPRODUCT(MID(N24:Y24,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L23" s="24"/>
-      <c r="M23" s="23" t="str">
-        <f t="array" ref="M23">IF(L23&lt;&gt;"", SUMPRODUCT(LEFT(N23:X23,1)*1), "")</f>
+      <c r="L24" s="28"/>
+      <c r="M24" s="24" t="str">
+        <f t="array" ref="M24">IF(L24&lt;&gt;"", SUMPRODUCT(LEFT(N24:Y24,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N23" s="16"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="16"/>
-      <c r="S23" s="16"/>
-      <c r="T23" s="16"/>
-      <c r="U23" s="16"/>
-      <c r="V23" s="16"/>
-      <c r="W23" s="16"/>
-      <c r="X23" s="16"/>
-      <c r="AD23" s="5"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="str">
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="17"/>
+      <c r="V24" s="17"/>
+      <c r="W24" s="17"/>
+      <c r="X24" s="17"/>
+      <c r="Y24" s="17"/>
+      <c r="AD24" s="5"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="18" t="str">
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K24" s="23" t="str">
-        <f t="array" ref="K24">IF(L24&lt;&gt;"", SUMPRODUCT(MID(N24:X24,5,1)*1), "")</f>
+      <c r="K25" s="24" t="str">
+        <f t="array" ref="K25">IF(L25&lt;&gt;"", SUMPRODUCT(MID(N25:Y25,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L24" s="24"/>
-      <c r="M24" s="23" t="str">
-        <f t="array" ref="M24">IF(L24&lt;&gt;"", SUMPRODUCT(LEFT(N24:X24,1)*1), "")</f>
+      <c r="L25" s="28"/>
+      <c r="M25" s="24" t="str">
+        <f t="array" ref="M25">IF(L25&lt;&gt;"", SUMPRODUCT(LEFT(N25:Y25,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="16"/>
-      <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
-      <c r="X24" s="16"/>
-      <c r="AD24" s="5"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="str">
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="17"/>
+      <c r="U25" s="17"/>
+      <c r="V25" s="17"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="17"/>
+      <c r="Y25" s="17"/>
+      <c r="AD25" s="5"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="18" t="str">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K25" s="23" t="str">
-        <f t="array" ref="K25">IF(L25&lt;&gt;"", SUMPRODUCT(MID(N25:X25,5,1)*1), "")</f>
+      <c r="K26" s="24" t="str">
+        <f t="array" ref="K26">IF(L26&lt;&gt;"", SUMPRODUCT(MID(N26:Y26,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L25" s="24"/>
-      <c r="M25" s="23" t="str">
-        <f t="array" ref="M25">IF(L25&lt;&gt;"", SUMPRODUCT(LEFT(N25:X25,1)*1), "")</f>
+      <c r="L26" s="28"/>
+      <c r="M26" s="24" t="str">
+        <f t="array" ref="M26">IF(L26&lt;&gt;"", SUMPRODUCT(LEFT(N26:Y26,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N25" s="16"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="16"/>
-      <c r="S25" s="16"/>
-      <c r="T25" s="16"/>
-      <c r="U25" s="16"/>
-      <c r="V25" s="16"/>
-      <c r="W25" s="16"/>
-      <c r="X25" s="16"/>
-      <c r="AD25" s="5"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="str">
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="17"/>
+      <c r="U26" s="17"/>
+      <c r="V26" s="17"/>
+      <c r="W26" s="17"/>
+      <c r="X26" s="17"/>
+      <c r="Y26" s="17"/>
+      <c r="AD26" s="5"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="18" t="str">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K26" s="23" t="str">
-        <f t="array" ref="K26">IF(L26&lt;&gt;"", SUMPRODUCT(MID(N26:X26,5,1)*1), "")</f>
+      <c r="K27" s="24" t="str">
+        <f t="array" ref="K27">IF(L27&lt;&gt;"", SUMPRODUCT(MID(N27:Y27,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L26" s="24"/>
-      <c r="M26" s="23" t="str">
-        <f t="array" ref="M26">IF(L26&lt;&gt;"", SUMPRODUCT(LEFT(N26:X26,1)*1), "")</f>
+      <c r="L27" s="20"/>
+      <c r="M27" s="24" t="str">
+        <f t="array" ref="M27">IF(L27&lt;&gt;"", SUMPRODUCT(LEFT(N27:Y27,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="16"/>
-      <c r="S26" s="16"/>
-      <c r="T26" s="16"/>
-      <c r="U26" s="16"/>
-      <c r="V26" s="16"/>
-      <c r="W26" s="16"/>
-      <c r="X26" s="16"/>
-      <c r="AD26" s="5"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="str">
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="17"/>
+      <c r="U27" s="17"/>
+      <c r="V27" s="17"/>
+      <c r="W27" s="17"/>
+      <c r="X27" s="17"/>
+      <c r="Y27" s="17"/>
+      <c r="AD27" s="5"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="18" t="str">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K27" s="23" t="str">
-        <f t="array" ref="K27">IF(L27&lt;&gt;"", SUMPRODUCT(MID(N27:X27,5,1)*1), "")</f>
+      <c r="K28" s="24" t="str">
+        <f t="array" ref="K28">IF(L28&lt;&gt;"", SUMPRODUCT(MID(N28:Y28,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L27" s="19"/>
-      <c r="M27" s="23" t="str">
-        <f t="array" ref="M27">IF(L27&lt;&gt;"", SUMPRODUCT(LEFT(N27:X27,1)*1), "")</f>
+      <c r="L28" s="20"/>
+      <c r="M28" s="24" t="str">
+        <f t="array" ref="M28">IF(L28&lt;&gt;"", SUMPRODUCT(LEFT(N28:Y28,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="16"/>
-      <c r="S27" s="16"/>
-      <c r="T27" s="16"/>
-      <c r="U27" s="16"/>
-      <c r="V27" s="16"/>
-      <c r="W27" s="16"/>
-      <c r="X27" s="16"/>
-      <c r="AD27" s="5"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="str">
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="17"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
+      <c r="AD28" s="5"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="18" t="str">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K28" s="23" t="str">
-        <f t="array" ref="K28">IF(L28&lt;&gt;"", SUMPRODUCT(MID(N28:X28,5,1)*1), "")</f>
+      <c r="K29" s="24" t="str">
+        <f t="array" ref="K29">IF(L29&lt;&gt;"", SUMPRODUCT(MID(N29:Y29,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L28" s="19"/>
-      <c r="M28" s="23" t="str">
-        <f t="array" ref="M28">IF(L28&lt;&gt;"", SUMPRODUCT(LEFT(N28:X28,1)*1), "")</f>
+      <c r="L29" s="20"/>
+      <c r="M29" s="24" t="str">
+        <f t="array" ref="M29">IF(L29&lt;&gt;"", SUMPRODUCT(LEFT(N29:Y29,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
-      <c r="S28" s="16"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="16"/>
-      <c r="AD28" s="5"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="18" t="str">
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="17"/>
+      <c r="V29" s="17"/>
+      <c r="W29" s="17"/>
+      <c r="X29" s="17"/>
+      <c r="Y29" s="17"/>
+      <c r="AD29" s="5"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="18" t="str">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K29" s="23" t="str">
-        <f t="array" ref="K29">IF(L29&lt;&gt;"", SUMPRODUCT(MID(N29:X29,5,1)*1), "")</f>
+      <c r="K30" s="24" t="str">
+        <f t="array" ref="K30">IF(L30&lt;&gt;"", SUMPRODUCT(MID(N30:Y30,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L29" s="19"/>
-      <c r="M29" s="23" t="str">
-        <f t="array" ref="M29">IF(L29&lt;&gt;"", SUMPRODUCT(LEFT(N29:X29,1)*1), "")</f>
+      <c r="L30" s="20"/>
+      <c r="M30" s="24" t="str">
+        <f t="array" ref="M30">IF(L30&lt;&gt;"", SUMPRODUCT(LEFT(N30:Y30,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N29" s="16"/>
-      <c r="O29" s="16"/>
-      <c r="P29" s="16"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="16"/>
-      <c r="S29" s="16"/>
-      <c r="T29" s="16"/>
-      <c r="U29" s="16"/>
-      <c r="V29" s="16"/>
-      <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
-      <c r="AD29" s="5"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="str">
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="17"/>
+      <c r="U30" s="17"/>
+      <c r="V30" s="17"/>
+      <c r="W30" s="17"/>
+      <c r="X30" s="17"/>
+      <c r="Y30" s="17"/>
+      <c r="AD30" s="5"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="18" t="str">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K30" s="23" t="str">
-        <f t="array" ref="K30">IF(L30&lt;&gt;"", SUMPRODUCT(MID(N30:X30,5,1)*1), "")</f>
+      <c r="K31" s="24" t="str">
+        <f t="array" ref="K31">IF(L31&lt;&gt;"", SUMPRODUCT(MID(N31:Y31,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L30" s="19"/>
-      <c r="M30" s="23" t="str">
-        <f t="array" ref="M30">IF(L30&lt;&gt;"", SUMPRODUCT(LEFT(N30:X30,1)*1), "")</f>
+      <c r="L31" s="20"/>
+      <c r="M31" s="24" t="str">
+        <f t="array" ref="M31">IF(L31&lt;&gt;"", SUMPRODUCT(LEFT(N31:Y31,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16"/>
-      <c r="P30" s="16"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="16"/>
-      <c r="S30" s="16"/>
-      <c r="T30" s="16"/>
-      <c r="U30" s="16"/>
-      <c r="V30" s="16"/>
-      <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
-      <c r="AD30" s="5"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="str">
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="17"/>
+      <c r="T31" s="17"/>
+      <c r="U31" s="17"/>
+      <c r="V31" s="17"/>
+      <c r="W31" s="17"/>
+      <c r="X31" s="17"/>
+      <c r="Y31" s="17"/>
+      <c r="AD31" s="5"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="18" t="str">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K31" s="23" t="str">
-        <f t="array" ref="K31">IF(L31&lt;&gt;"", SUMPRODUCT(MID(N31:X31,5,1)*1), "")</f>
+      <c r="K32" s="24" t="str">
+        <f t="array" ref="K32">IF(L32&lt;&gt;"", SUMPRODUCT(MID(N32:Y32,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L31" s="19"/>
-      <c r="M31" s="23" t="str">
-        <f t="array" ref="M31">IF(L31&lt;&gt;"", SUMPRODUCT(LEFT(N31:X31,1)*1), "")</f>
+      <c r="L32" s="20"/>
+      <c r="M32" s="24" t="str">
+        <f t="array" ref="M32">IF(L32&lt;&gt;"", SUMPRODUCT(LEFT(N32:Y32,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N31" s="16"/>
-      <c r="O31" s="16"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="16"/>
-      <c r="S31" s="16"/>
-      <c r="T31" s="16"/>
-      <c r="U31" s="16"/>
-      <c r="V31" s="16"/>
-      <c r="W31" s="16"/>
-      <c r="X31" s="16"/>
-      <c r="AD31" s="5"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="str">
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="17"/>
+      <c r="U32" s="17"/>
+      <c r="V32" s="17"/>
+      <c r="W32" s="17"/>
+      <c r="X32" s="17"/>
+      <c r="Y32" s="17"/>
+      <c r="AD32" s="5"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="18" t="str">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K32" s="23" t="str">
-        <f t="array" ref="K32">IF(L32&lt;&gt;"", SUMPRODUCT(MID(N32:X32,5,1)*1), "")</f>
+      <c r="K33" s="24" t="str">
+        <f t="array" ref="K33">IF(L33&lt;&gt;"", SUMPRODUCT(MID(N33:Y33,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L32" s="19"/>
-      <c r="M32" s="23" t="str">
-        <f t="array" ref="M32">IF(L32&lt;&gt;"", SUMPRODUCT(LEFT(N32:X32,1)*1), "")</f>
+      <c r="L33" s="20"/>
+      <c r="M33" s="24" t="str">
+        <f t="array" ref="M33">IF(L33&lt;&gt;"", SUMPRODUCT(LEFT(N33:Y33,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="16"/>
-      <c r="R32" s="16"/>
-      <c r="S32" s="16"/>
-      <c r="T32" s="16"/>
-      <c r="U32" s="16"/>
-      <c r="V32" s="16"/>
-      <c r="W32" s="16"/>
-      <c r="X32" s="16"/>
-      <c r="AD32" s="5"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="str">
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="17"/>
+      <c r="V33" s="17"/>
+      <c r="W33" s="17"/>
+      <c r="X33" s="17"/>
+      <c r="Y33" s="17"/>
+      <c r="AD33" s="5"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="18" t="str">
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K33" s="23" t="str">
-        <f t="array" ref="K33">IF(L33&lt;&gt;"", SUMPRODUCT(MID(N33:X33,5,1)*1), "")</f>
+      <c r="K34" s="24" t="str">
+        <f t="array" ref="K34">IF(L34&lt;&gt;"", SUMPRODUCT(MID(N34:Y34,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L33" s="19"/>
-      <c r="M33" s="23" t="str">
-        <f t="array" ref="M33">IF(L33&lt;&gt;"", SUMPRODUCT(LEFT(N33:X33,1)*1), "")</f>
+      <c r="L34" s="20"/>
+      <c r="M34" s="24" t="str">
+        <f t="array" ref="M34">IF(L34&lt;&gt;"", SUMPRODUCT(LEFT(N34:Y34,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N33" s="16"/>
-      <c r="O33" s="16"/>
-      <c r="P33" s="16"/>
-      <c r="Q33" s="16"/>
-      <c r="R33" s="16"/>
-      <c r="S33" s="16"/>
-      <c r="T33" s="16"/>
-      <c r="U33" s="16"/>
-      <c r="V33" s="16"/>
-      <c r="W33" s="16"/>
-      <c r="X33" s="16"/>
-      <c r="AD33" s="5"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="18" t="str">
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="17"/>
+      <c r="V34" s="17"/>
+      <c r="W34" s="17"/>
+      <c r="X34" s="17"/>
+      <c r="Y34" s="17"/>
+      <c r="AD34" s="5"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="18" t="str">
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K34" s="23" t="str">
-        <f t="array" ref="K34">IF(L34&lt;&gt;"", SUMPRODUCT(MID(N34:X34,5,1)*1), "")</f>
+      <c r="K35" s="24" t="str">
+        <f t="array" ref="K35">IF(L35&lt;&gt;"", SUMPRODUCT(MID(N35:Y35,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L34" s="19"/>
-      <c r="M34" s="23" t="str">
-        <f t="array" ref="M34">IF(L34&lt;&gt;"", SUMPRODUCT(LEFT(N34:W34,1)*1), "")</f>
+      <c r="L35" s="20"/>
+      <c r="M35" s="24" t="str">
+        <f t="array" ref="M35">IF(L35&lt;&gt;"", SUMPRODUCT(LEFT(N35:Y35,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N34" s="16"/>
-      <c r="O34" s="16"/>
-      <c r="P34" s="16"/>
-      <c r="Q34" s="16"/>
-      <c r="R34" s="16"/>
-      <c r="S34" s="16"/>
-      <c r="T34" s="16"/>
-      <c r="U34" s="16"/>
-      <c r="V34" s="16"/>
-      <c r="W34" s="16"/>
-      <c r="X34" s="16"/>
-      <c r="AD34" s="5"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="18" t="str">
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="17"/>
+      <c r="V35" s="17"/>
+      <c r="W35" s="17"/>
+      <c r="X35" s="17"/>
+      <c r="Y35" s="17"/>
+      <c r="AD35" s="5"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="18" t="str">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K35" s="23" t="str">
-        <f t="array" ref="K35">IF(L35&lt;&gt;"", SUMPRODUCT(MID(N35:W35,5,1)*1), "")</f>
+      <c r="K36" s="24" t="str">
+        <f t="array" ref="K36">IF(L36&lt;&gt;"", SUMPRODUCT(MID(N36:Y36,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L35" s="19"/>
-      <c r="M35" s="23" t="str">
-        <f t="array" ref="M35">IF(L35&lt;&gt;"", SUMPRODUCT(LEFT(N35:W35,1)*1), "")</f>
+      <c r="L36" s="28"/>
+      <c r="M36" s="24" t="str">
+        <f t="array" ref="M36">IF(L36&lt;&gt;"", SUMPRODUCT(LEFT(N36:Y36,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N35" s="16"/>
-      <c r="O35" s="16"/>
-      <c r="P35" s="16"/>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="16"/>
-      <c r="S35" s="16"/>
-      <c r="T35" s="16"/>
-      <c r="U35" s="16"/>
-      <c r="V35" s="16"/>
-      <c r="W35" s="16"/>
-      <c r="X35" s="16"/>
-      <c r="AD35" s="5"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="18" t="str">
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="17"/>
+      <c r="V36" s="17"/>
+      <c r="W36" s="17"/>
+      <c r="X36" s="17"/>
+      <c r="Y36" s="17"/>
+      <c r="AD36" s="5"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="18" t="str">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="23" t="str">
-        <f t="array" ref="K36">IF(L36&lt;&gt;"", SUMPRODUCT(MID(N36:W36,5,1)*1), "")</f>
+      <c r="K37" s="24" t="str">
+        <f t="array" ref="K37">IF(L37&lt;&gt;"", SUMPRODUCT(MID(N37:Y37,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L36" s="24"/>
-      <c r="M36" s="23" t="str">
-        <f t="array" ref="M36">IF(L36&lt;&gt;"", SUMPRODUCT(LEFT(N36:W36,1)*1), "")</f>
+      <c r="L37" s="20"/>
+      <c r="M37" s="24" t="str">
+        <f t="array" ref="M37">IF(L37&lt;&gt;"", SUMPRODUCT(LEFT(N37:Y37,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N36" s="16"/>
-      <c r="O36" s="16"/>
-      <c r="P36" s="16"/>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="16"/>
-      <c r="S36" s="16"/>
-      <c r="T36" s="16"/>
-      <c r="U36" s="16"/>
-      <c r="V36" s="16"/>
-      <c r="W36" s="16"/>
-      <c r="X36" s="16"/>
-      <c r="AD36" s="5"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="18" t="str">
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="17"/>
+      <c r="V37" s="17"/>
+      <c r="W37" s="17"/>
+      <c r="X37" s="17"/>
+      <c r="Y37" s="17"/>
+      <c r="AD37" s="5"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="18" t="str">
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K37" s="23" t="str">
-        <f t="array" ref="K37">IF(L37&lt;&gt;"", SUMPRODUCT(MID(N37:W37,5,1)*1), "")</f>
+      <c r="K38" s="24" t="str">
+        <f t="array" ref="K38">IF(L38&lt;&gt;"", SUMPRODUCT(MID(N38:Y38,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L37" s="19"/>
-      <c r="M37" s="23" t="str">
-        <f t="array" ref="M37">IF(L37&lt;&gt;"", SUMPRODUCT(LEFT(N37:W37,1)*1), "")</f>
+      <c r="L38" s="20"/>
+      <c r="M38" s="24" t="str">
+        <f t="array" ref="M38">IF(L38&lt;&gt;"", SUMPRODUCT(LEFT(N38:Y38,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N37" s="16"/>
-      <c r="O37" s="16"/>
-      <c r="P37" s="16"/>
-      <c r="Q37" s="16"/>
-      <c r="R37" s="16"/>
-      <c r="S37" s="16"/>
-      <c r="T37" s="16"/>
-      <c r="U37" s="16"/>
-      <c r="V37" s="16"/>
-      <c r="W37" s="16"/>
-      <c r="X37" s="16"/>
-      <c r="AD37" s="5"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="18" t="str">
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="17"/>
+      <c r="V38" s="17"/>
+      <c r="W38" s="17"/>
+      <c r="X38" s="17"/>
+      <c r="Y38" s="17"/>
+      <c r="AD38" s="5"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="18" t="str">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K38" s="23" t="str">
-        <f t="array" ref="K38">IF(L38&lt;&gt;"", SUMPRODUCT(MID(N38:W38,5,1)*1), "")</f>
+      <c r="K39" s="24" t="str">
+        <f t="array" ref="K39">IF(L39&lt;&gt;"", SUMPRODUCT(MID(N39:Y39,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L38" s="19"/>
-      <c r="M38" s="23" t="str">
-        <f t="array" ref="M38">IF(L38&lt;&gt;"", SUMPRODUCT(LEFT(N38:W38,1)*1), "")</f>
+      <c r="L39" s="20"/>
+      <c r="M39" s="24" t="str">
+        <f t="array" ref="M39">IF(L39&lt;&gt;"", SUMPRODUCT(LEFT(N39:Y39,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="16"/>
-      <c r="Q38" s="16"/>
-      <c r="R38" s="16"/>
-      <c r="S38" s="16"/>
-      <c r="T38" s="16"/>
-      <c r="U38" s="16"/>
-      <c r="V38" s="16"/>
-      <c r="W38" s="16"/>
-      <c r="X38" s="16"/>
-      <c r="AD38" s="5"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="18" t="str">
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="17"/>
+      <c r="S39" s="17"/>
+      <c r="T39" s="17"/>
+      <c r="U39" s="17"/>
+      <c r="V39" s="17"/>
+      <c r="W39" s="17"/>
+      <c r="X39" s="17"/>
+      <c r="Y39" s="17"/>
+      <c r="AD39" s="5"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="18" t="str">
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K39" s="23" t="str">
-        <f t="array" ref="K39">IF(L39&lt;&gt;"", SUMPRODUCT(MID(N39:W39,5,1)*1), "")</f>
+      <c r="K40" s="24" t="str">
+        <f t="array" ref="K40">IF(L40&lt;&gt;"", SUMPRODUCT(MID(N40:Y40,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L39" s="19"/>
-      <c r="M39" s="23" t="str">
-        <f t="array" ref="M39">IF(L39&lt;&gt;"", SUMPRODUCT(LEFT(N39:W39,1)*1), "")</f>
+      <c r="L40" s="20"/>
+      <c r="M40" s="24" t="str">
+        <f t="array" ref="M40">IF(L40&lt;&gt;"", SUMPRODUCT(LEFT(N40:Y40,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="16"/>
-      <c r="R39" s="16"/>
-      <c r="S39" s="16"/>
-      <c r="T39" s="16"/>
-      <c r="U39" s="16"/>
-      <c r="V39" s="16"/>
-      <c r="W39" s="16"/>
-      <c r="X39" s="16"/>
-      <c r="AD39" s="5"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="23" t="str">
-        <f t="array" ref="K40">IF(L40&lt;&gt;"", SUMPRODUCT(MID(N40:W40,5,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="L40" s="19"/>
-      <c r="M40" s="23" t="str">
-        <f t="array" ref="M40">IF(L40&lt;&gt;"", SUMPRODUCT(LEFT(N40:W40,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="N40" s="16"/>
-      <c r="O40" s="16"/>
-      <c r="P40" s="16"/>
-      <c r="Q40" s="16"/>
-      <c r="R40" s="16"/>
-      <c r="S40" s="16"/>
-      <c r="T40" s="16"/>
-      <c r="U40" s="16"/>
-      <c r="V40" s="16"/>
-      <c r="W40" s="16"/>
-      <c r="X40" s="16"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="17"/>
+      <c r="S40" s="17"/>
+      <c r="T40" s="17"/>
+      <c r="U40" s="17"/>
+      <c r="V40" s="17"/>
+      <c r="W40" s="17"/>
+      <c r="X40" s="17"/>
+      <c r="Y40" s="17"/>
       <c r="AD40" s="5"/>
     </row>
     <row r="41">
@@ -2715,31 +2795,31 @@
         <v>4</v>
       </c>
       <c r="F44" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="H44" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="I44" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I44" s="4" t="s">
+      <c r="J44" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J44" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K44" s="16" t="s">
+      <c r="K44" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="L44" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="L44" s="30" t="s">
+      <c r="M44" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="M44" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="N44" s="16" t="s">
-        <v>74</v>
+      <c r="N44" s="17" t="s">
+        <v>77</v>
       </c>
       <c r="O44" s="5"/>
       <c r="T44" s="5"/>
@@ -2756,44 +2836,46 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B45" s="5">
+        <v>78</v>
+      </c>
+      <c r="B45" s="32">
         <v>1.0</v>
       </c>
-      <c r="C45" s="5">
+      <c r="C45" s="32">
         <v>1.0</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="32">
         <v>1.0</v>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="F45" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="G45" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="H45" s="32">
         <v>0.0</v>
       </c>
-      <c r="F45" s="5">
+      <c r="I45" s="32">
         <v>1.0</v>
       </c>
-      <c r="G45" s="5">
+      <c r="J45" s="32">
         <v>1.0</v>
       </c>
-      <c r="H45" s="31">
+      <c r="K45" s="32">
         <v>1.0</v>
       </c>
-      <c r="I45" s="5">
+      <c r="L45" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="M45" s="32">
         <v>1.0</v>
       </c>
-      <c r="J45" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="K45" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="L45" s="31">
-        <v>1.0</v>
-      </c>
-      <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-      <c r="O45" s="32">
+      <c r="O45" s="33">
         <f t="shared" ref="O45:O48" si="3">SUM(A45:N45)</f>
         <v>10</v>
       </c>
@@ -2811,46 +2893,48 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B46" s="5">
+        <v>45</v>
+      </c>
+      <c r="B46" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="C46" s="32">
         <v>1.0</v>
       </c>
-      <c r="C46" s="5">
+      <c r="D46" s="32">
         <v>1.0</v>
       </c>
-      <c r="D46" s="31">
+      <c r="E46" s="32">
         <v>1.0</v>
       </c>
-      <c r="E46" s="31">
+      <c r="F46" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="G46" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="H46" s="32">
         <v>0.0</v>
       </c>
-      <c r="F46" s="5">
+      <c r="I46" s="32">
         <v>1.0</v>
       </c>
-      <c r="G46" s="5">
+      <c r="J46" s="32">
         <v>1.0</v>
       </c>
-      <c r="H46" s="31">
-        <v>1.0</v>
-      </c>
-      <c r="I46" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="J46" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="K46" s="31">
+      <c r="K46" s="32">
         <v>0.0</v>
       </c>
-      <c r="L46" s="31">
+      <c r="L46" s="32">
         <v>0.0</v>
       </c>
-      <c r="M46" s="5"/>
+      <c r="M46" s="32">
+        <v>0.0</v>
+      </c>
       <c r="N46" s="5"/>
-      <c r="O46" s="32">
+      <c r="O46" s="33">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T46" s="5"/>
       <c r="U46" s="5"/>
@@ -2866,46 +2950,48 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B47" s="5">
+        <v>79</v>
+      </c>
+      <c r="B47" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="C47" s="32">
+        <v>3.0</v>
+      </c>
+      <c r="D47" s="32">
+        <v>2.0</v>
+      </c>
+      <c r="E47" s="32">
         <v>0.0</v>
       </c>
-      <c r="C47" s="31">
+      <c r="F47" s="32">
+        <v>3.0</v>
+      </c>
+      <c r="G47" s="32">
         <v>2.0</v>
       </c>
-      <c r="D47" s="31">
+      <c r="H47" s="32">
         <v>0.0</v>
       </c>
-      <c r="E47" s="31">
+      <c r="I47" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="J47" s="32">
+        <v>2.0</v>
+      </c>
+      <c r="K47" s="32">
         <v>0.0</v>
       </c>
-      <c r="F47" s="31">
-        <v>3.0</v>
-      </c>
-      <c r="G47" s="5">
+      <c r="L47" s="32">
         <v>0.0</v>
       </c>
-      <c r="H47" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I47" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="J47" s="31">
+      <c r="M47" s="32">
         <v>1.0</v>
       </c>
-      <c r="K47" s="31">
-        <v>1.0</v>
-      </c>
-      <c r="L47" s="31">
-        <v>1.0</v>
-      </c>
-      <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-      <c r="O47" s="32">
+      <c r="O47" s="33">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T47" s="5"/>
       <c r="U47" s="5"/>
@@ -2921,46 +3007,48 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B48" s="31">
+        <v>80</v>
+      </c>
+      <c r="B48" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="C48" s="32">
         <v>1.0</v>
       </c>
-      <c r="C48" s="31">
+      <c r="D48" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="E48" s="32">
         <v>1.0</v>
       </c>
-      <c r="D48" s="5">
+      <c r="F48" s="32">
+        <v>2.0</v>
+      </c>
+      <c r="G48" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="H48" s="32">
         <v>0.0</v>
       </c>
-      <c r="E48" s="31">
+      <c r="I48" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="J48" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="K48" s="32">
+        <v>2.0</v>
+      </c>
+      <c r="L48" s="32">
         <v>0.0</v>
       </c>
-      <c r="F48" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="G48" s="31">
+      <c r="M48" s="32">
         <v>1.0</v>
       </c>
-      <c r="H48" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="I48" s="31">
-        <v>1.0</v>
-      </c>
-      <c r="J48" s="31">
-        <v>1.0</v>
-      </c>
-      <c r="K48" s="31">
-        <v>1.0</v>
-      </c>
-      <c r="L48" s="31">
-        <v>2.0</v>
-      </c>
-      <c r="M48" s="5"/>
       <c r="N48" s="5"/>
-      <c r="O48" s="32">
+      <c r="O48" s="33">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T48" s="5"/>
       <c r="U48" s="5"/>
@@ -2978,51 +3066,51 @@
       <c r="A49" s="5"/>
       <c r="B49" s="5" t="str">
         <f t="shared" ref="B49:N49" si="4">B45&amp;","&amp;B46&amp;","&amp;B47&amp;","&amp;B48</f>
-        <v>1,1,0,1</v>
+        <v>1,0,1,0</v>
       </c>
       <c r="C49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,1,2,1</v>
+        <v>1,1,3,1</v>
       </c>
       <c r="D49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,1,0,0</v>
+        <v>1,1,2,0</v>
       </c>
       <c r="E49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>0,0,0,0</v>
+        <v>1,1,0,1</v>
       </c>
       <c r="F49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,1,3,0</v>
+        <v>1,1,3,2</v>
       </c>
       <c r="G49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,1,0,1</v>
+        <v>1,1,2,1</v>
       </c>
       <c r="H49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,1,0,0</v>
+        <v>0,0,0,0</v>
       </c>
       <c r="I49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,1,0,1</v>
+        <v>1,1,1,1</v>
       </c>
       <c r="J49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,1,1,1</v>
+        <v>1,1,2,1</v>
       </c>
       <c r="K49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,0,1,1</v>
+        <v>1,0,0,2</v>
       </c>
       <c r="L49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,0,1,2</v>
+        <v>0,0,0,0</v>
       </c>
       <c r="M49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>,,,</v>
+        <v>1,0,1,1</v>
       </c>
       <c r="N49" s="5" t="str">
         <f t="shared" si="4"/>
@@ -33111,7 +33199,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1"/>
+      <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="4" t="s">
         <v>1</v>
@@ -33140,9 +33228,7 @@
       <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="L1" s="5"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
@@ -33152,55 +33238,51 @@
       <c r="S1" s="5"/>
       <c r="T1" s="5"/>
       <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="17">
+      <c r="C2" s="11">
         <f t="array" ref="C2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <f t="array" ref="D2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z42, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
+        <v>7</v>
+      </c>
+      <c r="E2" s="11">
+        <f t="array" ref="E2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
+        <v>7</v>
+      </c>
+      <c r="F2" s="11">
+        <f t="array" ref="F2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>6</v>
       </c>
-      <c r="D2" s="17">
-        <f t="array" ref="D2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z42, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>6</v>
-      </c>
-      <c r="E2" s="17">
-        <f t="array" ref="E2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>6</v>
-      </c>
-      <c r="F2" s="17">
-        <f t="array" ref="F2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
+      <c r="G2" s="11">
+        <f t="array" ref="G2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
+        <v>7</v>
+      </c>
+      <c r="H2" s="11">
+        <f t="array" ref="H2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
+        <v>7</v>
+      </c>
+      <c r="I2" s="11">
+        <f t="array" ref="I2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>5</v>
       </c>
-      <c r="G2" s="17" t="str">
-        <f t="array" ref="G2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H2" s="17">
-        <f t="array" ref="H2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>6</v>
-      </c>
-      <c r="I2" s="17">
-        <f t="array" ref="I2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>6</v>
-      </c>
-      <c r="J2" s="17">
+      <c r="J2" s="11">
         <f t="array" ref="J2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="K2" s="17">
+        <v>7</v>
+      </c>
+      <c r="K2" s="11">
         <f t="array" ref="K2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>6</v>
-      </c>
-      <c r="L2" s="17">
-        <f t="array" ref="L2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(L$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
@@ -33210,53 +33292,49 @@
       <c r="S2" s="5"/>
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="26"/>
+      <c r="A3" s="25"/>
       <c r="B3" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="27">
+        <v>43</v>
+      </c>
+      <c r="C3" s="26">
         <f>C2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="26">
         <f>D2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="26">
         <f>E2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="26">
         <f>F2/MatchesDB!$B$1</f>
-        <v>0.8333333333</v>
-      </c>
-      <c r="G3" s="27" t="str">
+        <v>0.8571428571</v>
+      </c>
+      <c r="G3" s="26">
         <f>G2/MatchesDB!$B$1</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H3" s="27">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26">
         <f>H2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="I3" s="27">
-        <f>I2/MatchesDB!$B$1</f>
+      <c r="I3" s="26">
+        <f>I2/(MatchesDB!$B$1-4)</f>
+        <v>1.666666667</v>
+      </c>
+      <c r="J3" s="26">
+        <f>J2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="J3" s="27">
-        <f>J2/(MatchesDB!$B$1-4)</f>
-        <v>2.5</v>
-      </c>
-      <c r="K3" s="27">
+      <c r="K3" s="26">
         <f>K2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="L3" s="27">
-        <f>L2/MatchesDB!$B$1</f>
-        <v>1</v>
-      </c>
+      <c r="L3" s="5"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
@@ -33266,55 +33344,51 @@
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="s">
-        <v>69</v>
+      <c r="A4" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="28">
+        <v>11</v>
+      </c>
+      <c r="C4" s="27">
         <f t="array" ref="C4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>5</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="27">
         <f t="array" ref="D4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
+        <v>7</v>
+      </c>
+      <c r="E4" s="27">
+        <f t="array" ref="E4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
+        <v>4</v>
+      </c>
+      <c r="F4" s="27">
+        <f t="array" ref="F4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
+        <v>5</v>
+      </c>
+      <c r="G4" s="27">
+        <f t="array" ref="G4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>6</v>
       </c>
-      <c r="E4" s="28">
-        <f t="array" ref="E4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>3</v>
-      </c>
-      <c r="F4" s="28">
-        <f t="array" ref="F4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28" t="str">
-        <f t="array" ref="G4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H4" s="28">
+      <c r="H4" s="27">
         <f t="array" ref="H4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
+        <v>7</v>
+      </c>
+      <c r="I4" s="27">
+        <f t="array" ref="I4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>5</v>
       </c>
-      <c r="I4" s="28">
-        <f t="array" ref="I4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
+      <c r="J4" s="27">
+        <f t="array" ref="J4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>6</v>
       </c>
-      <c r="J4" s="28">
-        <f t="array" ref="J4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="K4" s="28">
+      <c r="K4" s="27">
         <f t="array" ref="K4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="L4" s="28">
-        <f t="array" ref="L4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(L$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
@@ -33324,53 +33398,49 @@
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
     </row>
     <row r="5">
-      <c r="A5" s="26"/>
+      <c r="A5" s="25"/>
       <c r="B5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="27">
-        <f t="shared" ref="C5:L5" si="1">C4/C2</f>
-        <v>0.8333333333</v>
-      </c>
-      <c r="D5" s="27">
+        <v>43</v>
+      </c>
+      <c r="C5" s="26">
+        <f t="shared" ref="C5:K5" si="1">C4/C2</f>
+        <v>0.7142857143</v>
+      </c>
+      <c r="D5" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="26">
         <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="F5" s="27">
-        <f t="shared" si="1"/>
-        <v>0.8</v>
-      </c>
-      <c r="G5" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="H5" s="27">
+        <v>0.5714285714</v>
+      </c>
+      <c r="F5" s="26">
         <f t="shared" si="1"/>
         <v>0.8333333333</v>
       </c>
-      <c r="I5" s="27">
+      <c r="G5" s="26">
+        <f t="shared" si="1"/>
+        <v>0.8571428571</v>
+      </c>
+      <c r="H5" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J5" s="27">
+      <c r="I5" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K5" s="27">
+      <c r="J5" s="26">
         <f t="shared" si="1"/>
-        <v>0.8333333333</v>
-      </c>
-      <c r="L5" s="27">
+        <v>0.8571428571</v>
+      </c>
+      <c r="K5" s="26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
+      <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
@@ -33380,55 +33450,51 @@
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="s">
-        <v>70</v>
+      <c r="A6" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="17">
+        <v>11</v>
+      </c>
+      <c r="C6" s="11">
         <f t="array" ref="C6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="17">
+        <v>1</v>
+      </c>
+      <c r="D6" s="11">
         <f t="array" ref="D6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>7</v>
-      </c>
-      <c r="E6" s="17">
+        <v>10</v>
+      </c>
+      <c r="E6" s="11">
         <f t="array" ref="E6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>2</v>
-      </c>
-      <c r="F6" s="17">
+        <v>4</v>
+      </c>
+      <c r="F6" s="11">
         <f t="array" ref="F6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>1</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="11">
         <f t="array" ref="G6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
+        <v>17</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="array" ref="H6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
+        <v>3</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="array" ref="I6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>0</v>
       </c>
-      <c r="H6" s="17">
-        <f t="array" ref="H6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>14</v>
-      </c>
-      <c r="I6" s="17">
-        <f t="array" ref="I6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>1</v>
-      </c>
-      <c r="J6" s="17">
+      <c r="J6" s="11">
         <f t="array" ref="J6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="17">
+        <v>5</v>
+      </c>
+      <c r="K6" s="11">
         <f t="array" ref="K6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>4</v>
-      </c>
-      <c r="L6" s="17">
-        <f t="array" ref="L6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(L$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>3</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
@@ -33438,53 +33504,49 @@
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
     </row>
     <row r="7">
-      <c r="A7" s="26"/>
+      <c r="A7" s="25"/>
       <c r="B7" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="29">
-        <f t="shared" ref="C7:L7" si="2">C6/C2</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="29">
+        <v>74</v>
+      </c>
+      <c r="C7" s="30">
+        <f t="shared" ref="C7:K7" si="2">C6/C2</f>
+        <v>0.1428571429</v>
+      </c>
+      <c r="D7" s="30">
         <f t="shared" si="2"/>
-        <v>1.166666667</v>
-      </c>
-      <c r="E7" s="29">
+        <v>1.428571429</v>
+      </c>
+      <c r="E7" s="30">
         <f t="shared" si="2"/>
-        <v>0.3333333333</v>
-      </c>
-      <c r="F7" s="29">
-        <f t="shared" si="2"/>
-        <v>0.2</v>
-      </c>
-      <c r="G7" s="29" t="str">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="H7" s="29">
-        <f t="shared" si="2"/>
-        <v>2.333333333</v>
-      </c>
-      <c r="I7" s="29">
+        <v>0.5714285714</v>
+      </c>
+      <c r="F7" s="30">
         <f t="shared" si="2"/>
         <v>0.1666666667</v>
       </c>
-      <c r="J7" s="29">
+      <c r="G7" s="30">
+        <f t="shared" si="2"/>
+        <v>2.428571429</v>
+      </c>
+      <c r="H7" s="30">
+        <f t="shared" si="2"/>
+        <v>0.4285714286</v>
+      </c>
+      <c r="I7" s="30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K7" s="29">
+      <c r="J7" s="30">
         <f t="shared" si="2"/>
-        <v>0.6666666667</v>
-      </c>
-      <c r="L7" s="29">
+        <v>0.7142857143</v>
+      </c>
+      <c r="K7" s="30">
         <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
+        <v>0.7142857143</v>
+      </c>
+      <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
@@ -33494,55 +33556,51 @@
       <c r="S7" s="5"/>
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="s">
-        <v>72</v>
+      <c r="A8" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="28">
+        <v>11</v>
+      </c>
+      <c r="C8" s="27">
         <f t="array" ref="C8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>5</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="27">
         <f t="array" ref="D8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>6</v>
-      </c>
-      <c r="E8" s="28">
+        <v>7</v>
+      </c>
+      <c r="E8" s="27">
         <f t="array" ref="E8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>1</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="27">
         <f t="array" ref="F8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>1</v>
-      </c>
-      <c r="G8" s="28">
+        <v>2</v>
+      </c>
+      <c r="G8" s="27">
         <f t="array" ref="G8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
+        <v>3</v>
+      </c>
+      <c r="H8" s="27">
+        <f t="array" ref="H8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
+        <v>2</v>
+      </c>
+      <c r="I8" s="27">
+        <f t="array" ref="I8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>0</v>
       </c>
-      <c r="H8" s="28">
-        <f t="array" ref="H8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>1</v>
-      </c>
-      <c r="I8" s="28">
-        <f t="array" ref="I8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>1</v>
-      </c>
-      <c r="J8" s="28">
+      <c r="J8" s="27">
         <f t="array" ref="J8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="28">
+        <v>4</v>
+      </c>
+      <c r="K8" s="27">
         <f t="array" ref="K8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>3</v>
       </c>
-      <c r="L8" s="28">
-        <f t="array" ref="L8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(L$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>2</v>
-      </c>
+      <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
@@ -33552,53 +33610,49 @@
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
     </row>
     <row r="9">
-      <c r="A9" s="26"/>
+      <c r="A9" s="25"/>
       <c r="B9" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="29">
-        <f t="shared" ref="C9:L9" si="3">C8/C2</f>
-        <v>0.8333333333</v>
-      </c>
-      <c r="D9" s="29">
+        <v>74</v>
+      </c>
+      <c r="C9" s="30">
+        <f t="shared" ref="C9:K9" si="3">C8/C2</f>
+        <v>0.7142857143</v>
+      </c>
+      <c r="D9" s="30">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f t="shared" si="3"/>
-        <v>0.1666666667</v>
-      </c>
-      <c r="F9" s="29">
+        <v>0.1428571429</v>
+      </c>
+      <c r="F9" s="30">
         <f t="shared" si="3"/>
-        <v>0.2</v>
-      </c>
-      <c r="G9" s="29" t="str">
+        <v>0.3333333333</v>
+      </c>
+      <c r="G9" s="30">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="H9" s="29">
+        <v>0.4285714286</v>
+      </c>
+      <c r="H9" s="30">
         <f t="shared" si="3"/>
-        <v>0.1666666667</v>
-      </c>
-      <c r="I9" s="29">
-        <f t="shared" si="3"/>
-        <v>0.1666666667</v>
-      </c>
-      <c r="J9" s="29">
+        <v>0.2857142857</v>
+      </c>
+      <c r="I9" s="30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K9" s="29">
+      <c r="J9" s="30">
         <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="L9" s="29">
+        <v>0.5714285714</v>
+      </c>
+      <c r="K9" s="30">
         <f t="shared" si="3"/>
-        <v>0.3333333333</v>
-      </c>
+        <v>0.4285714286</v>
+      </c>
+      <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
@@ -33608,55 +33662,51 @@
       <c r="S9" s="5"/>
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
-      <c r="V9" s="5"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="s">
-        <v>78</v>
+      <c r="A10" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="17">
-        <f t="shared" ref="C10:L10" si="4">C6+C8</f>
+        <v>11</v>
+      </c>
+      <c r="C10" s="11">
+        <f t="shared" ref="C10:K10" si="4">C6+C8</f>
+        <v>6</v>
+      </c>
+      <c r="D10" s="11">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="E10" s="11">
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="D10" s="17">
-        <f t="shared" si="4"/>
-        <v>13</v>
-      </c>
-      <c r="E10" s="17">
+      <c r="F10" s="11">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="F10" s="17">
+      <c r="G10" s="11">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="G10" s="17">
+        <v>20</v>
+      </c>
+      <c r="H10" s="11">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="I10" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H10" s="17">
+      <c r="J10" s="11">
         <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="I10" s="17">
+        <v>9</v>
+      </c>
+      <c r="K10" s="11">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="J10" s="17">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="17">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="L10" s="17">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
@@ -33666,53 +33716,49 @@
       <c r="S10" s="5"/>
       <c r="T10" s="5"/>
       <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
     </row>
     <row r="11">
-      <c r="A11" s="26"/>
+      <c r="A11" s="25"/>
       <c r="B11" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="29">
-        <f t="shared" ref="C11:L11" si="5">C10/C2</f>
-        <v>0.8333333333</v>
-      </c>
-      <c r="D11" s="29">
+        <v>74</v>
+      </c>
+      <c r="C11" s="30">
+        <f t="shared" ref="C11:K11" si="5">C10/C2</f>
+        <v>0.8571428571</v>
+      </c>
+      <c r="D11" s="30">
         <f t="shared" si="5"/>
-        <v>2.166666667</v>
-      </c>
-      <c r="E11" s="29">
+        <v>2.428571429</v>
+      </c>
+      <c r="E11" s="30">
+        <f t="shared" si="5"/>
+        <v>0.7142857143</v>
+      </c>
+      <c r="F11" s="30">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="F11" s="29">
+      <c r="G11" s="30">
         <f t="shared" si="5"/>
-        <v>0.4</v>
-      </c>
-      <c r="G11" s="29" t="str">
+        <v>2.857142857</v>
+      </c>
+      <c r="H11" s="30">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="H11" s="29">
-        <f t="shared" si="5"/>
-        <v>2.5</v>
-      </c>
-      <c r="I11" s="29">
-        <f t="shared" si="5"/>
-        <v>0.3333333333</v>
-      </c>
-      <c r="J11" s="29">
+        <v>0.7142857143</v>
+      </c>
+      <c r="I11" s="30">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="29">
+      <c r="J11" s="30">
         <f t="shared" si="5"/>
-        <v>1.166666667</v>
-      </c>
-      <c r="L11" s="29">
+        <v>1.285714286</v>
+      </c>
+      <c r="K11" s="30">
         <f t="shared" si="5"/>
-        <v>0.8333333333</v>
-      </c>
+        <v>1.142857143</v>
+      </c>
+      <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
@@ -33722,7 +33768,6 @@
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
       <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
     </row>
     <row r="12">
       <c r="A12" s="5"/>
@@ -33746,7 +33791,6 @@
       <c r="S12" s="5"/>
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
-      <c r="V12" s="5"/>
     </row>
     <row r="13">
       <c r="A13" s="5"/>
@@ -33770,7 +33814,6 @@
       <c r="S13" s="5"/>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
     </row>
     <row r="14">
       <c r="A14" s="5"/>
@@ -33794,7 +33837,6 @@
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
       <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
     </row>
     <row r="15">
       <c r="A15" s="5"/>
@@ -33818,7 +33860,6 @@
       <c r="S15" s="5"/>
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
-      <c r="V15" s="5"/>
     </row>
     <row r="16">
       <c r="A16" s="5"/>
@@ -33842,7 +33883,6 @@
       <c r="S16" s="5"/>
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
-      <c r="V16" s="5"/>
     </row>
     <row r="17">
       <c r="A17" s="5"/>
@@ -33866,7 +33906,6 @@
       <c r="S17" s="5"/>
       <c r="T17" s="5"/>
       <c r="U17" s="5"/>
-      <c r="V17" s="5"/>
     </row>
     <row r="18">
       <c r="A18" s="5"/>
@@ -33890,7 +33929,6 @@
       <c r="S18" s="5"/>
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
-      <c r="V18" s="5"/>
     </row>
     <row r="19">
       <c r="A19" s="5"/>
@@ -33914,7 +33952,6 @@
       <c r="S19" s="5"/>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
-      <c r="V19" s="5"/>
     </row>
     <row r="20">
       <c r="A20" s="5"/>
@@ -33938,7 +33975,6 @@
       <c r="S20" s="5"/>
       <c r="T20" s="5"/>
       <c r="U20" s="5"/>
-      <c r="V20" s="5"/>
     </row>
     <row r="21">
       <c r="A21" s="5"/>
@@ -33962,7 +33998,6 @@
       <c r="S21" s="5"/>
       <c r="T21" s="5"/>
       <c r="U21" s="5"/>
-      <c r="V21" s="5"/>
     </row>
     <row r="22">
       <c r="A22" s="5"/>
@@ -33986,7 +34021,6 @@
       <c r="S22" s="5"/>
       <c r="T22" s="5"/>
       <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
     </row>
     <row r="23">
       <c r="A23" s="5"/>
@@ -34010,7 +34044,6 @@
       <c r="S23" s="5"/>
       <c r="T23" s="5"/>
       <c r="U23" s="5"/>
-      <c r="V23" s="5"/>
     </row>
     <row r="24">
       <c r="A24" s="5"/>
@@ -34034,7 +34067,6 @@
       <c r="S24" s="5"/>
       <c r="T24" s="5"/>
       <c r="U24" s="5"/>
-      <c r="V24" s="5"/>
     </row>
     <row r="25">
       <c r="A25" s="5"/>
@@ -34058,7 +34090,6 @@
       <c r="S25" s="5"/>
       <c r="T25" s="5"/>
       <c r="U25" s="5"/>
-      <c r="V25" s="5"/>
     </row>
     <row r="26">
       <c r="A26" s="5"/>
@@ -34082,7 +34113,6 @@
       <c r="S26" s="5"/>
       <c r="T26" s="5"/>
       <c r="U26" s="5"/>
-      <c r="V26" s="5"/>
     </row>
     <row r="27">
       <c r="A27" s="5"/>
@@ -34106,7 +34136,6 @@
       <c r="S27" s="5"/>
       <c r="T27" s="5"/>
       <c r="U27" s="5"/>
-      <c r="V27" s="5"/>
     </row>
     <row r="28">
       <c r="A28" s="5"/>
@@ -34130,7 +34159,6 @@
       <c r="S28" s="5"/>
       <c r="T28" s="5"/>
       <c r="U28" s="5"/>
-      <c r="V28" s="5"/>
     </row>
     <row r="29">
       <c r="A29" s="5"/>
@@ -34154,7 +34182,6 @@
       <c r="S29" s="5"/>
       <c r="T29" s="5"/>
       <c r="U29" s="5"/>
-      <c r="V29" s="5"/>
     </row>
     <row r="30">
       <c r="A30" s="5"/>
@@ -34178,7 +34205,6 @@
       <c r="S30" s="5"/>
       <c r="T30" s="5"/>
       <c r="U30" s="5"/>
-      <c r="V30" s="5"/>
     </row>
     <row r="31">
       <c r="A31" s="5"/>
@@ -34202,7 +34228,6 @@
       <c r="S31" s="5"/>
       <c r="T31" s="5"/>
       <c r="U31" s="5"/>
-      <c r="V31" s="5"/>
     </row>
     <row r="32">
       <c r="A32" s="5"/>
@@ -34226,7 +34251,6 @@
       <c r="S32" s="5"/>
       <c r="T32" s="5"/>
       <c r="U32" s="5"/>
-      <c r="V32" s="5"/>
     </row>
     <row r="33">
       <c r="A33" s="5"/>
@@ -34250,7 +34274,6 @@
       <c r="S33" s="5"/>
       <c r="T33" s="5"/>
       <c r="U33" s="5"/>
-      <c r="V33" s="5"/>
     </row>
     <row r="34">
       <c r="A34" s="5"/>
@@ -34274,7 +34297,6 @@
       <c r="S34" s="5"/>
       <c r="T34" s="5"/>
       <c r="U34" s="5"/>
-      <c r="V34" s="5"/>
     </row>
     <row r="35">
       <c r="A35" s="5"/>
@@ -34298,7 +34320,6 @@
       <c r="S35" s="5"/>
       <c r="T35" s="5"/>
       <c r="U35" s="5"/>
-      <c r="V35" s="5"/>
     </row>
     <row r="36">
       <c r="A36" s="5"/>
@@ -34322,7 +34343,6 @@
       <c r="S36" s="5"/>
       <c r="T36" s="5"/>
       <c r="U36" s="5"/>
-      <c r="V36" s="5"/>
     </row>
     <row r="37">
       <c r="A37" s="5"/>
@@ -34346,7 +34366,6 @@
       <c r="S37" s="5"/>
       <c r="T37" s="5"/>
       <c r="U37" s="5"/>
-      <c r="V37" s="5"/>
     </row>
     <row r="38">
       <c r="A38" s="5"/>
@@ -34370,7 +34389,6 @@
       <c r="S38" s="5"/>
       <c r="T38" s="5"/>
       <c r="U38" s="5"/>
-      <c r="V38" s="5"/>
     </row>
     <row r="39">
       <c r="A39" s="5"/>
@@ -34394,7 +34412,6 @@
       <c r="S39" s="5"/>
       <c r="T39" s="5"/>
       <c r="U39" s="5"/>
-      <c r="V39" s="5"/>
     </row>
     <row r="40">
       <c r="A40" s="5"/>
@@ -34418,7 +34435,6 @@
       <c r="S40" s="5"/>
       <c r="T40" s="5"/>
       <c r="U40" s="5"/>
-      <c r="V40" s="5"/>
     </row>
     <row r="41">
       <c r="A41" s="5"/>
@@ -34442,7 +34458,6 @@
       <c r="S41" s="5"/>
       <c r="T41" s="5"/>
       <c r="U41" s="5"/>
-      <c r="V41" s="5"/>
     </row>
     <row r="42">
       <c r="A42" s="5"/>
@@ -34466,7 +34481,6 @@
       <c r="S42" s="5"/>
       <c r="T42" s="5"/>
       <c r="U42" s="5"/>
-      <c r="V42" s="5"/>
     </row>
     <row r="43">
       <c r="A43" s="5"/>
@@ -34490,7 +34504,6 @@
       <c r="S43" s="5"/>
       <c r="T43" s="5"/>
       <c r="U43" s="5"/>
-      <c r="V43" s="5"/>
     </row>
     <row r="44">
       <c r="A44" s="5"/>
@@ -34514,7 +34527,6 @@
       <c r="S44" s="5"/>
       <c r="T44" s="5"/>
       <c r="U44" s="5"/>
-      <c r="V44" s="5"/>
     </row>
     <row r="45">
       <c r="A45" s="5"/>
@@ -34538,7 +34550,6 @@
       <c r="S45" s="5"/>
       <c r="T45" s="5"/>
       <c r="U45" s="5"/>
-      <c r="V45" s="5"/>
     </row>
     <row r="46">
       <c r="A46" s="5"/>
@@ -34562,7 +34573,6 @@
       <c r="S46" s="5"/>
       <c r="T46" s="5"/>
       <c r="U46" s="5"/>
-      <c r="V46" s="5"/>
     </row>
     <row r="47">
       <c r="A47" s="5"/>
@@ -34586,7 +34596,6 @@
       <c r="S47" s="5"/>
       <c r="T47" s="5"/>
       <c r="U47" s="5"/>
-      <c r="V47" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/JO12-1/JO12-1_matchesDB.xlsx
+++ b/JO12-1/JO12-1_matchesDB.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="85">
   <si>
     <t>Matches</t>
   </si>
@@ -240,6 +240,18 @@
     <t>Amstelveen/Heemraad O12-1</t>
   </si>
   <si>
+    <t>1,1,0,3</t>
+  </si>
+  <si>
+    <t>1,1,2,3</t>
+  </si>
+  <si>
+    <t>1,0,2,1</t>
+  </si>
+  <si>
+    <t>1,1,6,1</t>
+  </si>
+  <si>
     <t>Scorers</t>
   </si>
   <si>
@@ -279,12 +291,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -353,6 +365,20 @@
   <borders count="11">
     <border/>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -360,20 +386,6 @@
         <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
@@ -392,6 +404,17 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
       <left/>
       <right style="medium">
         <color rgb="FF000000"/>
@@ -402,17 +425,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
     </border>
     <border>
       <left style="medium">
@@ -473,89 +485,92 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="5" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="6" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="7" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="8" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="9" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="16" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="16" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -783,15 +798,15 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6">
+      <c r="B1" s="7">
         <f>SUM(COUNTIF(J11:J40,"W"),COUNTIF(J11:J40,"D"),COUNTIF(J11:J40,"L"))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C1" s="5"/>
-      <c r="D1" s="7">
+      <c r="D1" s="8">
         <v>123.0</v>
       </c>
       <c r="E1" s="5"/>
@@ -827,7 +842,7 @@
       </c>
       <c r="B2" s="10">
         <f>COUNTIF(J11:J40,"W")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -938,7 +953,7 @@
       </c>
       <c r="B5" s="10">
         <f>B2*3+B4</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -975,10 +990,10 @@
       </c>
       <c r="B6" s="10">
         <f>B7-B8</f>
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="D6" s="11"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -1012,7 +1027,7 @@
       </c>
       <c r="B7" s="10">
         <f>SUM(K11:K40)</f>
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1044,12 +1059,12 @@
       <c r="AD7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="14">
         <f>SUM(L11:L40)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1094,16 +1109,16 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
       <c r="V9" s="5"/>
-      <c r="W9" s="14"/>
+      <c r="W9" s="15"/>
       <c r="X9" s="5"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5"/>
@@ -1113,43 +1128,43 @@
       <c r="AD9" s="5"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I10" s="16" t="s">
+      <c r="I10" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="K10" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="L10" s="16" t="s">
+      <c r="L10" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="M10" s="16" t="s">
+      <c r="M10" s="17" t="s">
         <v>30</v>
       </c>
       <c r="N10" s="4" t="s">
@@ -1179,1509 +1194,1534 @@
       <c r="V10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="W10" s="17" t="s">
+      <c r="W10" s="18" t="s">
         <v>31</v>
       </c>
       <c r="X10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="Y10" s="18" t="s">
+      <c r="Y10" s="19" t="s">
         <v>33</v>
       </c>
       <c r="AD10" s="5"/>
     </row>
     <row r="11">
-      <c r="A11" s="19">
+      <c r="A11" s="20">
         <f>IF(ISBLANK(B11),"",1)</f>
         <v>1</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="21">
         <v>1.0</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="22">
         <v>46256.0</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="23">
         <v>0.5555555555555556</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="19" t="str">
+      <c r="J11" s="20" t="str">
         <f t="shared" ref="J11:J40" si="1">IF(AND(NOT(ISBLANK(K11)),NOT(ISBLANK(L11))),IF(K11&gt;L11,"W",IF(K11&lt;L11,"L","D")),"")</f>
         <v>L</v>
       </c>
-      <c r="K11" s="24">
+      <c r="K11" s="25">
         <f t="array" ref="K11">IF(L11&lt;&gt;"", SUMPRODUCT(MID(N11:Y11,5,1)*1), "")</f>
         <v>1</v>
       </c>
-      <c r="L11" s="20">
+      <c r="L11" s="21">
         <v>2.0</v>
       </c>
-      <c r="M11" s="24">
+      <c r="M11" s="25">
         <f t="array" ref="M11">IF(L11&lt;&gt;"", SUMPRODUCT(LEFT(N11:Y11,1)*1), "")</f>
         <v>9</v>
       </c>
-      <c r="N11" s="17" t="s">
+      <c r="N11" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="O11" s="17" t="s">
+      <c r="O11" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="P11" s="17" t="s">
+      <c r="P11" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="Q11" s="17" t="s">
+      <c r="Q11" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="R11" s="17" t="s">
+      <c r="R11" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="S11" s="17" t="s">
+      <c r="S11" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="T11" s="17" t="s">
+      <c r="T11" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="U11" s="17" t="s">
+      <c r="U11" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="V11" s="17" t="s">
+      <c r="V11" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="W11" s="17" t="s">
+      <c r="W11" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="X11" s="17" t="s">
+      <c r="X11" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="Y11" s="17" t="s">
+      <c r="Y11" s="18" t="s">
         <v>41</v>
       </c>
       <c r="AD11" s="5"/>
     </row>
     <row r="12">
-      <c r="A12" s="19">
+      <c r="A12" s="20">
         <f t="shared" ref="A12:A40" si="2">IF(ISBLANK(B12),"",A11+1)</f>
         <v>2</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="21">
         <v>1.0</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="22">
         <v>46256.0</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="23">
         <v>0.5972222222222222</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="20" t="s">
+      <c r="G12" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="H12" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="20" t="s">
+      <c r="I12" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J12" s="19" t="str">
+      <c r="J12" s="20" t="str">
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="K12" s="24">
+      <c r="K12" s="25">
         <f t="array" ref="K12">IF(L12&lt;&gt;"", SUMPRODUCT(MID(N12:Y12,5,1)*1), "")</f>
         <v>0</v>
       </c>
-      <c r="L12" s="20">
+      <c r="L12" s="21">
         <v>1.0</v>
       </c>
-      <c r="M12" s="24">
+      <c r="M12" s="25">
         <f t="array" ref="M12">IF(L12&lt;&gt;"", SUMPRODUCT(LEFT(N12:Y12,1)*1), "")</f>
         <v>9</v>
       </c>
-      <c r="N12" s="17" t="s">
+      <c r="N12" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="O12" s="17" t="s">
+      <c r="O12" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="P12" s="17" t="s">
+      <c r="P12" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q12" s="17" t="s">
+      <c r="Q12" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="R12" s="17" t="s">
+      <c r="R12" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="S12" s="17" t="s">
+      <c r="S12" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="T12" s="17" t="s">
+      <c r="T12" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="U12" s="17" t="s">
+      <c r="U12" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="V12" s="17" t="s">
+      <c r="V12" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="W12" s="17" t="s">
+      <c r="W12" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="X12" s="17" t="s">
+      <c r="X12" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="Y12" s="17" t="s">
+      <c r="Y12" s="18" t="s">
         <v>41</v>
       </c>
       <c r="AD12" s="5"/>
     </row>
     <row r="13">
-      <c r="A13" s="19">
+      <c r="A13" s="20">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="21">
         <v>1.0</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="22">
         <v>46256.0</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="23">
         <v>0.6388888888888888</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="H13" s="20" t="s">
+      <c r="H13" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="20" t="s">
+      <c r="I13" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="19" t="str">
+      <c r="J13" s="20" t="str">
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="K13" s="24">
+      <c r="K13" s="25">
         <f t="array" ref="K13">IF(L13&lt;&gt;"", SUMPRODUCT(MID(N13:Y13,5,1)*1), "")</f>
         <v>1</v>
       </c>
-      <c r="L13" s="20">
+      <c r="L13" s="21">
         <v>3.0</v>
       </c>
-      <c r="M13" s="24">
+      <c r="M13" s="25">
         <f t="array" ref="M13">IF(L13&lt;&gt;"", SUMPRODUCT(LEFT(N13:Y13,1)*1), "")</f>
         <v>9</v>
       </c>
-      <c r="N13" s="17" t="s">
+      <c r="N13" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="17" t="s">
+      <c r="O13" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="P13" s="17" t="s">
+      <c r="P13" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q13" s="17" t="s">
+      <c r="Q13" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="R13" s="17" t="s">
+      <c r="R13" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="S13" s="17" t="s">
+      <c r="S13" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="T13" s="17" t="s">
+      <c r="T13" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="U13" s="17" t="s">
+      <c r="U13" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="V13" s="17" t="s">
+      <c r="V13" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="W13" s="17" t="s">
+      <c r="W13" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="X13" s="17" t="s">
+      <c r="X13" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="Y13" s="17" t="s">
+      <c r="Y13" s="18" t="s">
         <v>41</v>
       </c>
       <c r="AD13" s="5"/>
     </row>
     <row r="14">
-      <c r="A14" s="19">
+      <c r="A14" s="20">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="21">
         <v>1.0</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="22">
         <v>46270.0</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="23">
         <v>0.4166666666666667</v>
       </c>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20" t="s">
+      <c r="F14" s="21"/>
+      <c r="G14" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="I14" s="20" t="s">
+      <c r="I14" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J14" s="19" t="str">
+      <c r="J14" s="20" t="str">
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="K14" s="24">
+      <c r="K14" s="25">
         <f t="array" ref="K14">IF(L14&lt;&gt;"", SUMPRODUCT(MID(N14:Y14,5,1)*1), "")</f>
         <v>12</v>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="29">
         <v>5.0</v>
       </c>
-      <c r="M14" s="24">
+      <c r="M14" s="25">
         <f t="array" ref="M14">IF(L14&lt;&gt;"", SUMPRODUCT(LEFT(N14:Y14,1)*1), "")</f>
         <v>9</v>
       </c>
-      <c r="N14" s="17" t="s">
+      <c r="N14" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="O14" s="17" t="s">
+      <c r="O14" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="P14" s="17" t="s">
+      <c r="P14" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="Q14" s="17" t="s">
+      <c r="Q14" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="R14" s="17" t="s">
+      <c r="R14" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="S14" s="17" t="s">
+      <c r="S14" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="T14" s="17" t="s">
+      <c r="T14" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="U14" s="17" t="s">
+      <c r="U14" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="V14" s="17" t="s">
+      <c r="V14" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="W14" s="17" t="s">
+      <c r="W14" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="X14" s="17" t="s">
+      <c r="X14" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="Y14" s="17" t="s">
+      <c r="Y14" s="18" t="s">
         <v>41</v>
       </c>
       <c r="AD14" s="5"/>
     </row>
     <row r="15">
-      <c r="A15" s="19">
+      <c r="A15" s="20">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="21">
         <v>1.0</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="22">
         <v>46277.0</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="23">
         <v>0.375</v>
       </c>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20" t="s">
+      <c r="F15" s="21"/>
+      <c r="G15" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20" t="s">
+      <c r="H15" s="21"/>
+      <c r="I15" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="J15" s="19" t="str">
+      <c r="J15" s="20" t="str">
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="K15" s="24">
+      <c r="K15" s="25">
         <f t="array" ref="K15">IF(L15&lt;&gt;"", SUMPRODUCT(MID(N15:Y15,5,1)*1), "")</f>
         <v>14</v>
       </c>
-      <c r="L15" s="28">
+      <c r="L15" s="29">
         <v>3.0</v>
       </c>
-      <c r="M15" s="24">
+      <c r="M15" s="25">
         <f t="array" ref="M15">IF(L15&lt;&gt;"", SUMPRODUCT(LEFT(N15:Y15,1)*1), "")</f>
         <v>9</v>
       </c>
-      <c r="N15" s="17" t="s">
+      <c r="N15" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="O15" s="17" t="s">
+      <c r="O15" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="P15" s="17" t="s">
+      <c r="P15" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="Q15" s="17" t="s">
+      <c r="Q15" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="R15" s="17" t="s">
+      <c r="R15" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="S15" s="17" t="s">
+      <c r="S15" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="T15" s="17" t="s">
+      <c r="T15" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="U15" s="17" t="s">
+      <c r="U15" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="V15" s="17" t="s">
+      <c r="V15" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="W15" s="17" t="s">
+      <c r="W15" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="X15" s="17" t="s">
+      <c r="X15" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="Y15" s="17" t="s">
+      <c r="Y15" s="18" t="s">
         <v>41</v>
       </c>
       <c r="AD15" s="5"/>
     </row>
     <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="19">
+      <c r="A16" s="20">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="21">
         <v>1.0</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="22">
         <v>46284.0</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="23">
         <v>0.4375</v>
       </c>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20" t="s">
+      <c r="F16" s="21"/>
+      <c r="G16" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="H16" s="20" t="s">
+      <c r="H16" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="I16" s="20" t="s">
+      <c r="I16" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J16" s="19" t="str">
+      <c r="J16" s="20" t="str">
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="K16" s="24">
+      <c r="K16" s="25">
         <f t="array" ref="K16">IF(L16&lt;&gt;"", SUMPRODUCT(MID(N16:Y16,5,1)*1), "")</f>
         <v>8</v>
       </c>
-      <c r="L16" s="29">
+      <c r="L16" s="30">
         <v>1.0</v>
       </c>
-      <c r="M16" s="24">
+      <c r="M16" s="25">
         <f t="array" ref="M16">IF(L16&lt;&gt;"", SUMPRODUCT(LEFT(N16:Y16,1)*1), "")</f>
         <v>10</v>
       </c>
-      <c r="N16" s="17" t="s">
+      <c r="N16" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="O16" s="17" t="s">
+      <c r="O16" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="P16" s="17" t="s">
+      <c r="P16" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q16" s="17" t="s">
+      <c r="Q16" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="R16" s="17" t="s">
+      <c r="R16" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="S16" s="17" t="s">
+      <c r="S16" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="T16" s="17" t="s">
+      <c r="T16" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="U16" s="17" t="s">
+      <c r="U16" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="V16" s="17" t="s">
+      <c r="V16" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="W16" s="17" t="s">
+      <c r="W16" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="X16" s="17" t="s">
+      <c r="X16" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="Y16" s="17" t="s">
+      <c r="Y16" s="18" t="s">
         <v>41</v>
       </c>
       <c r="AD16" s="5"/>
     </row>
     <row r="17">
-      <c r="A17" s="19">
+      <c r="A17" s="20">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="21">
         <v>1.0</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="22">
         <v>46291.0</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="23">
         <v>0.375</v>
       </c>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20" t="s">
+      <c r="F17" s="21"/>
+      <c r="G17" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20" t="s">
+      <c r="H17" s="21"/>
+      <c r="I17" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="J17" s="19" t="str">
+      <c r="J17" s="20" t="str">
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="K17" s="24">
+      <c r="K17" s="25">
         <f t="array" ref="K17">IF(L17&lt;&gt;"", SUMPRODUCT(MID(N17:Y17,5,1)*1), "")</f>
         <v>15</v>
       </c>
-      <c r="L17" s="29">
+      <c r="L17" s="30">
         <v>1.0</v>
       </c>
-      <c r="M17" s="24">
+      <c r="M17" s="25">
         <f t="array" ref="M17">IF(L17&lt;&gt;"", SUMPRODUCT(LEFT(N17:Y17,1)*1), "")</f>
         <v>10</v>
       </c>
-      <c r="N17" s="17" t="s">
+      <c r="N17" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="O17" s="17" t="s">
+      <c r="O17" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="P17" s="17" t="s">
+      <c r="P17" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="Q17" s="17" t="s">
+      <c r="Q17" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="R17" s="17" t="s">
+      <c r="R17" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="S17" s="17" t="s">
+      <c r="S17" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="T17" s="17" t="s">
+      <c r="T17" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="U17" s="17" t="s">
+      <c r="U17" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="V17" s="17" t="s">
+      <c r="V17" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="W17" s="17" t="s">
+      <c r="W17" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="X17" s="17" t="s">
+      <c r="X17" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="Y17" s="17" t="s">
+      <c r="Y17" s="18" t="s">
         <v>66</v>
       </c>
       <c r="AD17" s="5"/>
     </row>
     <row r="18">
-      <c r="A18" s="19">
+      <c r="A18" s="20">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="B18" s="20">
+      <c r="B18" s="21">
         <v>1.0</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="22">
         <v>46298.0</v>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="23">
         <v>0.375</v>
       </c>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20" t="s">
+      <c r="F18" s="21"/>
+      <c r="G18" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20" t="s">
+      <c r="H18" s="21"/>
+      <c r="I18" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="J18" s="19" t="str">
+      <c r="J18" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>W</v>
+      </c>
+      <c r="K18" s="31">
+        <v>19.0</v>
+      </c>
+      <c r="L18" s="30">
+        <v>2.0</v>
+      </c>
+      <c r="M18" s="25">
+        <f t="array" ref="M18">IF(L18&lt;&gt;"", SUMPRODUCT(LEFT(N18:Y18,1)*1), "")</f>
+        <v>9</v>
+      </c>
+      <c r="N18" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="O18" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="P18" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q18" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="R18" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="S18" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="T18" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="U18" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="V18" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="W18" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="X18" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y18" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD18" s="5"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K18" s="24" t="str">
-        <f t="array" ref="K18">IF(L18&lt;&gt;"", SUMPRODUCT(MID(N18:Y18,5,1)*1), "")</f>
+      <c r="K19" s="25" t="str">
+        <f t="array" ref="K19">IF(L19&lt;&gt;"", SUMPRODUCT(MID(N19:Y19,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L18" s="28"/>
-      <c r="M18" s="24" t="str">
-        <f t="array" ref="M18">IF(L18&lt;&gt;"", SUMPRODUCT(LEFT(N18:Y18,1)*1), "")</f>
+      <c r="L19" s="29"/>
+      <c r="M19" s="25" t="str">
+        <f t="array" ref="M19">IF(L19&lt;&gt;"", SUMPRODUCT(LEFT(N19:Y19,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="17"/>
-      <c r="T18" s="17"/>
-      <c r="U18" s="17"/>
-      <c r="V18" s="17"/>
-      <c r="W18" s="17"/>
-      <c r="X18" s="17"/>
-      <c r="Y18" s="17"/>
-      <c r="AD18" s="5"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="str">
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="18"/>
+      <c r="R19" s="18"/>
+      <c r="S19" s="18"/>
+      <c r="T19" s="18"/>
+      <c r="U19" s="18"/>
+      <c r="V19" s="18"/>
+      <c r="W19" s="18"/>
+      <c r="X19" s="18"/>
+      <c r="Y19" s="18"/>
+      <c r="AD19" s="5"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="19" t="str">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K19" s="24" t="str">
-        <f t="array" ref="K19">IF(L19&lt;&gt;"", SUMPRODUCT(MID(N19:Y19,5,1)*1), "")</f>
+      <c r="K20" s="25" t="str">
+        <f t="array" ref="K20">IF(L20&lt;&gt;"", SUMPRODUCT(MID(N20:Y20,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L19" s="28"/>
-      <c r="M19" s="24" t="str">
-        <f t="array" ref="M19">IF(L19&lt;&gt;"", SUMPRODUCT(LEFT(N19:Y19,1)*1), "")</f>
+      <c r="L20" s="29"/>
+      <c r="M20" s="25" t="str">
+        <f t="array" ref="M20">IF(L20&lt;&gt;"", SUMPRODUCT(LEFT(N20:Y20,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="17"/>
-      <c r="T19" s="17"/>
-      <c r="U19" s="17"/>
-      <c r="V19" s="17"/>
-      <c r="W19" s="17"/>
-      <c r="X19" s="17"/>
-      <c r="Y19" s="17"/>
-      <c r="AD19" s="5"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="str">
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="18"/>
+      <c r="R20" s="18"/>
+      <c r="S20" s="18"/>
+      <c r="T20" s="18"/>
+      <c r="U20" s="18"/>
+      <c r="V20" s="18"/>
+      <c r="W20" s="18"/>
+      <c r="X20" s="18"/>
+      <c r="Y20" s="18"/>
+      <c r="AD20" s="5"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="19" t="str">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K20" s="24" t="str">
-        <f t="array" ref="K20">IF(L20&lt;&gt;"", SUMPRODUCT(MID(N20:Y20,5,1)*1), "")</f>
+      <c r="K21" s="25" t="str">
+        <f t="array" ref="K21">IF(L21&lt;&gt;"", SUMPRODUCT(MID(N21:Y21,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L20" s="28"/>
-      <c r="M20" s="24" t="str">
-        <f t="array" ref="M20">IF(L20&lt;&gt;"", SUMPRODUCT(LEFT(N20:Y20,1)*1), "")</f>
+      <c r="L21" s="29"/>
+      <c r="M21" s="25" t="str">
+        <f t="array" ref="M21">IF(L21&lt;&gt;"", SUMPRODUCT(LEFT(N21:Y21,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
-      <c r="R20" s="17"/>
-      <c r="S20" s="17"/>
-      <c r="T20" s="17"/>
-      <c r="U20" s="17"/>
-      <c r="V20" s="17"/>
-      <c r="W20" s="17"/>
-      <c r="X20" s="17"/>
-      <c r="Y20" s="17"/>
-      <c r="AD20" s="5"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="str">
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="18"/>
+      <c r="S21" s="18"/>
+      <c r="T21" s="18"/>
+      <c r="U21" s="18"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="18"/>
+      <c r="X21" s="18"/>
+      <c r="Y21" s="18"/>
+      <c r="AD21" s="5"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="19" t="str">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K21" s="24" t="str">
-        <f t="array" ref="K21">IF(L21&lt;&gt;"", SUMPRODUCT(MID(N21:Y21,5,1)*1), "")</f>
+      <c r="K22" s="25" t="str">
+        <f t="array" ref="K22">IF(L22&lt;&gt;"", SUMPRODUCT(MID(N22:Y22,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L21" s="28"/>
-      <c r="M21" s="24" t="str">
-        <f t="array" ref="M21">IF(L21&lt;&gt;"", SUMPRODUCT(LEFT(N21:Y21,1)*1), "")</f>
+      <c r="L22" s="29"/>
+      <c r="M22" s="25" t="str">
+        <f t="array" ref="M22">IF(L22&lt;&gt;"", SUMPRODUCT(LEFT(N22:Y22,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17"/>
-      <c r="S21" s="17"/>
-      <c r="T21" s="17"/>
-      <c r="U21" s="17"/>
-      <c r="V21" s="17"/>
-      <c r="W21" s="17"/>
-      <c r="X21" s="17"/>
-      <c r="Y21" s="17"/>
-      <c r="AD21" s="5"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="19" t="str">
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="18"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="18"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="18"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="18"/>
+      <c r="X22" s="18"/>
+      <c r="Y22" s="18"/>
+      <c r="AD22" s="5"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="19" t="str">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K22" s="24" t="str">
-        <f t="array" ref="K22">IF(L22&lt;&gt;"", SUMPRODUCT(MID(N22:Y22,5,1)*1), "")</f>
+      <c r="K23" s="25" t="str">
+        <f t="array" ref="K23">IF(L23&lt;&gt;"", SUMPRODUCT(MID(N23:Y23,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L22" s="28"/>
-      <c r="M22" s="24" t="str">
-        <f t="array" ref="M22">IF(L22&lt;&gt;"", SUMPRODUCT(LEFT(N22:Y22,1)*1), "")</f>
+      <c r="L23" s="29"/>
+      <c r="M23" s="25" t="str">
+        <f t="array" ref="M23">IF(L23&lt;&gt;"", SUMPRODUCT(LEFT(N23:Y23,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="17"/>
-      <c r="T22" s="17"/>
-      <c r="U22" s="17"/>
-      <c r="V22" s="17"/>
-      <c r="W22" s="17"/>
-      <c r="X22" s="17"/>
-      <c r="Y22" s="17"/>
-      <c r="AD22" s="5"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="str">
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="18"/>
+      <c r="R23" s="18"/>
+      <c r="S23" s="18"/>
+      <c r="T23" s="18"/>
+      <c r="U23" s="18"/>
+      <c r="V23" s="18"/>
+      <c r="W23" s="18"/>
+      <c r="X23" s="18"/>
+      <c r="Y23" s="18"/>
+      <c r="AD23" s="5"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="19" t="str">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K23" s="24" t="str">
-        <f t="array" ref="K23">IF(L23&lt;&gt;"", SUMPRODUCT(MID(N23:Y23,5,1)*1), "")</f>
+      <c r="K24" s="25" t="str">
+        <f t="array" ref="K24">IF(L24&lt;&gt;"", SUMPRODUCT(MID(N24:Y24,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L23" s="28"/>
-      <c r="M23" s="24" t="str">
-        <f t="array" ref="M23">IF(L23&lt;&gt;"", SUMPRODUCT(LEFT(N23:Y23,1)*1), "")</f>
+      <c r="L24" s="29"/>
+      <c r="M24" s="25" t="str">
+        <f t="array" ref="M24">IF(L24&lt;&gt;"", SUMPRODUCT(LEFT(N24:Y24,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="17"/>
-      <c r="S23" s="17"/>
-      <c r="T23" s="17"/>
-      <c r="U23" s="17"/>
-      <c r="V23" s="17"/>
-      <c r="W23" s="17"/>
-      <c r="X23" s="17"/>
-      <c r="Y23" s="17"/>
-      <c r="AD23" s="5"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="19" t="str">
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="18"/>
+      <c r="R24" s="18"/>
+      <c r="S24" s="18"/>
+      <c r="T24" s="18"/>
+      <c r="U24" s="18"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="18"/>
+      <c r="X24" s="18"/>
+      <c r="Y24" s="18"/>
+      <c r="AD24" s="5"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="19" t="str">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K24" s="24" t="str">
-        <f t="array" ref="K24">IF(L24&lt;&gt;"", SUMPRODUCT(MID(N24:Y24,5,1)*1), "")</f>
+      <c r="K25" s="25" t="str">
+        <f t="array" ref="K25">IF(L25&lt;&gt;"", SUMPRODUCT(MID(N25:Y25,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L24" s="28"/>
-      <c r="M24" s="24" t="str">
-        <f t="array" ref="M24">IF(L24&lt;&gt;"", SUMPRODUCT(LEFT(N24:Y24,1)*1), "")</f>
+      <c r="L25" s="29"/>
+      <c r="M25" s="25" t="str">
+        <f t="array" ref="M25">IF(L25&lt;&gt;"", SUMPRODUCT(LEFT(N25:Y25,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
-      <c r="R24" s="17"/>
-      <c r="S24" s="17"/>
-      <c r="T24" s="17"/>
-      <c r="U24" s="17"/>
-      <c r="V24" s="17"/>
-      <c r="W24" s="17"/>
-      <c r="X24" s="17"/>
-      <c r="Y24" s="17"/>
-      <c r="AD24" s="5"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="str">
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="18"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="18"/>
+      <c r="T25" s="18"/>
+      <c r="U25" s="18"/>
+      <c r="V25" s="18"/>
+      <c r="W25" s="18"/>
+      <c r="X25" s="18"/>
+      <c r="Y25" s="18"/>
+      <c r="AD25" s="5"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="19" t="str">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K25" s="24" t="str">
-        <f t="array" ref="K25">IF(L25&lt;&gt;"", SUMPRODUCT(MID(N25:Y25,5,1)*1), "")</f>
+      <c r="K26" s="25" t="str">
+        <f t="array" ref="K26">IF(L26&lt;&gt;"", SUMPRODUCT(MID(N26:Y26,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L25" s="28"/>
-      <c r="M25" s="24" t="str">
-        <f t="array" ref="M25">IF(L25&lt;&gt;"", SUMPRODUCT(LEFT(N25:Y25,1)*1), "")</f>
+      <c r="L26" s="29"/>
+      <c r="M26" s="25" t="str">
+        <f t="array" ref="M26">IF(L26&lt;&gt;"", SUMPRODUCT(LEFT(N26:Y26,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="17"/>
-      <c r="S25" s="17"/>
-      <c r="T25" s="17"/>
-      <c r="U25" s="17"/>
-      <c r="V25" s="17"/>
-      <c r="W25" s="17"/>
-      <c r="X25" s="17"/>
-      <c r="Y25" s="17"/>
-      <c r="AD25" s="5"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="19" t="str">
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="18"/>
+      <c r="T26" s="18"/>
+      <c r="U26" s="18"/>
+      <c r="V26" s="18"/>
+      <c r="W26" s="18"/>
+      <c r="X26" s="18"/>
+      <c r="Y26" s="18"/>
+      <c r="AD26" s="5"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="19" t="str">
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K26" s="24" t="str">
-        <f t="array" ref="K26">IF(L26&lt;&gt;"", SUMPRODUCT(MID(N26:Y26,5,1)*1), "")</f>
+      <c r="K27" s="25" t="str">
+        <f t="array" ref="K27">IF(L27&lt;&gt;"", SUMPRODUCT(MID(N27:Y27,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L26" s="28"/>
-      <c r="M26" s="24" t="str">
-        <f t="array" ref="M26">IF(L26&lt;&gt;"", SUMPRODUCT(LEFT(N26:Y26,1)*1), "")</f>
+      <c r="L27" s="21"/>
+      <c r="M27" s="25" t="str">
+        <f t="array" ref="M27">IF(L27&lt;&gt;"", SUMPRODUCT(LEFT(N27:Y27,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="17"/>
-      <c r="S26" s="17"/>
-      <c r="T26" s="17"/>
-      <c r="U26" s="17"/>
-      <c r="V26" s="17"/>
-      <c r="W26" s="17"/>
-      <c r="X26" s="17"/>
-      <c r="Y26" s="17"/>
-      <c r="AD26" s="5"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="str">
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="18"/>
+      <c r="T27" s="18"/>
+      <c r="U27" s="18"/>
+      <c r="V27" s="18"/>
+      <c r="W27" s="18"/>
+      <c r="X27" s="18"/>
+      <c r="Y27" s="18"/>
+      <c r="AD27" s="5"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="19" t="str">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K27" s="24" t="str">
-        <f t="array" ref="K27">IF(L27&lt;&gt;"", SUMPRODUCT(MID(N27:Y27,5,1)*1), "")</f>
+      <c r="K28" s="25" t="str">
+        <f t="array" ref="K28">IF(L28&lt;&gt;"", SUMPRODUCT(MID(N28:Y28,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L27" s="20"/>
-      <c r="M27" s="24" t="str">
-        <f t="array" ref="M27">IF(L27&lt;&gt;"", SUMPRODUCT(LEFT(N27:Y27,1)*1), "")</f>
+      <c r="L28" s="21"/>
+      <c r="M28" s="25" t="str">
+        <f t="array" ref="M28">IF(L28&lt;&gt;"", SUMPRODUCT(LEFT(N28:Y28,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
-      <c r="R27" s="17"/>
-      <c r="S27" s="17"/>
-      <c r="T27" s="17"/>
-      <c r="U27" s="17"/>
-      <c r="V27" s="17"/>
-      <c r="W27" s="17"/>
-      <c r="X27" s="17"/>
-      <c r="Y27" s="17"/>
-      <c r="AD27" s="5"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="str">
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="18"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="18"/>
+      <c r="T28" s="18"/>
+      <c r="U28" s="18"/>
+      <c r="V28" s="18"/>
+      <c r="W28" s="18"/>
+      <c r="X28" s="18"/>
+      <c r="Y28" s="18"/>
+      <c r="AD28" s="5"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="19" t="str">
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K28" s="24" t="str">
-        <f t="array" ref="K28">IF(L28&lt;&gt;"", SUMPRODUCT(MID(N28:Y28,5,1)*1), "")</f>
+      <c r="K29" s="25" t="str">
+        <f t="array" ref="K29">IF(L29&lt;&gt;"", SUMPRODUCT(MID(N29:Y29,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L28" s="20"/>
-      <c r="M28" s="24" t="str">
-        <f t="array" ref="M28">IF(L28&lt;&gt;"", SUMPRODUCT(LEFT(N28:Y28,1)*1), "")</f>
+      <c r="L29" s="21"/>
+      <c r="M29" s="25" t="str">
+        <f t="array" ref="M29">IF(L29&lt;&gt;"", SUMPRODUCT(LEFT(N29:Y29,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="17"/>
-      <c r="S28" s="17"/>
-      <c r="T28" s="17"/>
-      <c r="U28" s="17"/>
-      <c r="V28" s="17"/>
-      <c r="W28" s="17"/>
-      <c r="X28" s="17"/>
-      <c r="Y28" s="17"/>
-      <c r="AD28" s="5"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="str">
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="18"/>
+      <c r="R29" s="18"/>
+      <c r="S29" s="18"/>
+      <c r="T29" s="18"/>
+      <c r="U29" s="18"/>
+      <c r="V29" s="18"/>
+      <c r="W29" s="18"/>
+      <c r="X29" s="18"/>
+      <c r="Y29" s="18"/>
+      <c r="AD29" s="5"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="19" t="str">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K29" s="24" t="str">
-        <f t="array" ref="K29">IF(L29&lt;&gt;"", SUMPRODUCT(MID(N29:Y29,5,1)*1), "")</f>
+      <c r="K30" s="25" t="str">
+        <f t="array" ref="K30">IF(L30&lt;&gt;"", SUMPRODUCT(MID(N30:Y30,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L29" s="20"/>
-      <c r="M29" s="24" t="str">
-        <f t="array" ref="M29">IF(L29&lt;&gt;"", SUMPRODUCT(LEFT(N29:Y29,1)*1), "")</f>
+      <c r="L30" s="21"/>
+      <c r="M30" s="25" t="str">
+        <f t="array" ref="M30">IF(L30&lt;&gt;"", SUMPRODUCT(LEFT(N30:Y30,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="17"/>
-      <c r="T29" s="17"/>
-      <c r="U29" s="17"/>
-      <c r="V29" s="17"/>
-      <c r="W29" s="17"/>
-      <c r="X29" s="17"/>
-      <c r="Y29" s="17"/>
-      <c r="AD29" s="5"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="str">
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="18"/>
+      <c r="R30" s="18"/>
+      <c r="S30" s="18"/>
+      <c r="T30" s="18"/>
+      <c r="U30" s="18"/>
+      <c r="V30" s="18"/>
+      <c r="W30" s="18"/>
+      <c r="X30" s="18"/>
+      <c r="Y30" s="18"/>
+      <c r="AD30" s="5"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="19" t="str">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K30" s="24" t="str">
-        <f t="array" ref="K30">IF(L30&lt;&gt;"", SUMPRODUCT(MID(N30:Y30,5,1)*1), "")</f>
+      <c r="K31" s="25" t="str">
+        <f t="array" ref="K31">IF(L31&lt;&gt;"", SUMPRODUCT(MID(N31:Y31,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L30" s="20"/>
-      <c r="M30" s="24" t="str">
-        <f t="array" ref="M30">IF(L30&lt;&gt;"", SUMPRODUCT(LEFT(N30:Y30,1)*1), "")</f>
+      <c r="L31" s="21"/>
+      <c r="M31" s="25" t="str">
+        <f t="array" ref="M31">IF(L31&lt;&gt;"", SUMPRODUCT(LEFT(N31:Y31,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-      <c r="P30" s="17"/>
-      <c r="Q30" s="17"/>
-      <c r="R30" s="17"/>
-      <c r="S30" s="17"/>
-      <c r="T30" s="17"/>
-      <c r="U30" s="17"/>
-      <c r="V30" s="17"/>
-      <c r="W30" s="17"/>
-      <c r="X30" s="17"/>
-      <c r="Y30" s="17"/>
-      <c r="AD30" s="5"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="19" t="str">
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="18"/>
+      <c r="Q31" s="18"/>
+      <c r="R31" s="18"/>
+      <c r="S31" s="18"/>
+      <c r="T31" s="18"/>
+      <c r="U31" s="18"/>
+      <c r="V31" s="18"/>
+      <c r="W31" s="18"/>
+      <c r="X31" s="18"/>
+      <c r="Y31" s="18"/>
+      <c r="AD31" s="5"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="19" t="str">
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K31" s="24" t="str">
-        <f t="array" ref="K31">IF(L31&lt;&gt;"", SUMPRODUCT(MID(N31:Y31,5,1)*1), "")</f>
+      <c r="K32" s="25" t="str">
+        <f t="array" ref="K32">IF(L32&lt;&gt;"", SUMPRODUCT(MID(N32:Y32,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L31" s="20"/>
-      <c r="M31" s="24" t="str">
-        <f t="array" ref="M31">IF(L31&lt;&gt;"", SUMPRODUCT(LEFT(N31:Y31,1)*1), "")</f>
+      <c r="L32" s="21"/>
+      <c r="M32" s="25" t="str">
+        <f t="array" ref="M32">IF(L32&lt;&gt;"", SUMPRODUCT(LEFT(N32:Y32,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N31" s="17"/>
-      <c r="O31" s="17"/>
-      <c r="P31" s="17"/>
-      <c r="Q31" s="17"/>
-      <c r="R31" s="17"/>
-      <c r="S31" s="17"/>
-      <c r="T31" s="17"/>
-      <c r="U31" s="17"/>
-      <c r="V31" s="17"/>
-      <c r="W31" s="17"/>
-      <c r="X31" s="17"/>
-      <c r="Y31" s="17"/>
-      <c r="AD31" s="5"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="19" t="str">
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
+      <c r="Q32" s="18"/>
+      <c r="R32" s="18"/>
+      <c r="S32" s="18"/>
+      <c r="T32" s="18"/>
+      <c r="U32" s="18"/>
+      <c r="V32" s="18"/>
+      <c r="W32" s="18"/>
+      <c r="X32" s="18"/>
+      <c r="Y32" s="18"/>
+      <c r="AD32" s="5"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="19" t="str">
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K32" s="24" t="str">
-        <f t="array" ref="K32">IF(L32&lt;&gt;"", SUMPRODUCT(MID(N32:Y32,5,1)*1), "")</f>
+      <c r="K33" s="25" t="str">
+        <f t="array" ref="K33">IF(L33&lt;&gt;"", SUMPRODUCT(MID(N33:Y33,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L32" s="20"/>
-      <c r="M32" s="24" t="str">
-        <f t="array" ref="M32">IF(L32&lt;&gt;"", SUMPRODUCT(LEFT(N32:Y32,1)*1), "")</f>
+      <c r="L33" s="21"/>
+      <c r="M33" s="25" t="str">
+        <f t="array" ref="M33">IF(L33&lt;&gt;"", SUMPRODUCT(LEFT(N33:Y33,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
-      <c r="R32" s="17"/>
-      <c r="S32" s="17"/>
-      <c r="T32" s="17"/>
-      <c r="U32" s="17"/>
-      <c r="V32" s="17"/>
-      <c r="W32" s="17"/>
-      <c r="X32" s="17"/>
-      <c r="Y32" s="17"/>
-      <c r="AD32" s="5"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="19" t="str">
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="18"/>
+      <c r="Q33" s="18"/>
+      <c r="R33" s="18"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="18"/>
+      <c r="U33" s="18"/>
+      <c r="V33" s="18"/>
+      <c r="W33" s="18"/>
+      <c r="X33" s="18"/>
+      <c r="Y33" s="18"/>
+      <c r="AD33" s="5"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="19" t="str">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K33" s="24" t="str">
-        <f t="array" ref="K33">IF(L33&lt;&gt;"", SUMPRODUCT(MID(N33:Y33,5,1)*1), "")</f>
+      <c r="K34" s="25" t="str">
+        <f t="array" ref="K34">IF(L34&lt;&gt;"", SUMPRODUCT(MID(N34:Y34,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L33" s="20"/>
-      <c r="M33" s="24" t="str">
-        <f t="array" ref="M33">IF(L33&lt;&gt;"", SUMPRODUCT(LEFT(N33:Y33,1)*1), "")</f>
+      <c r="L34" s="21"/>
+      <c r="M34" s="25" t="str">
+        <f t="array" ref="M34">IF(L34&lt;&gt;"", SUMPRODUCT(LEFT(N34:Y34,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="17"/>
-      <c r="S33" s="17"/>
-      <c r="T33" s="17"/>
-      <c r="U33" s="17"/>
-      <c r="V33" s="17"/>
-      <c r="W33" s="17"/>
-      <c r="X33" s="17"/>
-      <c r="Y33" s="17"/>
-      <c r="AD33" s="5"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="19" t="str">
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="18"/>
+      <c r="Q34" s="18"/>
+      <c r="R34" s="18"/>
+      <c r="S34" s="18"/>
+      <c r="T34" s="18"/>
+      <c r="U34" s="18"/>
+      <c r="V34" s="18"/>
+      <c r="W34" s="18"/>
+      <c r="X34" s="18"/>
+      <c r="Y34" s="18"/>
+      <c r="AD34" s="5"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="19" t="str">
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K34" s="24" t="str">
-        <f t="array" ref="K34">IF(L34&lt;&gt;"", SUMPRODUCT(MID(N34:Y34,5,1)*1), "")</f>
+      <c r="K35" s="25" t="str">
+        <f t="array" ref="K35">IF(L35&lt;&gt;"", SUMPRODUCT(MID(N35:Y35,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L34" s="20"/>
-      <c r="M34" s="24" t="str">
-        <f t="array" ref="M34">IF(L34&lt;&gt;"", SUMPRODUCT(LEFT(N34:Y34,1)*1), "")</f>
+      <c r="L35" s="21"/>
+      <c r="M35" s="25" t="str">
+        <f t="array" ref="M35">IF(L35&lt;&gt;"", SUMPRODUCT(LEFT(N35:Y35,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-      <c r="R34" s="17"/>
-      <c r="S34" s="17"/>
-      <c r="T34" s="17"/>
-      <c r="U34" s="17"/>
-      <c r="V34" s="17"/>
-      <c r="W34" s="17"/>
-      <c r="X34" s="17"/>
-      <c r="Y34" s="17"/>
-      <c r="AD34" s="5"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="19" t="str">
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="18"/>
+      <c r="R35" s="18"/>
+      <c r="S35" s="18"/>
+      <c r="T35" s="18"/>
+      <c r="U35" s="18"/>
+      <c r="V35" s="18"/>
+      <c r="W35" s="18"/>
+      <c r="X35" s="18"/>
+      <c r="Y35" s="18"/>
+      <c r="AD35" s="5"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="19" t="str">
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K35" s="24" t="str">
-        <f t="array" ref="K35">IF(L35&lt;&gt;"", SUMPRODUCT(MID(N35:Y35,5,1)*1), "")</f>
+      <c r="K36" s="25" t="str">
+        <f t="array" ref="K36">IF(L36&lt;&gt;"", SUMPRODUCT(MID(N36:Y36,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L35" s="20"/>
-      <c r="M35" s="24" t="str">
-        <f t="array" ref="M35">IF(L35&lt;&gt;"", SUMPRODUCT(LEFT(N35:Y35,1)*1), "")</f>
+      <c r="L36" s="29"/>
+      <c r="M36" s="25" t="str">
+        <f t="array" ref="M36">IF(L36&lt;&gt;"", SUMPRODUCT(LEFT(N36:Y36,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-      <c r="R35" s="17"/>
-      <c r="S35" s="17"/>
-      <c r="T35" s="17"/>
-      <c r="U35" s="17"/>
-      <c r="V35" s="17"/>
-      <c r="W35" s="17"/>
-      <c r="X35" s="17"/>
-      <c r="Y35" s="17"/>
-      <c r="AD35" s="5"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="19" t="str">
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="18"/>
+      <c r="Q36" s="18"/>
+      <c r="R36" s="18"/>
+      <c r="S36" s="18"/>
+      <c r="T36" s="18"/>
+      <c r="U36" s="18"/>
+      <c r="V36" s="18"/>
+      <c r="W36" s="18"/>
+      <c r="X36" s="18"/>
+      <c r="Y36" s="18"/>
+      <c r="AD36" s="5"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="19" t="str">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="24" t="str">
-        <f t="array" ref="K36">IF(L36&lt;&gt;"", SUMPRODUCT(MID(N36:Y36,5,1)*1), "")</f>
+      <c r="K37" s="25" t="str">
+        <f t="array" ref="K37">IF(L37&lt;&gt;"", SUMPRODUCT(MID(N37:Y37,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L36" s="28"/>
-      <c r="M36" s="24" t="str">
-        <f t="array" ref="M36">IF(L36&lt;&gt;"", SUMPRODUCT(LEFT(N36:Y36,1)*1), "")</f>
+      <c r="L37" s="21"/>
+      <c r="M37" s="25" t="str">
+        <f t="array" ref="M37">IF(L37&lt;&gt;"", SUMPRODUCT(LEFT(N37:Y37,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="17"/>
-      <c r="T36" s="17"/>
-      <c r="U36" s="17"/>
-      <c r="V36" s="17"/>
-      <c r="W36" s="17"/>
-      <c r="X36" s="17"/>
-      <c r="Y36" s="17"/>
-      <c r="AD36" s="5"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="19" t="str">
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="18"/>
+      <c r="R37" s="18"/>
+      <c r="S37" s="18"/>
+      <c r="T37" s="18"/>
+      <c r="U37" s="18"/>
+      <c r="V37" s="18"/>
+      <c r="W37" s="18"/>
+      <c r="X37" s="18"/>
+      <c r="Y37" s="18"/>
+      <c r="AD37" s="5"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="19" t="str">
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K37" s="24" t="str">
-        <f t="array" ref="K37">IF(L37&lt;&gt;"", SUMPRODUCT(MID(N37:Y37,5,1)*1), "")</f>
+      <c r="K38" s="25" t="str">
+        <f t="array" ref="K38">IF(L38&lt;&gt;"", SUMPRODUCT(MID(N38:Y38,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L37" s="20"/>
-      <c r="M37" s="24" t="str">
-        <f t="array" ref="M37">IF(L37&lt;&gt;"", SUMPRODUCT(LEFT(N37:Y37,1)*1), "")</f>
+      <c r="L38" s="21"/>
+      <c r="M38" s="25" t="str">
+        <f t="array" ref="M38">IF(L38&lt;&gt;"", SUMPRODUCT(LEFT(N38:Y38,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-      <c r="R37" s="17"/>
-      <c r="S37" s="17"/>
-      <c r="T37" s="17"/>
-      <c r="U37" s="17"/>
-      <c r="V37" s="17"/>
-      <c r="W37" s="17"/>
-      <c r="X37" s="17"/>
-      <c r="Y37" s="17"/>
-      <c r="AD37" s="5"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="19" t="str">
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="18"/>
+      <c r="S38" s="18"/>
+      <c r="T38" s="18"/>
+      <c r="U38" s="18"/>
+      <c r="V38" s="18"/>
+      <c r="W38" s="18"/>
+      <c r="X38" s="18"/>
+      <c r="Y38" s="18"/>
+      <c r="AD38" s="5"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="19" t="str">
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K38" s="24" t="str">
-        <f t="array" ref="K38">IF(L38&lt;&gt;"", SUMPRODUCT(MID(N38:Y38,5,1)*1), "")</f>
+      <c r="K39" s="25" t="str">
+        <f t="array" ref="K39">IF(L39&lt;&gt;"", SUMPRODUCT(MID(N39:Y39,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L38" s="20"/>
-      <c r="M38" s="24" t="str">
-        <f t="array" ref="M38">IF(L38&lt;&gt;"", SUMPRODUCT(LEFT(N38:Y38,1)*1), "")</f>
+      <c r="L39" s="21"/>
+      <c r="M39" s="25" t="str">
+        <f t="array" ref="M39">IF(L39&lt;&gt;"", SUMPRODUCT(LEFT(N39:Y39,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
-      <c r="R38" s="17"/>
-      <c r="S38" s="17"/>
-      <c r="T38" s="17"/>
-      <c r="U38" s="17"/>
-      <c r="V38" s="17"/>
-      <c r="W38" s="17"/>
-      <c r="X38" s="17"/>
-      <c r="Y38" s="17"/>
-      <c r="AD38" s="5"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="19" t="str">
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="18"/>
+      <c r="Q39" s="18"/>
+      <c r="R39" s="18"/>
+      <c r="S39" s="18"/>
+      <c r="T39" s="18"/>
+      <c r="U39" s="18"/>
+      <c r="V39" s="18"/>
+      <c r="W39" s="18"/>
+      <c r="X39" s="18"/>
+      <c r="Y39" s="18"/>
+      <c r="AD39" s="5"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="19" t="str">
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K39" s="24" t="str">
-        <f t="array" ref="K39">IF(L39&lt;&gt;"", SUMPRODUCT(MID(N39:Y39,5,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="L39" s="20"/>
-      <c r="M39" s="24" t="str">
-        <f t="array" ref="M39">IF(L39&lt;&gt;"", SUMPRODUCT(LEFT(N39:Y39,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="N39" s="17"/>
-      <c r="O39" s="17"/>
-      <c r="P39" s="17"/>
-      <c r="Q39" s="17"/>
-      <c r="R39" s="17"/>
-      <c r="S39" s="17"/>
-      <c r="T39" s="17"/>
-      <c r="U39" s="17"/>
-      <c r="V39" s="17"/>
-      <c r="W39" s="17"/>
-      <c r="X39" s="17"/>
-      <c r="Y39" s="17"/>
-      <c r="AD39" s="5"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="19" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="24" t="str">
+      <c r="K40" s="25" t="str">
         <f t="array" ref="K40">IF(L40&lt;&gt;"", SUMPRODUCT(MID(N40:Y40,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L40" s="20"/>
-      <c r="M40" s="24" t="str">
+      <c r="L40" s="21"/>
+      <c r="M40" s="25" t="str">
         <f t="array" ref="M40">IF(L40&lt;&gt;"", SUMPRODUCT(LEFT(N40:Y40,1)*1), "")</f>
         <v/>
       </c>
-      <c r="N40" s="17"/>
-      <c r="O40" s="17"/>
-      <c r="P40" s="17"/>
-      <c r="Q40" s="17"/>
-      <c r="R40" s="17"/>
-      <c r="S40" s="17"/>
-      <c r="T40" s="17"/>
-      <c r="U40" s="17"/>
-      <c r="V40" s="17"/>
-      <c r="W40" s="17"/>
-      <c r="X40" s="17"/>
-      <c r="Y40" s="17"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="18"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="18"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="18"/>
+      <c r="V40" s="18"/>
+      <c r="W40" s="18"/>
+      <c r="X40" s="18"/>
+      <c r="Y40" s="18"/>
       <c r="AD40" s="5"/>
     </row>
     <row r="41">
@@ -2809,17 +2849,17 @@
       <c r="J44" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K44" s="17" t="s">
+      <c r="K44" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="L44" s="31" t="s">
+      <c r="L44" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="M44" s="31" t="s">
+      <c r="M44" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="N44" s="17" t="s">
-        <v>77</v>
+      <c r="N44" s="18" t="s">
+        <v>81</v>
       </c>
       <c r="O44" s="5"/>
       <c r="T44" s="5"/>
@@ -2836,48 +2876,48 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B45" s="32">
+        <v>82</v>
+      </c>
+      <c r="B45" s="11">
         <v>1.0</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="11">
         <v>1.0</v>
       </c>
-      <c r="D45" s="32">
+      <c r="D45" s="11">
         <v>1.0</v>
       </c>
-      <c r="E45" s="32">
+      <c r="E45" s="11">
         <v>1.0</v>
       </c>
-      <c r="F45" s="32">
+      <c r="F45" s="11">
         <v>1.0</v>
       </c>
-      <c r="G45" s="32">
+      <c r="G45" s="11">
         <v>1.0</v>
       </c>
-      <c r="H45" s="32">
+      <c r="H45" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="I45" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="J45" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="K45" s="11">
         <v>0.0</v>
       </c>
-      <c r="I45" s="32">
-        <v>1.0</v>
-      </c>
-      <c r="J45" s="32">
-        <v>1.0</v>
-      </c>
-      <c r="K45" s="32">
-        <v>1.0</v>
-      </c>
-      <c r="L45" s="32">
+      <c r="L45" s="11">
         <v>0.0</v>
       </c>
-      <c r="M45" s="32">
-        <v>1.0</v>
+      <c r="M45" s="11">
+        <v>0.0</v>
       </c>
       <c r="N45" s="5"/>
-      <c r="O45" s="33">
+      <c r="O45" s="34">
         <f t="shared" ref="O45:O48" si="3">SUM(A45:N45)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" s="5"/>
       <c r="U45" s="5"/>
@@ -2895,46 +2935,46 @@
       <c r="A46" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="32">
+      <c r="B46" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="C46" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="D46" s="11">
         <v>0.0</v>
       </c>
-      <c r="C46" s="32">
+      <c r="E46" s="11">
         <v>1.0</v>
       </c>
-      <c r="D46" s="32">
+      <c r="F46" s="11">
         <v>1.0</v>
       </c>
-      <c r="E46" s="32">
+      <c r="G46" s="11">
         <v>1.0</v>
       </c>
-      <c r="F46" s="32">
+      <c r="H46" s="11">
         <v>1.0</v>
       </c>
-      <c r="G46" s="32">
+      <c r="I46" s="11">
         <v>1.0</v>
       </c>
-      <c r="H46" s="32">
+      <c r="J46" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="K46" s="11">
         <v>0.0</v>
       </c>
-      <c r="I46" s="32">
-        <v>1.0</v>
-      </c>
-      <c r="J46" s="32">
-        <v>1.0</v>
-      </c>
-      <c r="K46" s="32">
+      <c r="L46" s="11">
         <v>0.0</v>
       </c>
-      <c r="L46" s="32">
+      <c r="M46" s="11">
         <v>0.0</v>
       </c>
-      <c r="M46" s="32">
-        <v>0.0</v>
-      </c>
       <c r="N46" s="5"/>
-      <c r="O46" s="33">
+      <c r="O46" s="34">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T46" s="5"/>
       <c r="U46" s="5"/>
@@ -2950,48 +2990,48 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B47" s="32">
+        <v>83</v>
+      </c>
+      <c r="B47" s="11">
+        <v>0.0</v>
+      </c>
+      <c r="C47" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="D47" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="E47" s="11">
         <v>1.0</v>
       </c>
-      <c r="C47" s="32">
-        <v>3.0</v>
-      </c>
-      <c r="D47" s="32">
-        <v>2.0</v>
-      </c>
-      <c r="E47" s="32">
+      <c r="F47" s="11">
+        <v>4.0</v>
+      </c>
+      <c r="G47" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="H47" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="I47" s="11">
+        <v>6.0</v>
+      </c>
+      <c r="J47" s="11">
         <v>0.0</v>
       </c>
-      <c r="F47" s="32">
-        <v>3.0</v>
-      </c>
-      <c r="G47" s="32">
-        <v>2.0</v>
-      </c>
-      <c r="H47" s="32">
+      <c r="K47" s="11">
         <v>0.0</v>
       </c>
-      <c r="I47" s="32">
-        <v>1.0</v>
-      </c>
-      <c r="J47" s="32">
-        <v>2.0</v>
-      </c>
-      <c r="K47" s="32">
+      <c r="L47" s="11">
         <v>0.0</v>
       </c>
-      <c r="L47" s="32">
+      <c r="M47" s="11">
         <v>0.0</v>
       </c>
-      <c r="M47" s="32">
-        <v>1.0</v>
-      </c>
       <c r="N47" s="5"/>
-      <c r="O47" s="33">
+      <c r="O47" s="34">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T47" s="5"/>
       <c r="U47" s="5"/>
@@ -3007,46 +3047,46 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B48" s="32">
+        <v>84</v>
+      </c>
+      <c r="B48" s="11">
+        <v>3.0</v>
+      </c>
+      <c r="C48" s="11">
+        <v>3.0</v>
+      </c>
+      <c r="D48" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="E48" s="11">
         <v>0.0</v>
       </c>
-      <c r="C48" s="32">
+      <c r="F48" s="11">
         <v>1.0</v>
       </c>
-      <c r="D48" s="32">
+      <c r="G48" s="11">
         <v>0.0</v>
       </c>
-      <c r="E48" s="32">
+      <c r="H48" s="11">
+        <v>0.0</v>
+      </c>
+      <c r="I48" s="11">
         <v>1.0</v>
       </c>
-      <c r="F48" s="32">
-        <v>2.0</v>
-      </c>
-      <c r="G48" s="32">
+      <c r="J48" s="11">
         <v>1.0</v>
       </c>
-      <c r="H48" s="32">
+      <c r="K48" s="11">
         <v>0.0</v>
       </c>
-      <c r="I48" s="32">
-        <v>1.0</v>
-      </c>
-      <c r="J48" s="32">
-        <v>1.0</v>
-      </c>
-      <c r="K48" s="32">
-        <v>2.0</v>
-      </c>
-      <c r="L48" s="32">
+      <c r="L48" s="11">
         <v>0.0</v>
       </c>
-      <c r="M48" s="32">
-        <v>1.0</v>
+      <c r="M48" s="11">
+        <v>0.0</v>
       </c>
       <c r="N48" s="5"/>
-      <c r="O48" s="33">
+      <c r="O48" s="34">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -3066,43 +3106,43 @@
       <c r="A49" s="5"/>
       <c r="B49" s="5" t="str">
         <f t="shared" ref="B49:N49" si="4">B45&amp;","&amp;B46&amp;","&amp;B47&amp;","&amp;B48</f>
-        <v>1,0,1,0</v>
+        <v>1,1,0,3</v>
       </c>
       <c r="C49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,1,3,1</v>
+        <v>1,1,2,3</v>
       </c>
       <c r="D49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,1,2,0</v>
+        <v>1,0,2,1</v>
       </c>
       <c r="E49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,1,0,1</v>
+        <v>1,1,1,0</v>
       </c>
       <c r="F49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,1,3,2</v>
+        <v>1,1,4,1</v>
       </c>
       <c r="G49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,1,2,1</v>
+        <v>1,1,1,0</v>
       </c>
       <c r="H49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>0,0,0,0</v>
+        <v>1,1,1,0</v>
       </c>
       <c r="I49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,1,1,1</v>
+        <v>1,1,6,1</v>
       </c>
       <c r="J49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,1,2,1</v>
+        <v>1,1,0,1</v>
       </c>
       <c r="K49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,0,0,2</v>
+        <v>0,0,0,0</v>
       </c>
       <c r="L49" s="5" t="str">
         <f t="shared" si="4"/>
@@ -3110,7 +3150,7 @@
       </c>
       <c r="M49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>1,0,1,1</v>
+        <v>0,0,0,0</v>
       </c>
       <c r="N49" s="5" t="str">
         <f t="shared" si="4"/>
@@ -33197,9 +33237,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="14.88"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2"/>
+      <c r="A1" s="1"/>
       <c r="B1" s="3"/>
       <c r="C1" s="4" t="s">
         <v>1</v>
@@ -33240,47 +33283,47 @@
       <c r="U1" s="5"/>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <f t="array" ref="C2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
+        <v>8</v>
+      </c>
+      <c r="D2" s="12">
+        <f t="array" ref="D2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z42, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
+        <v>8</v>
+      </c>
+      <c r="E2" s="12">
+        <f t="array" ref="E2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
+        <v>8</v>
+      </c>
+      <c r="F2" s="12">
+        <f t="array" ref="F2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <f t="array" ref="D2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z42, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>7</v>
-      </c>
-      <c r="E2" s="11">
-        <f t="array" ref="E2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>7</v>
-      </c>
-      <c r="F2" s="11">
-        <f t="array" ref="F2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
+      <c r="G2" s="12">
+        <f t="array" ref="G2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
+        <v>8</v>
+      </c>
+      <c r="H2" s="12">
+        <f t="array" ref="H2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
+        <v>8</v>
+      </c>
+      <c r="I2" s="12">
+        <f t="array" ref="I2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>6</v>
       </c>
-      <c r="G2" s="11">
-        <f t="array" ref="G2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>7</v>
-      </c>
-      <c r="H2" s="11">
-        <f t="array" ref="H2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>7</v>
-      </c>
-      <c r="I2" s="11">
-        <f t="array" ref="I2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="J2" s="11">
+      <c r="J2" s="12">
         <f t="array" ref="J2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>7</v>
-      </c>
-      <c r="K2" s="11">
+        <v>8</v>
+      </c>
+      <c r="K2" s="12">
         <f t="array" ref="K2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -33294,43 +33337,43 @@
       <c r="U2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="25"/>
+      <c r="A3" s="26"/>
       <c r="B3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="27">
         <f>C2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="27">
         <f>D2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="27">
         <f>E2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="27">
         <f>F2/MatchesDB!$B$1</f>
-        <v>0.8571428571</v>
-      </c>
-      <c r="G3" s="26">
+        <v>0.875</v>
+      </c>
+      <c r="G3" s="27">
         <f>G2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="H3" s="26">
+      <c r="H3" s="27">
         <f>H2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="27">
         <f>I2/(MatchesDB!$B$1-4)</f>
-        <v>1.666666667</v>
-      </c>
-      <c r="J3" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="J3" s="27">
         <f>J2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="27">
         <f>K2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
@@ -33346,47 +33389,47 @@
       <c r="U3" s="5"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="28">
         <f t="array" ref="C4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="D4" s="27">
+        <v>6</v>
+      </c>
+      <c r="D4" s="28">
         <f t="array" ref="D4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>7</v>
-      </c>
-      <c r="E4" s="27">
+        <v>8</v>
+      </c>
+      <c r="E4" s="28">
         <f t="array" ref="E4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>4</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="28">
         <f t="array" ref="F4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="G4" s="27">
+        <v>6</v>
+      </c>
+      <c r="G4" s="28">
         <f t="array" ref="G4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
+        <v>7</v>
+      </c>
+      <c r="H4" s="28">
+        <f t="array" ref="H4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
+        <v>8</v>
+      </c>
+      <c r="I4" s="28">
+        <f t="array" ref="I4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>6</v>
       </c>
-      <c r="H4" s="27">
-        <f t="array" ref="H4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
+      <c r="J4" s="28">
+        <f t="array" ref="J4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>7</v>
       </c>
-      <c r="I4" s="27">
-        <f t="array" ref="I4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="J4" s="27">
-        <f t="array" ref="J4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>6</v>
-      </c>
-      <c r="K4" s="27">
+      <c r="K4" s="28">
         <f t="array" ref="K4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
@@ -33400,43 +33443,43 @@
       <c r="U4" s="5"/>
     </row>
     <row r="5">
-      <c r="A5" s="25"/>
+      <c r="A5" s="26"/>
       <c r="B5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <f t="shared" ref="C5:K5" si="1">C4/C2</f>
-        <v>0.7142857143</v>
-      </c>
-      <c r="D5" s="26">
+        <v>0.75</v>
+      </c>
+      <c r="D5" s="27">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <f t="shared" si="1"/>
-        <v>0.5714285714</v>
-      </c>
-      <c r="F5" s="26">
-        <f t="shared" si="1"/>
-        <v>0.8333333333</v>
-      </c>
-      <c r="G5" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="27">
         <f t="shared" si="1"/>
         <v>0.8571428571</v>
       </c>
-      <c r="H5" s="26">
+      <c r="G5" s="27">
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+      <c r="H5" s="27">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="27">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J5" s="26">
+      <c r="J5" s="27">
         <f t="shared" si="1"/>
-        <v>0.8571428571</v>
-      </c>
-      <c r="K5" s="26">
+        <v>0.875</v>
+      </c>
+      <c r="K5" s="27">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -33452,45 +33495,45 @@
       <c r="U5" s="5"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
-        <v>73</v>
+      <c r="A6" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="12">
         <f t="array" ref="C6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>1</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="12">
         <f t="array" ref="D6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>10</v>
-      </c>
-      <c r="E6" s="11">
+        <v>12</v>
+      </c>
+      <c r="E6" s="12">
         <f t="array" ref="E6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
+        <v>6</v>
+      </c>
+      <c r="F6" s="12">
+        <f t="array" ref="F6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
+        <v>2</v>
+      </c>
+      <c r="G6" s="12">
+        <f t="array" ref="G6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
+        <v>21</v>
+      </c>
+      <c r="H6" s="12">
+        <f t="array" ref="H6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>4</v>
       </c>
-      <c r="F6" s="11">
-        <f t="array" ref="F6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
+      <c r="I6" s="12">
+        <f t="array" ref="I6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>1</v>
       </c>
-      <c r="G6" s="11">
-        <f t="array" ref="G6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>17</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="array" ref="H6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>3</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="array" ref="I6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="11">
+      <c r="J6" s="12">
         <f t="array" ref="J6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>5</v>
-      </c>
-      <c r="K6" s="11">
+        <v>11</v>
+      </c>
+      <c r="K6" s="12">
         <f t="array" ref="K6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>5</v>
       </c>
@@ -33506,45 +33549,45 @@
       <c r="U6" s="5"/>
     </row>
     <row r="7">
-      <c r="A7" s="25"/>
+      <c r="A7" s="26"/>
       <c r="B7" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="30">
+        <v>78</v>
+      </c>
+      <c r="C7" s="32">
         <f t="shared" ref="C7:K7" si="2">C6/C2</f>
-        <v>0.1428571429</v>
-      </c>
-      <c r="D7" s="30">
+        <v>0.125</v>
+      </c>
+      <c r="D7" s="32">
         <f t="shared" si="2"/>
-        <v>1.428571429</v>
-      </c>
-      <c r="E7" s="30">
+        <v>1.5</v>
+      </c>
+      <c r="E7" s="32">
         <f t="shared" si="2"/>
-        <v>0.5714285714</v>
-      </c>
-      <c r="F7" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="F7" s="32">
+        <f t="shared" si="2"/>
+        <v>0.2857142857</v>
+      </c>
+      <c r="G7" s="32">
+        <f t="shared" si="2"/>
+        <v>2.625</v>
+      </c>
+      <c r="H7" s="32">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="I7" s="32">
         <f t="shared" si="2"/>
         <v>0.1666666667</v>
       </c>
-      <c r="G7" s="30">
+      <c r="J7" s="32">
         <f t="shared" si="2"/>
-        <v>2.428571429</v>
-      </c>
-      <c r="H7" s="30">
+        <v>1.375</v>
+      </c>
+      <c r="K7" s="32">
         <f t="shared" si="2"/>
-        <v>0.4285714286</v>
-      </c>
-      <c r="I7" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="30">
-        <f t="shared" si="2"/>
-        <v>0.7142857143</v>
-      </c>
-      <c r="K7" s="30">
-        <f t="shared" si="2"/>
-        <v>0.7142857143</v>
+        <v>0.625</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
@@ -33558,47 +33601,47 @@
       <c r="U7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="s">
-        <v>75</v>
+      <c r="A8" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <f t="array" ref="C8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>5</v>
-      </c>
-      <c r="D8" s="27">
+        <v>8</v>
+      </c>
+      <c r="D8" s="28">
         <f t="array" ref="D8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>7</v>
-      </c>
-      <c r="E8" s="27">
+        <v>10</v>
+      </c>
+      <c r="E8" s="28">
         <f t="array" ref="E8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>1</v>
-      </c>
-      <c r="F8" s="27">
+        <v>2</v>
+      </c>
+      <c r="F8" s="28">
         <f t="array" ref="F8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>2</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="28">
         <f t="array" ref="G8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>3</v>
-      </c>
-      <c r="H8" s="27">
+        <v>4</v>
+      </c>
+      <c r="H8" s="28">
         <f t="array" ref="H8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>2</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="28">
         <f t="array" ref="I8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>0</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="28">
         <f t="array" ref="J8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
+        <v>5</v>
+      </c>
+      <c r="K8" s="28">
+        <f t="array" ref="K8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>4</v>
-      </c>
-      <c r="K8" s="27">
-        <f t="array" ref="K8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
-        <v>3</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
@@ -33612,45 +33655,45 @@
       <c r="U8" s="5"/>
     </row>
     <row r="9">
-      <c r="A9" s="25"/>
+      <c r="A9" s="26"/>
       <c r="B9" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="30">
+        <v>78</v>
+      </c>
+      <c r="C9" s="32">
         <f t="shared" ref="C9:K9" si="3">C8/C2</f>
-        <v>0.7142857143</v>
-      </c>
-      <c r="D9" s="30">
+        <v>1</v>
+      </c>
+      <c r="D9" s="32">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="E9" s="30">
+        <v>1.25</v>
+      </c>
+      <c r="E9" s="32">
         <f t="shared" si="3"/>
-        <v>0.1428571429</v>
-      </c>
-      <c r="F9" s="30">
-        <f t="shared" si="3"/>
-        <v>0.3333333333</v>
-      </c>
-      <c r="G9" s="30">
-        <f t="shared" si="3"/>
-        <v>0.4285714286</v>
-      </c>
-      <c r="H9" s="30">
+        <v>0.25</v>
+      </c>
+      <c r="F9" s="32">
         <f t="shared" si="3"/>
         <v>0.2857142857</v>
       </c>
-      <c r="I9" s="30">
+      <c r="G9" s="32">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="32">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="I9" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="32">
         <f t="shared" si="3"/>
-        <v>0.5714285714</v>
-      </c>
-      <c r="K9" s="30">
+        <v>0.625</v>
+      </c>
+      <c r="K9" s="32">
         <f t="shared" si="3"/>
-        <v>0.4285714286</v>
+        <v>0.5</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -33664,47 +33707,47 @@
       <c r="U9" s="5"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="s">
-        <v>76</v>
+      <c r="A10" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="12">
         <f t="shared" ref="C10:K10" si="4">C6+C8</f>
+        <v>9</v>
+      </c>
+      <c r="D10" s="12">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="E10" s="12">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="F10" s="12">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="G10" s="12">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="H10" s="12">
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="D10" s="11">
+      <c r="I10" s="12">
         <f t="shared" si="4"/>
-        <v>17</v>
-      </c>
-      <c r="E10" s="11">
+        <v>1</v>
+      </c>
+      <c r="J10" s="12">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="F10" s="11">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="G10" s="11">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="H10" s="11">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="I10" s="11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="11">
+        <v>16</v>
+      </c>
+      <c r="K10" s="12">
         <f t="shared" si="4"/>
         <v>9</v>
-      </c>
-      <c r="K10" s="11">
-        <f t="shared" si="4"/>
-        <v>8</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
@@ -33718,45 +33761,45 @@
       <c r="U10" s="5"/>
     </row>
     <row r="11">
-      <c r="A11" s="25"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="30">
+        <v>78</v>
+      </c>
+      <c r="C11" s="32">
         <f t="shared" ref="C11:K11" si="5">C10/C2</f>
-        <v>0.8571428571</v>
-      </c>
-      <c r="D11" s="30">
+        <v>1.125</v>
+      </c>
+      <c r="D11" s="32">
         <f t="shared" si="5"/>
-        <v>2.428571429</v>
-      </c>
-      <c r="E11" s="30">
+        <v>2.75</v>
+      </c>
+      <c r="E11" s="32">
         <f t="shared" si="5"/>
-        <v>0.7142857143</v>
-      </c>
-      <c r="F11" s="30">
+        <v>1</v>
+      </c>
+      <c r="F11" s="32">
         <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="G11" s="30">
+        <v>0.5714285714</v>
+      </c>
+      <c r="G11" s="32">
         <f t="shared" si="5"/>
-        <v>2.857142857</v>
-      </c>
-      <c r="H11" s="30">
+        <v>3.125</v>
+      </c>
+      <c r="H11" s="32">
         <f t="shared" si="5"/>
-        <v>0.7142857143</v>
-      </c>
-      <c r="I11" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="I11" s="32">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="30">
+        <v>0.1666666667</v>
+      </c>
+      <c r="J11" s="32">
         <f t="shared" si="5"/>
-        <v>1.285714286</v>
-      </c>
-      <c r="K11" s="30">
+        <v>2</v>
+      </c>
+      <c r="K11" s="32">
         <f t="shared" si="5"/>
-        <v>1.142857143</v>
+        <v>1.125</v>
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>

--- a/JO12-1/JO12-1_matchesDB.xlsx
+++ b/JO12-1/JO12-1_matchesDB.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="97">
   <si>
     <t>Matches</t>
   </si>
@@ -151,10 +151,10 @@
     <t>%</t>
   </si>
   <si>
-    <t>SDO JO 12-1</t>
+    <t>1st lineup</t>
   </si>
   <si>
-    <t>1st lineup</t>
+    <t>SDO JO 12-1</t>
   </si>
   <si>
     <t>1,1,0,1</t>
@@ -228,6 +228,9 @@
     <t>Sporting Martinus O12-2</t>
   </si>
   <si>
+    <t>Scorers</t>
+  </si>
+  <si>
     <t>1,1,3,1</t>
   </si>
   <si>
@@ -252,13 +255,46 @@
     <t>1,1,6,1</t>
   </si>
   <si>
-    <t>Scorers</t>
+    <t>HK-A3</t>
+  </si>
+  <si>
+    <t>WV-HEDW O12-1</t>
+  </si>
+  <si>
+    <t>Sportpark Middenmeer, Amsterdam</t>
+  </si>
+  <si>
+    <t>DSS O12-2JM</t>
+  </si>
+  <si>
+    <t>NVC O12-1</t>
+  </si>
+  <si>
+    <t>Sportpark Naarden, Naarden</t>
+  </si>
+  <si>
+    <t>FC Weesp O12-1</t>
   </si>
   <si>
     <t>Average</t>
   </si>
   <si>
+    <t>Abcoude FC O12-1</t>
+  </si>
+  <si>
+    <t>Ruwelspad 1 Abcoude</t>
+  </si>
+  <si>
     <t>Assists</t>
+  </si>
+  <si>
+    <t>Ouderkerk sv. O12-1</t>
+  </si>
+  <si>
+    <t>Diemen sv. O12-2</t>
+  </si>
+  <si>
+    <t>Sportlaan 13 Diemen</t>
   </si>
   <si>
     <t>Goal contribution</t>
@@ -379,6 +415,17 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -386,17 +433,6 @@
         <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
@@ -490,8 +526,8 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
@@ -798,7 +834,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7">
@@ -1289,7 +1325,7 @@
     </row>
     <row r="12">
       <c r="A12" s="20">
-        <f t="shared" ref="A12:A40" si="2">IF(ISBLANK(B12),"",A11+1)</f>
+        <f t="shared" ref="A12:A18" si="2">IF(ISBLANK(B12),"",A11+1)</f>
         <v>2</v>
       </c>
       <c r="B12" s="21">
@@ -1390,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H13" s="21" t="s">
         <v>34</v>
@@ -1733,7 +1769,7 @@
         <v>47</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P17" s="18" t="s">
         <v>61</v>
@@ -1742,7 +1778,7 @@
         <v>46</v>
       </c>
       <c r="R17" s="18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S17" s="18" t="s">
         <v>62</v>
@@ -1757,7 +1793,7 @@
         <v>62</v>
       </c>
       <c r="W17" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X17" s="18" t="s">
         <v>41</v>
@@ -1786,7 +1822,7 @@
       </c>
       <c r="F18" s="21"/>
       <c r="G18" s="21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H18" s="21"/>
       <c r="I18" s="21" t="s">
@@ -1807,13 +1843,13 @@
         <v>9</v>
       </c>
       <c r="N18" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P18" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q18" s="18" t="s">
         <v>40</v>
@@ -1828,7 +1864,7 @@
         <v>40</v>
       </c>
       <c r="U18" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V18" s="18" t="s">
         <v>46</v>
@@ -1845,27 +1881,38 @@
       <c r="AD18" s="5"/>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
+      <c r="A19" s="20">
+        <v>9.0</v>
+      </c>
+      <c r="B19" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="22">
+        <v>46319.0</v>
+      </c>
+      <c r="E19" s="23">
+        <v>0.3541666666666667</v>
+      </c>
+      <c r="F19" s="21"/>
+      <c r="G19" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="H19" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="I19" s="21"/>
       <c r="J19" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K19" s="25" t="str">
+      <c r="K19" s="31" t="str">
         <f t="array" ref="K19">IF(L19&lt;&gt;"", SUMPRODUCT(MID(N19:Y19,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L19" s="29"/>
+      <c r="L19" s="30"/>
       <c r="M19" s="25" t="str">
         <f t="array" ref="M19">IF(L19&lt;&gt;"", SUMPRODUCT(LEFT(N19:Y19,1)*1), "")</f>
         <v/>
@@ -1885,27 +1932,36 @@
       <c r="AD19" s="5"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
+      <c r="A20" s="20">
+        <v>10.0</v>
+      </c>
+      <c r="B20" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="22">
+        <v>46326.0</v>
+      </c>
+      <c r="E20" s="23">
+        <v>0.375</v>
+      </c>
+      <c r="F20" s="21"/>
+      <c r="G20" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
       <c r="J20" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K20" s="25" t="str">
+      <c r="K20" s="31" t="str">
         <f t="array" ref="K20">IF(L20&lt;&gt;"", SUMPRODUCT(MID(N20:Y20,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L20" s="29"/>
+      <c r="L20" s="30"/>
       <c r="M20" s="25" t="str">
         <f t="array" ref="M20">IF(L20&lt;&gt;"", SUMPRODUCT(LEFT(N20:Y20,1)*1), "")</f>
         <v/>
@@ -1925,27 +1981,38 @@
       <c r="AD20" s="5"/>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
+      <c r="A21" s="20">
+        <v>11.0</v>
+      </c>
+      <c r="B21" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="22">
+        <v>46333.0</v>
+      </c>
+      <c r="E21" s="23">
+        <v>0.4895833333333333</v>
+      </c>
+      <c r="F21" s="21"/>
+      <c r="G21" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="H21" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="I21" s="21"/>
       <c r="J21" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K21" s="25" t="str">
+      <c r="K21" s="31" t="str">
         <f t="array" ref="K21">IF(L21&lt;&gt;"", SUMPRODUCT(MID(N21:Y21,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L21" s="29"/>
+      <c r="L21" s="30"/>
       <c r="M21" s="25" t="str">
         <f t="array" ref="M21">IF(L21&lt;&gt;"", SUMPRODUCT(LEFT(N21:Y21,1)*1), "")</f>
         <v/>
@@ -1965,27 +2032,36 @@
       <c r="AD21" s="5"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
+      <c r="A22" s="20">
+        <v>12.0</v>
+      </c>
+      <c r="B22" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="22">
+        <v>46340.0</v>
+      </c>
+      <c r="E22" s="23">
+        <v>0.375</v>
+      </c>
+      <c r="F22" s="21"/>
+      <c r="G22" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
       <c r="J22" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K22" s="25" t="str">
+      <c r="K22" s="31" t="str">
         <f t="array" ref="K22">IF(L22&lt;&gt;"", SUMPRODUCT(MID(N22:Y22,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L22" s="29"/>
+      <c r="L22" s="30"/>
       <c r="M22" s="25" t="str">
         <f t="array" ref="M22">IF(L22&lt;&gt;"", SUMPRODUCT(LEFT(N22:Y22,1)*1), "")</f>
         <v/>
@@ -2005,27 +2081,38 @@
       <c r="AD22" s="5"/>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
+      <c r="A23" s="20">
+        <v>13.0</v>
+      </c>
+      <c r="B23" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="22">
+        <v>46347.0</v>
+      </c>
+      <c r="E23" s="23">
+        <v>0.46875</v>
+      </c>
+      <c r="F23" s="21"/>
+      <c r="G23" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="H23" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="I23" s="21"/>
       <c r="J23" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K23" s="25" t="str">
+      <c r="K23" s="31" t="str">
         <f t="array" ref="K23">IF(L23&lt;&gt;"", SUMPRODUCT(MID(N23:Y23,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L23" s="29"/>
+      <c r="L23" s="30"/>
       <c r="M23" s="25" t="str">
         <f t="array" ref="M23">IF(L23&lt;&gt;"", SUMPRODUCT(LEFT(N23:Y23,1)*1), "")</f>
         <v/>
@@ -2045,27 +2132,36 @@
       <c r="AD23" s="5"/>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+      <c r="A24" s="20">
+        <v>14.0</v>
+      </c>
+      <c r="B24" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="22">
+        <v>46354.0</v>
+      </c>
+      <c r="E24" s="23">
+        <v>0.375</v>
+      </c>
+      <c r="F24" s="21"/>
+      <c r="G24" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
       <c r="J24" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K24" s="25" t="str">
+      <c r="K24" s="31" t="str">
         <f t="array" ref="K24">IF(L24&lt;&gt;"", SUMPRODUCT(MID(N24:Y24,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L24" s="29"/>
+      <c r="L24" s="30"/>
       <c r="M24" s="25" t="str">
         <f t="array" ref="M24">IF(L24&lt;&gt;"", SUMPRODUCT(LEFT(N24:Y24,1)*1), "")</f>
         <v/>
@@ -2085,27 +2181,38 @@
       <c r="AD24" s="5"/>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+      <c r="A25" s="20">
+        <v>15.0</v>
+      </c>
+      <c r="B25" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="22">
+        <v>46361.0</v>
+      </c>
+      <c r="E25" s="23">
+        <v>0.40625</v>
+      </c>
+      <c r="F25" s="21"/>
+      <c r="G25" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="H25" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="I25" s="21"/>
       <c r="J25" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K25" s="25" t="str">
+      <c r="K25" s="31" t="str">
         <f t="array" ref="K25">IF(L25&lt;&gt;"", SUMPRODUCT(MID(N25:Y25,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L25" s="29"/>
+      <c r="L25" s="30"/>
       <c r="M25" s="25" t="str">
         <f t="array" ref="M25">IF(L25&lt;&gt;"", SUMPRODUCT(LEFT(N25:Y25,1)*1), "")</f>
         <v/>
@@ -2126,7 +2233,7 @@
     </row>
     <row r="26">
       <c r="A26" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A26:A40" si="3">IF(ISBLANK(B26),"",A25+1)</f>
         <v/>
       </c>
       <c r="B26" s="1"/>
@@ -2166,7 +2273,7 @@
     </row>
     <row r="27">
       <c r="A27" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B27" s="1"/>
@@ -2206,7 +2313,7 @@
     </row>
     <row r="28">
       <c r="A28" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B28" s="1"/>
@@ -2246,7 +2353,7 @@
     </row>
     <row r="29">
       <c r="A29" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B29" s="1"/>
@@ -2286,7 +2393,7 @@
     </row>
     <row r="30">
       <c r="A30" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B30" s="1"/>
@@ -2326,7 +2433,7 @@
     </row>
     <row r="31">
       <c r="A31" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B31" s="1"/>
@@ -2366,7 +2473,7 @@
     </row>
     <row r="32">
       <c r="A32" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B32" s="1"/>
@@ -2406,7 +2513,7 @@
     </row>
     <row r="33">
       <c r="A33" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B33" s="1"/>
@@ -2446,7 +2553,7 @@
     </row>
     <row r="34">
       <c r="A34" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B34" s="1"/>
@@ -2486,7 +2593,7 @@
     </row>
     <row r="35">
       <c r="A35" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B35" s="1"/>
@@ -2526,7 +2633,7 @@
     </row>
     <row r="36">
       <c r="A36" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B36" s="1"/>
@@ -2566,7 +2673,7 @@
     </row>
     <row r="37">
       <c r="A37" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B37" s="1"/>
@@ -2606,7 +2713,7 @@
     </row>
     <row r="38">
       <c r="A38" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B38" s="1"/>
@@ -2646,7 +2753,7 @@
     </row>
     <row r="39">
       <c r="A39" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B39" s="1"/>
@@ -2686,7 +2793,7 @@
     </row>
     <row r="40">
       <c r="A40" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B40" s="1"/>
@@ -2859,7 +2966,7 @@
         <v>33</v>
       </c>
       <c r="N44" s="18" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="O44" s="5"/>
       <c r="T44" s="5"/>
@@ -2876,7 +2983,7 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B45" s="11">
         <v>1.0</v>
@@ -2916,7 +3023,7 @@
       </c>
       <c r="N45" s="5"/>
       <c r="O45" s="34">
-        <f t="shared" ref="O45:O48" si="3">SUM(A45:N45)</f>
+        <f t="shared" ref="O45:O48" si="4">SUM(A45:N45)</f>
         <v>9</v>
       </c>
       <c r="T45" s="5"/>
@@ -2933,7 +3040,7 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" s="11">
         <v>1.0</v>
@@ -2973,7 +3080,7 @@
       </c>
       <c r="N46" s="5"/>
       <c r="O46" s="34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="T46" s="5"/>
@@ -2990,7 +3097,7 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B47" s="11">
         <v>0.0</v>
@@ -3030,7 +3137,7 @@
       </c>
       <c r="N47" s="5"/>
       <c r="O47" s="34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="T47" s="5"/>
@@ -3047,7 +3154,7 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B48" s="11">
         <v>3.0</v>
@@ -3087,7 +3194,7 @@
       </c>
       <c r="N48" s="5"/>
       <c r="O48" s="34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="T48" s="5"/>
@@ -3105,55 +3212,55 @@
     <row r="49">
       <c r="A49" s="5"/>
       <c r="B49" s="5" t="str">
-        <f t="shared" ref="B49:N49" si="4">B45&amp;","&amp;B46&amp;","&amp;B47&amp;","&amp;B48</f>
+        <f t="shared" ref="B49:N49" si="5">B45&amp;","&amp;B46&amp;","&amp;B47&amp;","&amp;B48</f>
         <v>1,1,0,3</v>
       </c>
       <c r="C49" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1,1,2,3</v>
       </c>
       <c r="D49" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1,0,2,1</v>
       </c>
       <c r="E49" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1,1,1,0</v>
       </c>
       <c r="F49" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1,1,4,1</v>
       </c>
       <c r="G49" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1,1,1,0</v>
       </c>
       <c r="H49" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1,1,1,0</v>
       </c>
       <c r="I49" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1,1,6,1</v>
       </c>
       <c r="J49" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1,1,0,1</v>
       </c>
       <c r="K49" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0,0,0,0</v>
       </c>
       <c r="L49" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0,0,0,0</v>
       </c>
       <c r="M49" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0,0,0,0</v>
       </c>
       <c r="N49" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>,,,</v>
       </c>
       <c r="O49" s="5"/>
@@ -33243,7 +33350,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="3"/>
+      <c r="B1" s="2"/>
       <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
@@ -33390,7 +33497,7 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>11</v>
@@ -33496,7 +33603,7 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>11</v>
@@ -33551,7 +33658,7 @@
     <row r="7">
       <c r="A7" s="26"/>
       <c r="B7" s="4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C7" s="32">
         <f t="shared" ref="C7:K7" si="2">C6/C2</f>
@@ -33602,7 +33709,7 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>11</v>
@@ -33657,7 +33764,7 @@
     <row r="9">
       <c r="A9" s="26"/>
       <c r="B9" s="4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C9" s="32">
         <f t="shared" ref="C9:K9" si="3">C8/C2</f>
@@ -33708,7 +33815,7 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>11</v>
@@ -33763,7 +33870,7 @@
     <row r="11">
       <c r="A11" s="26"/>
       <c r="B11" s="4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C11" s="32">
         <f t="shared" ref="C11:K11" si="5">C10/C2</f>

--- a/JO12-1/JO12-1_matchesDB.xlsx
+++ b/JO12-1/JO12-1_matchesDB.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="97">
   <si>
     <t>Matches</t>
   </si>
@@ -148,12 +148,6 @@
     <t>KFC</t>
   </si>
   <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>1st lineup</t>
-  </si>
-  <si>
     <t>SDO JO 12-1</t>
   </si>
   <si>
@@ -170,6 +164,12 @@
   </si>
   <si>
     <t>Gustav Mahlerlaan 2009, 1081 LB Amsterdam</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>1st lineup</t>
   </si>
   <si>
     <t>1,1,1,3</t>
@@ -228,9 +228,6 @@
     <t>Sporting Martinus O12-2</t>
   </si>
   <si>
-    <t>Scorers</t>
-  </si>
-  <si>
     <t>1,1,3,1</t>
   </si>
   <si>
@@ -273,19 +270,16 @@
     <t>Sportpark Naarden, Naarden</t>
   </si>
   <si>
-    <t>FC Weesp O12-1</t>
+    <t>Scorers</t>
   </si>
   <si>
-    <t>Average</t>
+    <t>FC Weesp O12-1</t>
   </si>
   <si>
     <t>Abcoude FC O12-1</t>
   </si>
   <si>
     <t>Ruwelspad 1 Abcoude</t>
-  </si>
-  <si>
-    <t>Assists</t>
   </si>
   <si>
     <t>Ouderkerk sv. O12-1</t>
@@ -295,6 +289,12 @@
   </si>
   <si>
     <t>Sportlaan 13 Diemen</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Assists</t>
   </si>
   <si>
     <t>Goal contribution</t>
@@ -415,10 +415,13 @@
       </bottom>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <top style="thin">
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
@@ -426,13 +429,10 @@
       </bottom>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
+      <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
@@ -526,8 +526,8 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
@@ -548,12 +548,12 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
-    </xf>
     <xf borderId="8" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="9" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -588,11 +588,11 @@
     <xf borderId="1" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -834,7 +834,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7">
@@ -1095,10 +1095,10 @@
       <c r="AD7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="13">
         <f>SUM(L11:L40)</f>
         <v>18</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H13" s="21" t="s">
         <v>34</v>
@@ -1453,7 +1453,7 @@
         <v>39</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P13" s="18" t="s">
         <v>39</v>
@@ -1462,7 +1462,7 @@
         <v>39</v>
       </c>
       <c r="R13" s="18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S13" s="18" t="s">
         <v>39</v>
@@ -1496,7 +1496,7 @@
         <v>1.0</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D14" s="22">
         <v>46270.0</v>
@@ -1506,10 +1506,10 @@
       </c>
       <c r="F14" s="21"/>
       <c r="G14" s="21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I14" s="21" t="s">
         <v>37</v>
@@ -1522,7 +1522,7 @@
         <f t="array" ref="K14">IF(L14&lt;&gt;"", SUMPRODUCT(MID(N14:Y14,5,1)*1), "")</f>
         <v>12</v>
       </c>
-      <c r="L14" s="29">
+      <c r="L14" s="28">
         <v>5.0</v>
       </c>
       <c r="M14" s="25">
@@ -1576,7 +1576,7 @@
         <v>1.0</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D15" s="22">
         <v>46277.0</v>
@@ -1600,7 +1600,7 @@
         <f t="array" ref="K15">IF(L15&lt;&gt;"", SUMPRODUCT(MID(N15:Y15,5,1)*1), "")</f>
         <v>14</v>
       </c>
-      <c r="L15" s="29">
+      <c r="L15" s="28">
         <v>3.0</v>
       </c>
       <c r="M15" s="25">
@@ -1654,7 +1654,7 @@
         <v>1.0</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D16" s="22">
         <v>46284.0</v>
@@ -1688,7 +1688,7 @@
         <v>10</v>
       </c>
       <c r="N16" s="18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O16" s="18" t="s">
         <v>62</v>
@@ -1703,13 +1703,13 @@
         <v>65</v>
       </c>
       <c r="S16" s="18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="T16" s="18" t="s">
         <v>39</v>
       </c>
       <c r="U16" s="18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="V16" s="18" t="s">
         <v>60</v>
@@ -1734,7 +1734,7 @@
         <v>1.0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D17" s="22">
         <v>46291.0</v>
@@ -1766,19 +1766,19 @@
         <v>10</v>
       </c>
       <c r="N17" s="18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P17" s="18" t="s">
         <v>61</v>
       </c>
       <c r="Q17" s="18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="R17" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S17" s="18" t="s">
         <v>62</v>
@@ -1793,7 +1793,7 @@
         <v>62</v>
       </c>
       <c r="W17" s="18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="X17" s="18" t="s">
         <v>41</v>
@@ -1812,7 +1812,7 @@
         <v>1.0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D18" s="22">
         <v>46298.0</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="F18" s="21"/>
       <c r="G18" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H18" s="21"/>
       <c r="I18" s="21" t="s">
@@ -1843,13 +1843,13 @@
         <v>9</v>
       </c>
       <c r="N18" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="O18" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="O18" s="18" t="s">
+      <c r="P18" s="18" t="s">
         <v>75</v>
-      </c>
-      <c r="P18" s="18" t="s">
-        <v>76</v>
       </c>
       <c r="Q18" s="18" t="s">
         <v>40</v>
@@ -1864,10 +1864,10 @@
         <v>40</v>
       </c>
       <c r="U18" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V18" s="18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="W18" s="18" t="s">
         <v>41</v>
@@ -1888,7 +1888,7 @@
         <v>2.0</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D19" s="22">
         <v>46319.0</v>
@@ -1898,12 +1898,14 @@
       </c>
       <c r="F19" s="21"/>
       <c r="G19" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="H19" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="H19" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="I19" s="21"/>
+      <c r="I19" s="30" t="s">
+        <v>37</v>
+      </c>
       <c r="J19" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1939,7 +1941,7 @@
         <v>2.0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D20" s="22">
         <v>46326.0</v>
@@ -1949,10 +1951,12 @@
       </c>
       <c r="F20" s="21"/>
       <c r="G20" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
+      <c r="I20" s="21" t="s">
+        <v>56</v>
+      </c>
       <c r="J20" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1988,7 +1992,7 @@
         <v>2.0</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D21" s="22">
         <v>46333.0</v>
@@ -1998,12 +2002,14 @@
       </c>
       <c r="F21" s="21"/>
       <c r="G21" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="H21" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="I21" s="21"/>
+      <c r="I21" s="30" t="s">
+        <v>37</v>
+      </c>
       <c r="J21" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2039,7 +2045,7 @@
         <v>2.0</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D22" s="22">
         <v>46340.0</v>
@@ -2052,7 +2058,9 @@
         <v>84</v>
       </c>
       <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
+      <c r="I22" s="21" t="s">
+        <v>56</v>
+      </c>
       <c r="J22" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2088,7 +2096,7 @@
         <v>2.0</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D23" s="22">
         <v>46347.0</v>
@@ -2098,12 +2106,14 @@
       </c>
       <c r="F23" s="21"/>
       <c r="G23" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="H23" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="H23" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="I23" s="21"/>
+      <c r="I23" s="30" t="s">
+        <v>37</v>
+      </c>
       <c r="J23" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2139,7 +2149,7 @@
         <v>2.0</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D24" s="22">
         <v>46354.0</v>
@@ -2149,10 +2159,12 @@
       </c>
       <c r="F24" s="21"/>
       <c r="G24" s="30" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
+      <c r="I24" s="21" t="s">
+        <v>56</v>
+      </c>
       <c r="J24" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2188,7 +2200,7 @@
         <v>2.0</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D25" s="22">
         <v>46361.0</v>
@@ -2198,12 +2210,14 @@
       </c>
       <c r="F25" s="21"/>
       <c r="G25" s="30" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H25" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="I25" s="21"/>
+        <v>89</v>
+      </c>
+      <c r="I25" s="30" t="s">
+        <v>37</v>
+      </c>
       <c r="J25" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2252,7 +2266,7 @@
         <f t="array" ref="K26">IF(L26&lt;&gt;"", SUMPRODUCT(MID(N26:Y26,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L26" s="29"/>
+      <c r="L26" s="28"/>
       <c r="M26" s="25" t="str">
         <f t="array" ref="M26">IF(L26&lt;&gt;"", SUMPRODUCT(LEFT(N26:Y26,1)*1), "")</f>
         <v/>
@@ -2652,7 +2666,7 @@
         <f t="array" ref="K36">IF(L36&lt;&gt;"", SUMPRODUCT(MID(N36:Y36,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L36" s="29"/>
+      <c r="L36" s="28"/>
       <c r="M36" s="25" t="str">
         <f t="array" ref="M36">IF(L36&lt;&gt;"", SUMPRODUCT(LEFT(N36:Y36,1)*1), "")</f>
         <v/>
@@ -3040,7 +3054,7 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B46" s="11">
         <v>1.0</v>
@@ -33350,7 +33364,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
+      <c r="B1" s="3"/>
       <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
@@ -33396,39 +33410,39 @@
       <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="14">
         <f t="array" ref="C2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="14">
         <f t="array" ref="D2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z42, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="14">
         <f t="array" ref="E2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="14">
         <f t="array" ref="F2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>7</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="14">
         <f t="array" ref="G2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="14">
         <f t="array" ref="H2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="14">
         <f t="array" ref="I2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>6</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="14">
         <f t="array" ref="J2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="14">
         <f t="array" ref="K2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
@@ -33446,7 +33460,7 @@
     <row r="3">
       <c r="A3" s="26"/>
       <c r="B3" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C3" s="27">
         <f>C2/MatchesDB!$B$1</f>
@@ -33497,44 +33511,44 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="29">
         <f t="array" ref="C4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>6</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="29">
         <f t="array" ref="D4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="29">
         <f t="array" ref="E4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>4</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="29">
         <f t="array" ref="F4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>6</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="29">
         <f t="array" ref="G4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>7</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="29">
         <f t="array" ref="H4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="29">
         <f t="array" ref="I4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>6</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="29">
         <f t="array" ref="J4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>7</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="29">
         <f t="array" ref="K4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
@@ -33552,7 +33566,7 @@
     <row r="5">
       <c r="A5" s="26"/>
       <c r="B5" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C5" s="27">
         <f t="shared" ref="C5:K5" si="1">C4/C2</f>
@@ -33603,44 +33617,44 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="14">
         <f t="array" ref="C6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>1</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="14">
         <f t="array" ref="D6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>12</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="14">
         <f t="array" ref="E6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>6</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="14">
         <f t="array" ref="F6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>2</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="14">
         <f t="array" ref="G6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>21</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="14">
         <f t="array" ref="H6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>4</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="14">
         <f t="array" ref="I6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>1</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="14">
         <f t="array" ref="J6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>11</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="14">
         <f t="array" ref="K6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>5</v>
       </c>
@@ -33658,7 +33672,7 @@
     <row r="7">
       <c r="A7" s="26"/>
       <c r="B7" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C7" s="32">
         <f t="shared" ref="C7:K7" si="2">C6/C2</f>
@@ -33709,44 +33723,44 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="29">
         <f t="array" ref="C8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>8</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <f t="array" ref="D8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>10</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <f t="array" ref="E8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>2</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <f t="array" ref="F8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>2</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="29">
         <f t="array" ref="G8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>4</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="29">
         <f t="array" ref="H8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>2</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="29">
         <f t="array" ref="I8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>0</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="29">
         <f t="array" ref="J8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>5</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="29">
         <f t="array" ref="K8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>4</v>
       </c>
@@ -33764,7 +33778,7 @@
     <row r="9">
       <c r="A9" s="26"/>
       <c r="B9" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C9" s="32">
         <f t="shared" ref="C9:K9" si="3">C8/C2</f>
@@ -33820,39 +33834,39 @@
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="14">
         <f t="shared" ref="C10:K10" si="4">C6+C8</f>
         <v>9</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="14">
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="14">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="14">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="14">
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="14">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="14">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="14">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="K10" s="12">
+      <c r="K10" s="14">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
@@ -33870,7 +33884,7 @@
     <row r="11">
       <c r="A11" s="26"/>
       <c r="B11" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C11" s="32">
         <f t="shared" ref="C11:K11" si="5">C10/C2</f>

--- a/JO12-1/JO12-1_matchesDB.xlsx
+++ b/JO12-1/JO12-1_matchesDB.xlsx
@@ -151,10 +151,16 @@
     <t>SDO JO 12-1</t>
   </si>
   <si>
+    <t>%</t>
+  </si>
+  <si>
     <t>1,1,0,1</t>
   </si>
   <si>
     <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1st lineup</t>
   </si>
   <si>
     <t>1e 21</t>
@@ -164,12 +170,6 @@
   </si>
   <si>
     <t>Gustav Mahlerlaan 2009, 1081 LB Amsterdam</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>1st lineup</t>
   </si>
   <si>
     <t>1,1,1,3</t>
@@ -258,7 +258,10 @@
     <t>WV-HEDW O12-1</t>
   </si>
   <si>
-    <t>Sportpark Middenmeer, Amsterdam</t>
+    <t>Sportpark Middenmeer, Radioweg 86, Amsterdam</t>
+  </si>
+  <si>
+    <t>Scorers</t>
   </si>
   <si>
     <t>DSS O12-2JM</t>
@@ -267,10 +270,7 @@
     <t>NVC O12-1</t>
   </si>
   <si>
-    <t>Sportpark Naarden, Naarden</t>
-  </si>
-  <si>
-    <t>Scorers</t>
+    <t>Sportpark Naarden, Amersfoortsestraatweg 14, Naarden</t>
   </si>
   <si>
     <t>FC Weesp O12-1</t>
@@ -279,22 +279,22 @@
     <t>Abcoude FC O12-1</t>
   </si>
   <si>
-    <t>Ruwelspad 1 Abcoude</t>
+    <t>Sportpark Hollandse Kade, Ruwelspad 1, Abcoude</t>
+  </si>
+  <si>
+    <t>Average</t>
   </si>
   <si>
     <t>Ouderkerk sv. O12-1</t>
   </si>
   <si>
+    <t>Assists</t>
+  </si>
+  <si>
     <t>Diemen sv. O12-2</t>
   </si>
   <si>
-    <t>Sportlaan 13 Diemen</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Assists</t>
+    <t>Sportpark Diemen, Sportlaan 13, Diemen</t>
   </si>
   <si>
     <t>Goal contribution</t>
@@ -545,15 +545,15 @@
     <xf borderId="7" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="8" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="9" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1029,7 +1029,7 @@
         <v>52</v>
       </c>
       <c r="C6" s="5"/>
-      <c r="D6" s="11"/>
+      <c r="D6" s="12"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -1095,10 +1095,10 @@
       <c r="AD7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="14">
         <f>SUM(L11:L40)</f>
         <v>18</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>39</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P13" s="18" t="s">
         <v>39</v>
@@ -1462,7 +1462,7 @@
         <v>39</v>
       </c>
       <c r="R13" s="18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S13" s="18" t="s">
         <v>39</v>
@@ -1496,7 +1496,7 @@
         <v>1.0</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D14" s="22">
         <v>46270.0</v>
@@ -1506,10 +1506,10 @@
       </c>
       <c r="F14" s="21"/>
       <c r="G14" s="21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I14" s="21" t="s">
         <v>37</v>
@@ -1576,7 +1576,7 @@
         <v>1.0</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D15" s="22">
         <v>46277.0</v>
@@ -1654,7 +1654,7 @@
         <v>1.0</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D16" s="22">
         <v>46284.0</v>
@@ -1688,7 +1688,7 @@
         <v>10</v>
       </c>
       <c r="N16" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O16" s="18" t="s">
         <v>62</v>
@@ -1703,13 +1703,13 @@
         <v>65</v>
       </c>
       <c r="S16" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T16" s="18" t="s">
         <v>39</v>
       </c>
       <c r="U16" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V16" s="18" t="s">
         <v>60</v>
@@ -1734,7 +1734,7 @@
         <v>1.0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D17" s="22">
         <v>46291.0</v>
@@ -1766,7 +1766,7 @@
         <v>10</v>
       </c>
       <c r="N17" s="18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O17" s="18" t="s">
         <v>69</v>
@@ -1775,7 +1775,7 @@
         <v>61</v>
       </c>
       <c r="Q17" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R17" s="18" t="s">
         <v>70</v>
@@ -1812,7 +1812,7 @@
         <v>1.0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D18" s="22">
         <v>46298.0</v>
@@ -1867,7 +1867,7 @@
         <v>76</v>
       </c>
       <c r="V18" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W18" s="18" t="s">
         <v>41</v>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="F20" s="21"/>
       <c r="G20" s="30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H20" s="21"/>
       <c r="I20" s="21" t="s">
@@ -2002,10 +2002,10 @@
       </c>
       <c r="F21" s="21"/>
       <c r="G21" s="30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H21" s="30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I21" s="30" t="s">
         <v>37</v>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="F24" s="21"/>
       <c r="G24" s="30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H24" s="21"/>
       <c r="I24" s="21" t="s">
@@ -2210,10 +2210,10 @@
       </c>
       <c r="F25" s="21"/>
       <c r="G25" s="30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H25" s="30" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I25" s="30" t="s">
         <v>37</v>
@@ -2999,40 +2999,40 @@
       <c r="A45" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B45" s="11">
+      <c r="B45" s="12">
         <v>1.0</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="12">
         <v>1.0</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="12">
         <v>1.0</v>
       </c>
-      <c r="E45" s="11">
+      <c r="E45" s="12">
         <v>1.0</v>
       </c>
-      <c r="F45" s="11">
+      <c r="F45" s="12">
         <v>1.0</v>
       </c>
-      <c r="G45" s="11">
+      <c r="G45" s="12">
         <v>1.0</v>
       </c>
-      <c r="H45" s="11">
+      <c r="H45" s="12">
         <v>1.0</v>
       </c>
-      <c r="I45" s="11">
+      <c r="I45" s="12">
         <v>1.0</v>
       </c>
-      <c r="J45" s="11">
+      <c r="J45" s="12">
         <v>1.0</v>
       </c>
-      <c r="K45" s="11">
+      <c r="K45" s="12">
         <v>0.0</v>
       </c>
-      <c r="L45" s="11">
+      <c r="L45" s="12">
         <v>0.0</v>
       </c>
-      <c r="M45" s="11">
+      <c r="M45" s="12">
         <v>0.0</v>
       </c>
       <c r="N45" s="5"/>
@@ -3054,42 +3054,42 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B46" s="11">
+        <v>47</v>
+      </c>
+      <c r="B46" s="12">
         <v>1.0</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C46" s="12">
         <v>1.0</v>
       </c>
-      <c r="D46" s="11">
+      <c r="D46" s="12">
         <v>0.0</v>
       </c>
-      <c r="E46" s="11">
+      <c r="E46" s="12">
         <v>1.0</v>
       </c>
-      <c r="F46" s="11">
+      <c r="F46" s="12">
         <v>1.0</v>
       </c>
-      <c r="G46" s="11">
+      <c r="G46" s="12">
         <v>1.0</v>
       </c>
-      <c r="H46" s="11">
+      <c r="H46" s="12">
         <v>1.0</v>
       </c>
-      <c r="I46" s="11">
+      <c r="I46" s="12">
         <v>1.0</v>
       </c>
-      <c r="J46" s="11">
+      <c r="J46" s="12">
         <v>1.0</v>
       </c>
-      <c r="K46" s="11">
+      <c r="K46" s="12">
         <v>0.0</v>
       </c>
-      <c r="L46" s="11">
+      <c r="L46" s="12">
         <v>0.0</v>
       </c>
-      <c r="M46" s="11">
+      <c r="M46" s="12">
         <v>0.0</v>
       </c>
       <c r="N46" s="5"/>
@@ -3113,40 +3113,40 @@
       <c r="A47" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="12">
         <v>0.0</v>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="12">
         <v>2.0</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="12">
         <v>2.0</v>
       </c>
-      <c r="E47" s="11">
+      <c r="E47" s="12">
         <v>1.0</v>
       </c>
-      <c r="F47" s="11">
+      <c r="F47" s="12">
         <v>4.0</v>
       </c>
-      <c r="G47" s="11">
+      <c r="G47" s="12">
         <v>1.0</v>
       </c>
-      <c r="H47" s="11">
+      <c r="H47" s="12">
         <v>1.0</v>
       </c>
-      <c r="I47" s="11">
+      <c r="I47" s="12">
         <v>6.0</v>
       </c>
-      <c r="J47" s="11">
+      <c r="J47" s="12">
         <v>0.0</v>
       </c>
-      <c r="K47" s="11">
+      <c r="K47" s="12">
         <v>0.0</v>
       </c>
-      <c r="L47" s="11">
+      <c r="L47" s="12">
         <v>0.0</v>
       </c>
-      <c r="M47" s="11">
+      <c r="M47" s="12">
         <v>0.0</v>
       </c>
       <c r="N47" s="5"/>
@@ -3170,40 +3170,40 @@
       <c r="A48" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B48" s="11">
+      <c r="B48" s="12">
         <v>3.0</v>
       </c>
-      <c r="C48" s="11">
+      <c r="C48" s="12">
         <v>3.0</v>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="12">
         <v>1.0</v>
       </c>
-      <c r="E48" s="11">
+      <c r="E48" s="12">
         <v>0.0</v>
       </c>
-      <c r="F48" s="11">
+      <c r="F48" s="12">
         <v>1.0</v>
       </c>
-      <c r="G48" s="11">
+      <c r="G48" s="12">
         <v>0.0</v>
       </c>
-      <c r="H48" s="11">
+      <c r="H48" s="12">
         <v>0.0</v>
       </c>
-      <c r="I48" s="11">
+      <c r="I48" s="12">
         <v>1.0</v>
       </c>
-      <c r="J48" s="11">
+      <c r="J48" s="12">
         <v>1.0</v>
       </c>
-      <c r="K48" s="11">
+      <c r="K48" s="12">
         <v>0.0</v>
       </c>
-      <c r="L48" s="11">
+      <c r="L48" s="12">
         <v>0.0</v>
       </c>
-      <c r="M48" s="11">
+      <c r="M48" s="12">
         <v>0.0</v>
       </c>
       <c r="N48" s="5"/>
@@ -33410,39 +33410,39 @@
       <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="11">
         <f t="array" ref="C2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="11">
         <f t="array" ref="D2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z42, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="11">
         <f t="array" ref="E2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="11">
         <f t="array" ref="F2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>7</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="11">
         <f t="array" ref="G2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="11">
         <f t="array" ref="H2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="11">
         <f t="array" ref="I2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>6</v>
       </c>
-      <c r="J2" s="14">
+      <c r="J2" s="11">
         <f t="array" ref="J2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
-      <c r="K2" s="14">
+      <c r="K2" s="11">
         <f t="array" ref="K2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
@@ -33460,7 +33460,7 @@
     <row r="3">
       <c r="A3" s="26"/>
       <c r="B3" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C3" s="27">
         <f>C2/MatchesDB!$B$1</f>
@@ -33511,7 +33511,7 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>11</v>
@@ -33566,7 +33566,7 @@
     <row r="5">
       <c r="A5" s="26"/>
       <c r="B5" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C5" s="27">
         <f t="shared" ref="C5:K5" si="1">C4/C2</f>
@@ -33617,44 +33617,44 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="11">
         <f t="array" ref="C6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>1</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="11">
         <f t="array" ref="D6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>12</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="11">
         <f t="array" ref="E6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>6</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="11">
         <f t="array" ref="F6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>2</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="11">
         <f t="array" ref="G6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>21</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="11">
         <f t="array" ref="H6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>4</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="11">
         <f t="array" ref="I6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>1</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="11">
         <f t="array" ref="J6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>11</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="11">
         <f t="array" ref="K6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>5</v>
       </c>
@@ -33672,7 +33672,7 @@
     <row r="7">
       <c r="A7" s="26"/>
       <c r="B7" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C7" s="32">
         <f t="shared" ref="C7:K7" si="2">C6/C2</f>
@@ -33723,7 +33723,7 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>11</v>
@@ -33778,7 +33778,7 @@
     <row r="9">
       <c r="A9" s="26"/>
       <c r="B9" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C9" s="32">
         <f t="shared" ref="C9:K9" si="3">C8/C2</f>
@@ -33834,39 +33834,39 @@
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="11">
         <f t="shared" ref="C10:K10" si="4">C6+C8</f>
         <v>9</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="11">
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="11">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="11">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="11">
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="11">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="11">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="11">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="11">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
@@ -33884,7 +33884,7 @@
     <row r="11">
       <c r="A11" s="26"/>
       <c r="B11" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C11" s="32">
         <f t="shared" ref="C11:K11" si="5">C10/C2</f>

--- a/JO12-1/JO12-1_matchesDB.xlsx
+++ b/JO12-1/JO12-1_matchesDB.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="97">
   <si>
     <t>Matches</t>
   </si>
@@ -133,6 +133,9 @@
     <t>A</t>
   </si>
   <si>
+    <t>%</t>
+  </si>
+  <si>
     <t>1,0,0,0</t>
   </si>
   <si>
@@ -145,22 +148,19 @@
     <t>0,0,0,0</t>
   </si>
   <si>
+    <t>1st lineup</t>
+  </si>
+  <si>
     <t>KFC</t>
   </si>
   <si>
     <t>SDO JO 12-1</t>
   </si>
   <si>
-    <t>%</t>
-  </si>
-  <si>
     <t>1,1,0,1</t>
   </si>
   <si>
     <t>1,0,1,0</t>
-  </si>
-  <si>
-    <t>1st lineup</t>
   </si>
   <si>
     <t>1e 21</t>
@@ -216,6 +216,9 @@
 1187ZT Amstelveen</t>
   </si>
   <si>
+    <t>Scorers</t>
+  </si>
+  <si>
     <t>1,1,3,0</t>
   </si>
   <si>
@@ -261,9 +264,6 @@
     <t>Sportpark Middenmeer, Radioweg 86, Amsterdam</t>
   </si>
   <si>
-    <t>Scorers</t>
-  </si>
-  <si>
     <t>DSS O12-2JM</t>
   </si>
   <si>
@@ -271,6 +271,12 @@
   </si>
   <si>
     <t>Sportpark Naarden, Amersfoortsestraatweg 14, Naarden</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Assists</t>
   </si>
   <si>
     <t>FC Weesp O12-1</t>
@@ -282,13 +288,7 @@
     <t>Sportpark Hollandse Kade, Ruwelspad 1, Abcoude</t>
   </si>
   <si>
-    <t>Average</t>
-  </si>
-  <si>
     <t>Ouderkerk sv. O12-1</t>
-  </si>
-  <si>
-    <t>Assists</t>
   </si>
   <si>
     <t>Diemen sv. O12-2</t>
@@ -327,12 +327,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -401,6 +401,20 @@
   <borders count="11">
     <border/>
     <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -408,20 +422,6 @@
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
@@ -525,14 +525,14 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="5" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -541,72 +541,72 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="6" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="7" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="8" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="9" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="16" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="16" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -834,12 +834,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7">
         <f>SUM(COUNTIF(J11:J40,"W"),COUNTIF(J11:J40,"D"),COUNTIF(J11:J40,"L"))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C1" s="5"/>
       <c r="D1" s="8">
@@ -915,7 +915,7 @@
       </c>
       <c r="B3" s="10">
         <f>COUNTIF(J11:J40,"L")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B6" s="10">
         <f>B7-B8</f>
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="12"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B7" s="10">
         <f>SUM(K11:K40)</f>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B8" s="14">
         <f>SUM(L11:L40)</f>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1249,7 +1249,7 @@
       <c r="B11" s="21">
         <v>1.0</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="22">
@@ -1274,52 +1274,52 @@
         <f t="shared" ref="J11:J40" si="1">IF(AND(NOT(ISBLANK(K11)),NOT(ISBLANK(L11))),IF(K11&gt;L11,"W",IF(K11&lt;L11,"L","D")),"")</f>
         <v>L</v>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="26">
         <f t="array" ref="K11">IF(L11&lt;&gt;"", SUMPRODUCT(MID(N11:Y11,5,1)*1), "")</f>
         <v>1</v>
       </c>
       <c r="L11" s="21">
         <v>2.0</v>
       </c>
-      <c r="M11" s="25">
+      <c r="M11" s="26">
         <f t="array" ref="M11">IF(L11&lt;&gt;"", SUMPRODUCT(LEFT(N11:Y11,1)*1), "")</f>
         <v>9</v>
       </c>
       <c r="N11" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O11" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="P11" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="P11" s="18" t="s">
-        <v>38</v>
-      </c>
       <c r="Q11" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R11" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="S11" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="S11" s="18" t="s">
-        <v>39</v>
-      </c>
       <c r="T11" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U11" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V11" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W11" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="X11" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y11" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AD11" s="5"/>
     </row>
@@ -1331,7 +1331,7 @@
       <c r="B12" s="21">
         <v>1.0</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="22">
@@ -1344,7 +1344,7 @@
         <v>35</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H12" s="21" t="s">
         <v>34</v>
@@ -1356,52 +1356,52 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="26">
         <f t="array" ref="K12">IF(L12&lt;&gt;"", SUMPRODUCT(MID(N12:Y12,5,1)*1), "")</f>
         <v>0</v>
       </c>
       <c r="L12" s="21">
         <v>1.0</v>
       </c>
-      <c r="M12" s="25">
+      <c r="M12" s="26">
         <f t="array" ref="M12">IF(L12&lt;&gt;"", SUMPRODUCT(LEFT(N12:Y12,1)*1), "")</f>
         <v>9</v>
       </c>
       <c r="N12" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="O12" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="P12" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q12" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="O12" s="18" t="s">
+      <c r="R12" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="S12" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="T12" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="U12" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="P12" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q12" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="R12" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="S12" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="T12" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="U12" s="18" t="s">
-        <v>38</v>
-      </c>
       <c r="V12" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W12" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="X12" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y12" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AD12" s="5"/>
     </row>
@@ -1413,7 +1413,7 @@
       <c r="B13" s="21">
         <v>1.0</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="22">
@@ -1426,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H13" s="21" t="s">
         <v>34</v>
@@ -1438,52 +1438,52 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="26">
         <f t="array" ref="K13">IF(L13&lt;&gt;"", SUMPRODUCT(MID(N13:Y13,5,1)*1), "")</f>
         <v>1</v>
       </c>
       <c r="L13" s="21">
         <v>3.0</v>
       </c>
-      <c r="M13" s="25">
+      <c r="M13" s="26">
         <f t="array" ref="M13">IF(L13&lt;&gt;"", SUMPRODUCT(LEFT(N13:Y13,1)*1), "")</f>
         <v>9</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P13" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q13" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R13" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S13" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T13" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U13" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V13" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W13" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="X13" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y13" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AD13" s="5"/>
     </row>
@@ -1495,7 +1495,7 @@
       <c r="B14" s="21">
         <v>1.0</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D14" s="22">
@@ -1518,19 +1518,19 @@
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="26">
         <f t="array" ref="K14">IF(L14&lt;&gt;"", SUMPRODUCT(MID(N14:Y14,5,1)*1), "")</f>
         <v>12</v>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="29">
         <v>5.0</v>
       </c>
-      <c r="M14" s="25">
+      <c r="M14" s="26">
         <f t="array" ref="M14">IF(L14&lt;&gt;"", SUMPRODUCT(LEFT(N14:Y14,1)*1), "")</f>
         <v>9</v>
       </c>
       <c r="N14" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O14" s="18" t="s">
         <v>51</v>
@@ -1539,31 +1539,31 @@
         <v>52</v>
       </c>
       <c r="Q14" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R14" s="18" t="s">
         <v>53</v>
       </c>
       <c r="S14" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="T14" s="18" t="s">
         <v>40</v>
-      </c>
-      <c r="T14" s="18" t="s">
-        <v>39</v>
       </c>
       <c r="U14" s="18" t="s">
         <v>54</v>
       </c>
       <c r="V14" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W14" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="X14" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y14" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AD14" s="5"/>
     </row>
@@ -1575,7 +1575,7 @@
       <c r="B15" s="21">
         <v>1.0</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D15" s="22">
@@ -1596,14 +1596,14 @@
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="K15" s="25">
+      <c r="K15" s="26">
         <f t="array" ref="K15">IF(L15&lt;&gt;"", SUMPRODUCT(MID(N15:Y15,5,1)*1), "")</f>
         <v>14</v>
       </c>
-      <c r="L15" s="28">
+      <c r="L15" s="29">
         <v>3.0</v>
       </c>
-      <c r="M15" s="25">
+      <c r="M15" s="26">
         <f t="array" ref="M15">IF(L15&lt;&gt;"", SUMPRODUCT(LEFT(N15:Y15,1)*1), "")</f>
         <v>9</v>
       </c>
@@ -1620,13 +1620,13 @@
         <v>60</v>
       </c>
       <c r="R15" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="S15" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="S15" s="18" t="s">
-        <v>39</v>
-      </c>
       <c r="T15" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U15" s="18" t="s">
         <v>61</v>
@@ -1638,10 +1638,10 @@
         <v>61</v>
       </c>
       <c r="X15" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y15" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AD15" s="5"/>
     </row>
@@ -1653,7 +1653,7 @@
       <c r="B16" s="21">
         <v>1.0</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D16" s="22">
@@ -1676,52 +1676,52 @@
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="K16" s="25">
+      <c r="K16" s="26">
         <f t="array" ref="K16">IF(L16&lt;&gt;"", SUMPRODUCT(MID(N16:Y16,5,1)*1), "")</f>
         <v>8</v>
       </c>
       <c r="L16" s="30">
         <v>1.0</v>
       </c>
-      <c r="M16" s="25">
+      <c r="M16" s="26">
         <f t="array" ref="M16">IF(L16&lt;&gt;"", SUMPRODUCT(LEFT(N16:Y16,1)*1), "")</f>
         <v>10</v>
       </c>
       <c r="N16" s="18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O16" s="18" t="s">
         <v>62</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q16" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R16" s="18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="S16" s="18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T16" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U16" s="18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V16" s="18" t="s">
         <v>60</v>
       </c>
       <c r="W16" s="18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X16" s="18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y16" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AD16" s="5"/>
     </row>
@@ -1733,7 +1733,7 @@
       <c r="B17" s="21">
         <v>1.0</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D17" s="22">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="F17" s="21"/>
       <c r="G17" s="21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H17" s="21"/>
       <c r="I17" s="21" t="s">
@@ -1754,37 +1754,37 @@
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="K17" s="25">
+      <c r="K17" s="26">
         <f t="array" ref="K17">IF(L17&lt;&gt;"", SUMPRODUCT(MID(N17:Y17,5,1)*1), "")</f>
         <v>15</v>
       </c>
       <c r="L17" s="30">
         <v>1.0</v>
       </c>
-      <c r="M17" s="25">
+      <c r="M17" s="26">
         <f t="array" ref="M17">IF(L17&lt;&gt;"", SUMPRODUCT(LEFT(N17:Y17,1)*1), "")</f>
         <v>10</v>
       </c>
       <c r="N17" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P17" s="18" t="s">
         <v>61</v>
       </c>
       <c r="Q17" s="18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R17" s="18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S17" s="18" t="s">
         <v>62</v>
       </c>
       <c r="T17" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U17" s="18" t="s">
         <v>60</v>
@@ -1793,13 +1793,13 @@
         <v>62</v>
       </c>
       <c r="W17" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X17" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y17" s="18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD17" s="5"/>
     </row>
@@ -1811,7 +1811,7 @@
       <c r="B18" s="21">
         <v>1.0</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D18" s="22">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="F18" s="21"/>
       <c r="G18" s="21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H18" s="21"/>
       <c r="I18" s="21" t="s">
@@ -1838,45 +1838,45 @@
       <c r="L18" s="30">
         <v>2.0</v>
       </c>
-      <c r="M18" s="25">
+      <c r="M18" s="26">
         <f t="array" ref="M18">IF(L18&lt;&gt;"", SUMPRODUCT(LEFT(N18:Y18,1)*1), "")</f>
         <v>9</v>
       </c>
       <c r="N18" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P18" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q18" s="18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R18" s="18" t="s">
         <v>58</v>
       </c>
       <c r="S18" s="18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T18" s="18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U18" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V18" s="18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W18" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="X18" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y18" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AD18" s="5"/>
     </row>
@@ -1887,8 +1887,8 @@
       <c r="B19" s="21">
         <v>2.0</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>77</v>
+      <c r="C19" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="D19" s="22">
         <v>46319.0</v>
@@ -1897,40 +1897,66 @@
         <v>0.3541666666666667</v>
       </c>
       <c r="F19" s="21"/>
-      <c r="G19" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="H19" s="30" t="s">
+      <c r="G19" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="I19" s="30" t="s">
+      <c r="H19" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="I19" s="21" t="s">
         <v>37</v>
       </c>
       <c r="J19" s="20" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="31" t="str">
+        <v>L</v>
+      </c>
+      <c r="K19" s="31">
         <f t="array" ref="K19">IF(L19&lt;&gt;"", SUMPRODUCT(MID(N19:Y19,5,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="L19" s="30"/>
-      <c r="M19" s="25" t="str">
+        <v>1</v>
+      </c>
+      <c r="L19" s="30">
+        <v>5.0</v>
+      </c>
+      <c r="M19" s="26">
         <f t="array" ref="M19">IF(L19&lt;&gt;"", SUMPRODUCT(LEFT(N19:Y19,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="18"/>
-      <c r="R19" s="18"/>
-      <c r="S19" s="18"/>
-      <c r="T19" s="18"/>
-      <c r="U19" s="18"/>
-      <c r="V19" s="18"/>
-      <c r="W19" s="18"/>
-      <c r="X19" s="18"/>
-      <c r="Y19" s="18"/>
+        <v>10</v>
+      </c>
+      <c r="N19" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="O19" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="P19" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q19" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="R19" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="S19" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="T19" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="U19" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="V19" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="W19" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="X19" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y19" s="18" t="s">
+        <v>42</v>
+      </c>
       <c r="AD19" s="5"/>
     </row>
     <row r="20">
@@ -1940,8 +1966,8 @@
       <c r="B20" s="21">
         <v>2.0</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>77</v>
+      <c r="C20" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="D20" s="22">
         <v>46326.0</v>
@@ -1966,7 +1992,7 @@
         <v/>
       </c>
       <c r="L20" s="30"/>
-      <c r="M20" s="25" t="str">
+      <c r="M20" s="26" t="str">
         <f t="array" ref="M20">IF(L20&lt;&gt;"", SUMPRODUCT(LEFT(N20:Y20,1)*1), "")</f>
         <v/>
       </c>
@@ -1991,8 +2017,8 @@
       <c r="B21" s="21">
         <v>2.0</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>77</v>
+      <c r="C21" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="D21" s="22">
         <v>46333.0</v>
@@ -2019,7 +2045,7 @@
         <v/>
       </c>
       <c r="L21" s="30"/>
-      <c r="M21" s="25" t="str">
+      <c r="M21" s="26" t="str">
         <f t="array" ref="M21">IF(L21&lt;&gt;"", SUMPRODUCT(LEFT(N21:Y21,1)*1), "")</f>
         <v/>
       </c>
@@ -2044,8 +2070,8 @@
       <c r="B22" s="21">
         <v>2.0</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>77</v>
+      <c r="C22" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="D22" s="22">
         <v>46340.0</v>
@@ -2055,7 +2081,7 @@
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H22" s="21"/>
       <c r="I22" s="21" t="s">
@@ -2070,7 +2096,7 @@
         <v/>
       </c>
       <c r="L22" s="30"/>
-      <c r="M22" s="25" t="str">
+      <c r="M22" s="26" t="str">
         <f t="array" ref="M22">IF(L22&lt;&gt;"", SUMPRODUCT(LEFT(N22:Y22,1)*1), "")</f>
         <v/>
       </c>
@@ -2095,8 +2121,8 @@
       <c r="B23" s="21">
         <v>2.0</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>77</v>
+      <c r="C23" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="D23" s="22">
         <v>46347.0</v>
@@ -2106,10 +2132,10 @@
       </c>
       <c r="F23" s="21"/>
       <c r="G23" s="30" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H23" s="30" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I23" s="30" t="s">
         <v>37</v>
@@ -2123,7 +2149,7 @@
         <v/>
       </c>
       <c r="L23" s="30"/>
-      <c r="M23" s="25" t="str">
+      <c r="M23" s="26" t="str">
         <f t="array" ref="M23">IF(L23&lt;&gt;"", SUMPRODUCT(LEFT(N23:Y23,1)*1), "")</f>
         <v/>
       </c>
@@ -2148,8 +2174,8 @@
       <c r="B24" s="21">
         <v>2.0</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>77</v>
+      <c r="C24" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="D24" s="22">
         <v>46354.0</v>
@@ -2159,7 +2185,7 @@
       </c>
       <c r="F24" s="21"/>
       <c r="G24" s="30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H24" s="21"/>
       <c r="I24" s="21" t="s">
@@ -2174,7 +2200,7 @@
         <v/>
       </c>
       <c r="L24" s="30"/>
-      <c r="M24" s="25" t="str">
+      <c r="M24" s="26" t="str">
         <f t="array" ref="M24">IF(L24&lt;&gt;"", SUMPRODUCT(LEFT(N24:Y24,1)*1), "")</f>
         <v/>
       </c>
@@ -2199,8 +2225,8 @@
       <c r="B25" s="21">
         <v>2.0</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>77</v>
+      <c r="C25" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="D25" s="22">
         <v>46361.0</v>
@@ -2227,7 +2253,7 @@
         <v/>
       </c>
       <c r="L25" s="30"/>
-      <c r="M25" s="25" t="str">
+      <c r="M25" s="26" t="str">
         <f t="array" ref="M25">IF(L25&lt;&gt;"", SUMPRODUCT(LEFT(N25:Y25,1)*1), "")</f>
         <v/>
       </c>
@@ -2250,24 +2276,24 @@
         <f t="shared" ref="A26:A40" si="3">IF(ISBLANK(B26),"",A25+1)</f>
         <v/>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
       <c r="J26" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K26" s="25" t="str">
+      <c r="K26" s="26" t="str">
         <f t="array" ref="K26">IF(L26&lt;&gt;"", SUMPRODUCT(MID(N26:Y26,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L26" s="28"/>
-      <c r="M26" s="25" t="str">
+      <c r="L26" s="29"/>
+      <c r="M26" s="26" t="str">
         <f t="array" ref="M26">IF(L26&lt;&gt;"", SUMPRODUCT(LEFT(N26:Y26,1)*1), "")</f>
         <v/>
       </c>
@@ -2290,24 +2316,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
       <c r="J27" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K27" s="25" t="str">
+      <c r="K27" s="26" t="str">
         <f t="array" ref="K27">IF(L27&lt;&gt;"", SUMPRODUCT(MID(N27:Y27,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L27" s="21"/>
-      <c r="M27" s="25" t="str">
+      <c r="M27" s="26" t="str">
         <f t="array" ref="M27">IF(L27&lt;&gt;"", SUMPRODUCT(LEFT(N27:Y27,1)*1), "")</f>
         <v/>
       </c>
@@ -2330,24 +2356,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
       <c r="J28" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K28" s="25" t="str">
+      <c r="K28" s="26" t="str">
         <f t="array" ref="K28">IF(L28&lt;&gt;"", SUMPRODUCT(MID(N28:Y28,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L28" s="21"/>
-      <c r="M28" s="25" t="str">
+      <c r="M28" s="26" t="str">
         <f t="array" ref="M28">IF(L28&lt;&gt;"", SUMPRODUCT(LEFT(N28:Y28,1)*1), "")</f>
         <v/>
       </c>
@@ -2370,24 +2396,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
       <c r="J29" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K29" s="25" t="str">
+      <c r="K29" s="26" t="str">
         <f t="array" ref="K29">IF(L29&lt;&gt;"", SUMPRODUCT(MID(N29:Y29,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L29" s="21"/>
-      <c r="M29" s="25" t="str">
+      <c r="M29" s="26" t="str">
         <f t="array" ref="M29">IF(L29&lt;&gt;"", SUMPRODUCT(LEFT(N29:Y29,1)*1), "")</f>
         <v/>
       </c>
@@ -2410,24 +2436,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
       <c r="J30" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K30" s="25" t="str">
+      <c r="K30" s="26" t="str">
         <f t="array" ref="K30">IF(L30&lt;&gt;"", SUMPRODUCT(MID(N30:Y30,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L30" s="21"/>
-      <c r="M30" s="25" t="str">
+      <c r="M30" s="26" t="str">
         <f t="array" ref="M30">IF(L30&lt;&gt;"", SUMPRODUCT(LEFT(N30:Y30,1)*1), "")</f>
         <v/>
       </c>
@@ -2450,24 +2476,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
       <c r="J31" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K31" s="25" t="str">
+      <c r="K31" s="26" t="str">
         <f t="array" ref="K31">IF(L31&lt;&gt;"", SUMPRODUCT(MID(N31:Y31,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L31" s="21"/>
-      <c r="M31" s="25" t="str">
+      <c r="M31" s="26" t="str">
         <f t="array" ref="M31">IF(L31&lt;&gt;"", SUMPRODUCT(LEFT(N31:Y31,1)*1), "")</f>
         <v/>
       </c>
@@ -2490,24 +2516,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
       <c r="J32" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K32" s="25" t="str">
+      <c r="K32" s="26" t="str">
         <f t="array" ref="K32">IF(L32&lt;&gt;"", SUMPRODUCT(MID(N32:Y32,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L32" s="21"/>
-      <c r="M32" s="25" t="str">
+      <c r="M32" s="26" t="str">
         <f t="array" ref="M32">IF(L32&lt;&gt;"", SUMPRODUCT(LEFT(N32:Y32,1)*1), "")</f>
         <v/>
       </c>
@@ -2530,24 +2556,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
       <c r="J33" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K33" s="25" t="str">
+      <c r="K33" s="26" t="str">
         <f t="array" ref="K33">IF(L33&lt;&gt;"", SUMPRODUCT(MID(N33:Y33,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L33" s="21"/>
-      <c r="M33" s="25" t="str">
+      <c r="M33" s="26" t="str">
         <f t="array" ref="M33">IF(L33&lt;&gt;"", SUMPRODUCT(LEFT(N33:Y33,1)*1), "")</f>
         <v/>
       </c>
@@ -2570,24 +2596,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
       <c r="J34" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K34" s="25" t="str">
+      <c r="K34" s="26" t="str">
         <f t="array" ref="K34">IF(L34&lt;&gt;"", SUMPRODUCT(MID(N34:Y34,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L34" s="21"/>
-      <c r="M34" s="25" t="str">
+      <c r="M34" s="26" t="str">
         <f t="array" ref="M34">IF(L34&lt;&gt;"", SUMPRODUCT(LEFT(N34:Y34,1)*1), "")</f>
         <v/>
       </c>
@@ -2610,24 +2636,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
       <c r="J35" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K35" s="25" t="str">
+      <c r="K35" s="26" t="str">
         <f t="array" ref="K35">IF(L35&lt;&gt;"", SUMPRODUCT(MID(N35:Y35,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L35" s="21"/>
-      <c r="M35" s="25" t="str">
+      <c r="M35" s="26" t="str">
         <f t="array" ref="M35">IF(L35&lt;&gt;"", SUMPRODUCT(LEFT(N35:Y35,1)*1), "")</f>
         <v/>
       </c>
@@ -2650,24 +2676,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
       <c r="J36" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="25" t="str">
+      <c r="K36" s="26" t="str">
         <f t="array" ref="K36">IF(L36&lt;&gt;"", SUMPRODUCT(MID(N36:Y36,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L36" s="28"/>
-      <c r="M36" s="25" t="str">
+      <c r="L36" s="29"/>
+      <c r="M36" s="26" t="str">
         <f t="array" ref="M36">IF(L36&lt;&gt;"", SUMPRODUCT(LEFT(N36:Y36,1)*1), "")</f>
         <v/>
       </c>
@@ -2690,24 +2716,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
       <c r="J37" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K37" s="25" t="str">
+      <c r="K37" s="26" t="str">
         <f t="array" ref="K37">IF(L37&lt;&gt;"", SUMPRODUCT(MID(N37:Y37,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L37" s="21"/>
-      <c r="M37" s="25" t="str">
+      <c r="M37" s="26" t="str">
         <f t="array" ref="M37">IF(L37&lt;&gt;"", SUMPRODUCT(LEFT(N37:Y37,1)*1), "")</f>
         <v/>
       </c>
@@ -2730,24 +2756,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
       <c r="J38" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K38" s="25" t="str">
+      <c r="K38" s="26" t="str">
         <f t="array" ref="K38">IF(L38&lt;&gt;"", SUMPRODUCT(MID(N38:Y38,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L38" s="21"/>
-      <c r="M38" s="25" t="str">
+      <c r="M38" s="26" t="str">
         <f t="array" ref="M38">IF(L38&lt;&gt;"", SUMPRODUCT(LEFT(N38:Y38,1)*1), "")</f>
         <v/>
       </c>
@@ -2770,24 +2796,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
       <c r="J39" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K39" s="25" t="str">
+      <c r="K39" s="26" t="str">
         <f t="array" ref="K39">IF(L39&lt;&gt;"", SUMPRODUCT(MID(N39:Y39,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L39" s="21"/>
-      <c r="M39" s="25" t="str">
+      <c r="M39" s="26" t="str">
         <f t="array" ref="M39">IF(L39&lt;&gt;"", SUMPRODUCT(LEFT(N39:Y39,1)*1), "")</f>
         <v/>
       </c>
@@ -2810,24 +2836,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
       <c r="J40" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K40" s="25" t="str">
+      <c r="K40" s="26" t="str">
         <f t="array" ref="K40">IF(L40&lt;&gt;"", SUMPRODUCT(MID(N40:Y40,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L40" s="21"/>
-      <c r="M40" s="25" t="str">
+      <c r="M40" s="26" t="str">
         <f t="array" ref="M40">IF(L40&lt;&gt;"", SUMPRODUCT(LEFT(N40:Y40,1)*1), "")</f>
         <v/>
       </c>
@@ -3030,7 +3056,7 @@
         <v>0.0</v>
       </c>
       <c r="L45" s="12">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M45" s="12">
         <v>0.0</v>
@@ -3038,7 +3064,7 @@
       <c r="N45" s="5"/>
       <c r="O45" s="34">
         <f t="shared" ref="O45:O48" si="4">SUM(A45:N45)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" s="5"/>
       <c r="U45" s="5"/>
@@ -3054,22 +3080,22 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B46" s="12">
         <v>1.0</v>
       </c>
       <c r="C46" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="D46" s="12">
         <v>1.0</v>
-      </c>
-      <c r="D46" s="12">
-        <v>0.0</v>
       </c>
       <c r="E46" s="12">
         <v>1.0</v>
       </c>
       <c r="F46" s="12">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G46" s="12">
         <v>1.0</v>
@@ -3087,7 +3113,7 @@
         <v>0.0</v>
       </c>
       <c r="L46" s="12">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M46" s="12">
         <v>0.0</v>
@@ -3117,25 +3143,25 @@
         <v>0.0</v>
       </c>
       <c r="C47" s="12">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="D47" s="12">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="E47" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F47" s="12">
         <v>1.0</v>
       </c>
-      <c r="F47" s="12">
-        <v>4.0</v>
-      </c>
       <c r="G47" s="12">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H47" s="12">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I47" s="12">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="J47" s="12">
         <v>0.0</v>
@@ -3152,7 +3178,7 @@
       <c r="N47" s="5"/>
       <c r="O47" s="34">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="T47" s="5"/>
       <c r="U47" s="5"/>
@@ -3171,19 +3197,19 @@
         <v>96</v>
       </c>
       <c r="B48" s="12">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C48" s="12">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="D48" s="12">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E48" s="12">
         <v>0.0</v>
       </c>
       <c r="F48" s="12">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G48" s="12">
         <v>0.0</v>
@@ -3192,10 +3218,10 @@
         <v>0.0</v>
       </c>
       <c r="I48" s="12">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J48" s="12">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K48" s="12">
         <v>0.0</v>
@@ -3209,7 +3235,7 @@
       <c r="N48" s="5"/>
       <c r="O48" s="34">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T48" s="5"/>
       <c r="U48" s="5"/>
@@ -3227,39 +3253,39 @@
       <c r="A49" s="5"/>
       <c r="B49" s="5" t="str">
         <f t="shared" ref="B49:N49" si="5">B45&amp;","&amp;B46&amp;","&amp;B47&amp;","&amp;B48</f>
-        <v>1,1,0,3</v>
+        <v>1,1,0,0</v>
       </c>
       <c r="C49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,2,3</v>
+        <v>1,0,0,0</v>
       </c>
       <c r="D49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>1,0,2,1</v>
+        <v>1,1,0,0</v>
       </c>
       <c r="E49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,1,0</v>
+        <v>1,1,0,0</v>
       </c>
       <c r="F49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,4,1</v>
+        <v>1,0,1,0</v>
       </c>
       <c r="G49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,1,0</v>
+        <v>1,1,0,0</v>
       </c>
       <c r="H49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,1,0</v>
+        <v>1,1,0,0</v>
       </c>
       <c r="I49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,6,1</v>
+        <v>1,1,0,0</v>
       </c>
       <c r="J49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,0,1</v>
+        <v>1,1,0,0</v>
       </c>
       <c r="K49" s="5" t="str">
         <f t="shared" si="5"/>
@@ -3267,7 +3293,7 @@
       </c>
       <c r="L49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>0,0,0,0</v>
+        <v>1,1,0,0</v>
       </c>
       <c r="M49" s="5" t="str">
         <f t="shared" si="5"/>
@@ -33363,7 +33389,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1"/>
+      <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="4" t="s">
         <v>1</v>
@@ -33412,39 +33438,39 @@
       </c>
       <c r="C2" s="11">
         <f t="array" ref="C2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="11">
         <f t="array" ref="D2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z42, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="11">
         <f t="array" ref="E2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="11">
         <f t="array" ref="F2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="11">
         <f t="array" ref="G2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="11">
         <f t="array" ref="H2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="11">
         <f t="array" ref="I2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J2" s="11">
         <f t="array" ref="J2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" s="11">
         <f t="array" ref="K2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -33458,9 +33484,9 @@
       <c r="U2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="26"/>
+      <c r="A3" s="25"/>
       <c r="B3" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C3" s="27">
         <f>C2/MatchesDB!$B$1</f>
@@ -33476,7 +33502,7 @@
       </c>
       <c r="F3" s="27">
         <f>F2/MatchesDB!$B$1</f>
-        <v>0.875</v>
+        <v>0.8888888889</v>
       </c>
       <c r="G3" s="27">
         <f>G2/MatchesDB!$B$1</f>
@@ -33488,7 +33514,7 @@
       </c>
       <c r="I3" s="27">
         <f>I2/(MatchesDB!$B$1-4)</f>
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J3" s="27">
         <f>J2/MatchesDB!$B$1</f>
@@ -33511,46 +33537,46 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="28">
         <f t="array" ref="C4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>6</v>
-      </c>
-      <c r="D4" s="29">
+        <v>7</v>
+      </c>
+      <c r="D4" s="28">
         <f t="array" ref="D4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="28">
         <f t="array" ref="E4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>4</v>
-      </c>
-      <c r="F4" s="29">
+        <v>5</v>
+      </c>
+      <c r="F4" s="28">
         <f t="array" ref="F4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>6</v>
-      </c>
-      <c r="G4" s="29">
+        <v>7</v>
+      </c>
+      <c r="G4" s="28">
         <f t="array" ref="G4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>7</v>
       </c>
-      <c r="H4" s="29">
+      <c r="H4" s="28">
         <f t="array" ref="H4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
+        <v>9</v>
+      </c>
+      <c r="I4" s="28">
+        <f t="array" ref="I4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
+        <v>7</v>
+      </c>
+      <c r="J4" s="28">
+        <f t="array" ref="J4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
-      <c r="I4" s="29">
-        <f t="array" ref="I4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>6</v>
-      </c>
-      <c r="J4" s="29">
-        <f t="array" ref="J4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>7</v>
-      </c>
-      <c r="K4" s="29">
+      <c r="K4" s="28">
         <f t="array" ref="K4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
@@ -33564,29 +33590,29 @@
       <c r="U4" s="5"/>
     </row>
     <row r="5">
-      <c r="A5" s="26"/>
+      <c r="A5" s="25"/>
       <c r="B5" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C5" s="27">
         <f t="shared" ref="C5:K5" si="1">C4/C2</f>
-        <v>0.75</v>
+        <v>0.7777777778</v>
       </c>
       <c r="D5" s="27">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.8888888889</v>
       </c>
       <c r="E5" s="27">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.5555555556</v>
       </c>
       <c r="F5" s="27">
         <f t="shared" si="1"/>
-        <v>0.8571428571</v>
+        <v>0.875</v>
       </c>
       <c r="G5" s="27">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.7777777778</v>
       </c>
       <c r="H5" s="27">
         <f t="shared" si="1"/>
@@ -33598,7 +33624,7 @@
       </c>
       <c r="J5" s="27">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.8888888889</v>
       </c>
       <c r="K5" s="27">
         <f t="shared" si="1"/>
@@ -33617,7 +33643,7 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>11</v>
@@ -33640,7 +33666,7 @@
       </c>
       <c r="G6" s="11">
         <f t="array" ref="G6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H6" s="11">
         <f t="array" ref="H6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
@@ -33670,45 +33696,45 @@
       <c r="U6" s="5"/>
     </row>
     <row r="7">
-      <c r="A7" s="26"/>
+      <c r="A7" s="25"/>
       <c r="B7" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C7" s="32">
         <f t="shared" ref="C7:K7" si="2">C6/C2</f>
-        <v>0.125</v>
+        <v>0.1111111111</v>
       </c>
       <c r="D7" s="32">
         <f t="shared" si="2"/>
-        <v>1.5</v>
+        <v>1.333333333</v>
       </c>
       <c r="E7" s="32">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.6666666667</v>
       </c>
       <c r="F7" s="32">
         <f t="shared" si="2"/>
-        <v>0.2857142857</v>
+        <v>0.25</v>
       </c>
       <c r="G7" s="32">
         <f t="shared" si="2"/>
-        <v>2.625</v>
+        <v>2.444444444</v>
       </c>
       <c r="H7" s="32">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.4444444444</v>
       </c>
       <c r="I7" s="32">
         <f t="shared" si="2"/>
-        <v>0.1666666667</v>
+        <v>0.1428571429</v>
       </c>
       <c r="J7" s="32">
         <f t="shared" si="2"/>
-        <v>1.375</v>
+        <v>1.222222222</v>
       </c>
       <c r="K7" s="32">
         <f t="shared" si="2"/>
-        <v>0.625</v>
+        <v>0.5555555556</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
@@ -33723,44 +33749,44 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="28">
         <f t="array" ref="C8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>8</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="28">
         <f t="array" ref="D8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>10</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="28">
         <f t="array" ref="E8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>2</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="28">
         <f t="array" ref="F8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>2</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="28">
         <f t="array" ref="G8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>4</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="28">
         <f t="array" ref="H8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>2</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="28">
         <f t="array" ref="I8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>0</v>
       </c>
-      <c r="J8" s="29">
+      <c r="J8" s="28">
         <f t="array" ref="J8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>5</v>
       </c>
-      <c r="K8" s="29">
+      <c r="K8" s="28">
         <f t="array" ref="K8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>4</v>
       </c>
@@ -33776,33 +33802,33 @@
       <c r="U8" s="5"/>
     </row>
     <row r="9">
-      <c r="A9" s="26"/>
+      <c r="A9" s="25"/>
       <c r="B9" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C9" s="32">
         <f t="shared" ref="C9:K9" si="3">C8/C2</f>
-        <v>1</v>
+        <v>0.8888888889</v>
       </c>
       <c r="D9" s="32">
         <f t="shared" si="3"/>
-        <v>1.25</v>
+        <v>1.111111111</v>
       </c>
       <c r="E9" s="32">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.2222222222</v>
       </c>
       <c r="F9" s="32">
         <f t="shared" si="3"/>
-        <v>0.2857142857</v>
+        <v>0.25</v>
       </c>
       <c r="G9" s="32">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.4444444444</v>
       </c>
       <c r="H9" s="32">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.2222222222</v>
       </c>
       <c r="I9" s="32">
         <f t="shared" si="3"/>
@@ -33810,11 +33836,11 @@
       </c>
       <c r="J9" s="32">
         <f t="shared" si="3"/>
-        <v>0.625</v>
+        <v>0.5555555556</v>
       </c>
       <c r="K9" s="32">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.4444444444</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -33852,7 +33878,7 @@
       </c>
       <c r="G10" s="11">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H10" s="11">
         <f t="shared" si="4"/>
@@ -33882,45 +33908,45 @@
       <c r="U10" s="5"/>
     </row>
     <row r="11">
-      <c r="A11" s="26"/>
+      <c r="A11" s="25"/>
       <c r="B11" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C11" s="32">
         <f t="shared" ref="C11:K11" si="5">C10/C2</f>
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="D11" s="32">
         <f t="shared" si="5"/>
-        <v>2.75</v>
+        <v>2.444444444</v>
       </c>
       <c r="E11" s="32">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.8888888889</v>
       </c>
       <c r="F11" s="32">
         <f t="shared" si="5"/>
-        <v>0.5714285714</v>
+        <v>0.5</v>
       </c>
       <c r="G11" s="32">
         <f t="shared" si="5"/>
-        <v>3.125</v>
+        <v>2.888888889</v>
       </c>
       <c r="H11" s="32">
         <f t="shared" si="5"/>
-        <v>0.75</v>
+        <v>0.6666666667</v>
       </c>
       <c r="I11" s="32">
         <f t="shared" si="5"/>
-        <v>0.1666666667</v>
+        <v>0.1428571429</v>
       </c>
       <c r="J11" s="32">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1.777777778</v>
       </c>
       <c r="K11" s="32">
         <f t="shared" si="5"/>
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>

--- a/JO12-1/JO12-1_matchesDB.xlsx
+++ b/JO12-1/JO12-1_matchesDB.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="97">
   <si>
     <t>Matches</t>
   </si>
@@ -133,9 +133,6 @@
     <t>A</t>
   </si>
   <si>
-    <t>%</t>
-  </si>
-  <si>
     <t>1,0,0,0</t>
   </si>
   <si>
@@ -146,9 +143,6 @@
   </si>
   <si>
     <t>0,0,0,0</t>
-  </si>
-  <si>
-    <t>1st lineup</t>
   </si>
   <si>
     <t>KFC</t>
@@ -216,7 +210,7 @@
 1187ZT Amstelveen</t>
   </si>
   <si>
-    <t>Scorers</t>
+    <t>%</t>
   </si>
   <si>
     <t>1,1,3,0</t>
@@ -241,6 +235,9 @@
   </si>
   <si>
     <t>Amstelveen/Heemraad O12-1</t>
+  </si>
+  <si>
+    <t>1st lineup</t>
   </si>
   <si>
     <t>1,1,0,3</t>
@@ -273,12 +270,6 @@
     <t>Sportpark Naarden, Amersfoortsestraatweg 14, Naarden</t>
   </si>
   <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Assists</t>
-  </si>
-  <si>
     <t>FC Weesp O12-1</t>
   </si>
   <si>
@@ -297,7 +288,13 @@
     <t>Sportpark Diemen, Sportlaan 13, Diemen</t>
   </si>
   <si>
-    <t>Goal contribution</t>
+    <t>Scorers</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Assists</t>
   </si>
   <si>
     <t>Player3</t>
@@ -310,6 +307,9 @@
   </si>
   <si>
     <t>assist</t>
+  </si>
+  <si>
+    <t>Goal contribution</t>
   </si>
 </sst>
 </file>
@@ -327,12 +327,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -401,6 +401,20 @@
   <borders count="11">
     <border/>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -408,20 +422,6 @@
         <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
@@ -525,14 +525,14 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="5" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -541,72 +541,72 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="6" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="7" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="8" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="9" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="16" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="16" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -834,12 +834,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7">
         <f>SUM(COUNTIF(J11:J40,"W"),COUNTIF(J11:J40,"D"),COUNTIF(J11:J40,"L"))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C1" s="5"/>
       <c r="D1" s="8">
@@ -915,7 +915,7 @@
       </c>
       <c r="B3" s="10">
         <f>COUNTIF(J11:J40,"L")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -1026,10 +1026,10 @@
       </c>
       <c r="B6" s="10">
         <f>B7-B8</f>
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C6" s="5"/>
-      <c r="D6" s="12"/>
+      <c r="D6" s="11"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B7" s="10">
         <f>SUM(K11:K40)</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1095,12 +1095,12 @@
       <c r="AD7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="13">
         <f>SUM(L11:L40)</f>
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1249,7 +1249,7 @@
       <c r="B11" s="21">
         <v>1.0</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="22">
@@ -1274,52 +1274,52 @@
         <f t="shared" ref="J11:J40" si="1">IF(AND(NOT(ISBLANK(K11)),NOT(ISBLANK(L11))),IF(K11&gt;L11,"W",IF(K11&lt;L11,"L","D")),"")</f>
         <v>L</v>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="25">
         <f t="array" ref="K11">IF(L11&lt;&gt;"", SUMPRODUCT(MID(N11:Y11,5,1)*1), "")</f>
         <v>1</v>
       </c>
       <c r="L11" s="21">
         <v>2.0</v>
       </c>
-      <c r="M11" s="26">
+      <c r="M11" s="25">
         <f t="array" ref="M11">IF(L11&lt;&gt;"", SUMPRODUCT(LEFT(N11:Y11,1)*1), "")</f>
         <v>9</v>
       </c>
       <c r="N11" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O11" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="18" t="s">
+      <c r="P11" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q11" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="R11" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="P11" s="18" t="s">
+      <c r="S11" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Q11" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="R11" s="18" t="s">
+      <c r="T11" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="U11" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="V11" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="W11" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S11" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="T11" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="U11" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="V11" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="W11" s="18" t="s">
-        <v>42</v>
-      </c>
       <c r="X11" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y11" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AD11" s="5"/>
     </row>
@@ -1331,7 +1331,7 @@
       <c r="B12" s="21">
         <v>1.0</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="22">
@@ -1344,7 +1344,7 @@
         <v>35</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H12" s="21" t="s">
         <v>34</v>
@@ -1356,52 +1356,52 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="K12" s="26">
+      <c r="K12" s="25">
         <f t="array" ref="K12">IF(L12&lt;&gt;"", SUMPRODUCT(MID(N12:Y12,5,1)*1), "")</f>
         <v>0</v>
       </c>
       <c r="L12" s="21">
         <v>1.0</v>
       </c>
-      <c r="M12" s="26">
+      <c r="M12" s="25">
         <f t="array" ref="M12">IF(L12&lt;&gt;"", SUMPRODUCT(LEFT(N12:Y12,1)*1), "")</f>
         <v>9</v>
       </c>
       <c r="N12" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P12" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q12" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="R12" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="R12" s="18" t="s">
-        <v>40</v>
-      </c>
       <c r="S12" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T12" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U12" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="V12" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="V12" s="18" t="s">
-        <v>40</v>
-      </c>
       <c r="W12" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X12" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y12" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AD12" s="5"/>
     </row>
@@ -1413,7 +1413,7 @@
       <c r="B13" s="21">
         <v>1.0</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="22">
@@ -1426,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H13" s="21" t="s">
         <v>34</v>
@@ -1438,52 +1438,52 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="25">
         <f t="array" ref="K13">IF(L13&lt;&gt;"", SUMPRODUCT(MID(N13:Y13,5,1)*1), "")</f>
         <v>1</v>
       </c>
       <c r="L13" s="21">
         <v>3.0</v>
       </c>
-      <c r="M13" s="26">
+      <c r="M13" s="25">
         <f t="array" ref="M13">IF(L13&lt;&gt;"", SUMPRODUCT(LEFT(N13:Y13,1)*1), "")</f>
         <v>9</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P13" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q13" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R13" s="18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S13" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T13" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U13" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V13" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W13" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X13" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y13" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AD13" s="5"/>
     </row>
@@ -1495,8 +1495,8 @@
       <c r="B14" s="21">
         <v>1.0</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>48</v>
+      <c r="C14" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="D14" s="22">
         <v>46270.0</v>
@@ -1506,10 +1506,10 @@
       </c>
       <c r="F14" s="21"/>
       <c r="G14" s="21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I14" s="21" t="s">
         <v>37</v>
@@ -1518,52 +1518,52 @@
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="K14" s="26">
+      <c r="K14" s="25">
         <f t="array" ref="K14">IF(L14&lt;&gt;"", SUMPRODUCT(MID(N14:Y14,5,1)*1), "")</f>
         <v>12</v>
       </c>
-      <c r="L14" s="29">
+      <c r="L14" s="26">
         <v>5.0</v>
       </c>
-      <c r="M14" s="26">
+      <c r="M14" s="25">
         <f t="array" ref="M14">IF(L14&lt;&gt;"", SUMPRODUCT(LEFT(N14:Y14,1)*1), "")</f>
         <v>9</v>
       </c>
       <c r="N14" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="O14" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="P14" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q14" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="R14" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="S14" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="O14" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="P14" s="18" t="s">
+      <c r="T14" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="U14" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="Q14" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="R14" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="S14" s="18" t="s">
+      <c r="V14" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="W14" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="T14" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="U14" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="V14" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="W14" s="18" t="s">
-        <v>42</v>
-      </c>
       <c r="X14" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y14" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AD14" s="5"/>
     </row>
@@ -1575,8 +1575,8 @@
       <c r="B15" s="21">
         <v>1.0</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>48</v>
+      <c r="C15" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="D15" s="22">
         <v>46277.0</v>
@@ -1586,62 +1586,62 @@
       </c>
       <c r="F15" s="21"/>
       <c r="G15" s="21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H15" s="21"/>
       <c r="I15" s="21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J15" s="20" t="str">
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="K15" s="26">
+      <c r="K15" s="25">
         <f t="array" ref="K15">IF(L15&lt;&gt;"", SUMPRODUCT(MID(N15:Y15,5,1)*1), "")</f>
         <v>14</v>
       </c>
-      <c r="L15" s="29">
+      <c r="L15" s="26">
         <v>3.0</v>
       </c>
-      <c r="M15" s="26">
+      <c r="M15" s="25">
         <f t="array" ref="M15">IF(L15&lt;&gt;"", SUMPRODUCT(LEFT(N15:Y15,1)*1), "")</f>
         <v>9</v>
       </c>
       <c r="N15" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="O15" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="P15" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="O15" s="18" t="s">
+      <c r="Q15" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="P15" s="18" t="s">
+      <c r="R15" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="S15" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="T15" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="U15" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="Q15" s="18" t="s">
+      <c r="V15" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="R15" s="18" t="s">
+      <c r="W15" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="X15" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="S15" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="T15" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="U15" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="V15" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="W15" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="X15" s="18" t="s">
-        <v>42</v>
-      </c>
       <c r="Y15" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AD15" s="5"/>
     </row>
@@ -1653,8 +1653,8 @@
       <c r="B16" s="21">
         <v>1.0</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>48</v>
+      <c r="C16" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="D16" s="22">
         <v>46284.0</v>
@@ -1664,10 +1664,10 @@
       </c>
       <c r="F16" s="21"/>
       <c r="G16" s="21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I16" s="21" t="s">
         <v>37</v>
@@ -1676,52 +1676,52 @@
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="K16" s="26">
+      <c r="K16" s="25">
         <f t="array" ref="K16">IF(L16&lt;&gt;"", SUMPRODUCT(MID(N16:Y16,5,1)*1), "")</f>
         <v>8</v>
       </c>
-      <c r="L16" s="30">
+      <c r="L16" s="27">
         <v>1.0</v>
       </c>
-      <c r="M16" s="26">
+      <c r="M16" s="25">
         <f t="array" ref="M16">IF(L16&lt;&gt;"", SUMPRODUCT(LEFT(N16:Y16,1)*1), "")</f>
         <v>10</v>
       </c>
       <c r="N16" s="18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q16" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R16" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="S16" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="T16" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="U16" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="V16" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="W16" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="X16" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="S16" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="T16" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="U16" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="V16" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="W16" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="X16" s="18" t="s">
-        <v>68</v>
-      </c>
       <c r="Y16" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AD16" s="5"/>
     </row>
@@ -1733,8 +1733,8 @@
       <c r="B17" s="21">
         <v>1.0</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>48</v>
+      <c r="C17" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="D17" s="22">
         <v>46291.0</v>
@@ -1744,62 +1744,62 @@
       </c>
       <c r="F17" s="21"/>
       <c r="G17" s="21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H17" s="21"/>
       <c r="I17" s="21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J17" s="20" t="str">
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="K17" s="26">
+      <c r="K17" s="25">
         <f t="array" ref="K17">IF(L17&lt;&gt;"", SUMPRODUCT(MID(N17:Y17,5,1)*1), "")</f>
         <v>15</v>
       </c>
-      <c r="L17" s="30">
+      <c r="L17" s="27">
         <v>1.0</v>
       </c>
-      <c r="M17" s="26">
+      <c r="M17" s="25">
         <f t="array" ref="M17">IF(L17&lt;&gt;"", SUMPRODUCT(LEFT(N17:Y17,1)*1), "")</f>
         <v>10</v>
       </c>
       <c r="N17" s="18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O17" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="P17" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q17" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="R17" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="S17" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="T17" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="U17" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="V17" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="W17" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="P17" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q17" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="R17" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="S17" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="T17" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="U17" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="V17" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="W17" s="18" t="s">
-        <v>72</v>
-      </c>
       <c r="X17" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y17" s="18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AD17" s="5"/>
     </row>
@@ -1811,8 +1811,8 @@
       <c r="B18" s="21">
         <v>1.0</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>48</v>
+      <c r="C18" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="D18" s="22">
         <v>46298.0</v>
@@ -1822,61 +1822,61 @@
       </c>
       <c r="F18" s="21"/>
       <c r="G18" s="21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H18" s="21"/>
       <c r="I18" s="21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J18" s="20" t="str">
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="K18" s="31">
+      <c r="K18" s="30">
         <v>19.0</v>
       </c>
-      <c r="L18" s="30">
+      <c r="L18" s="27">
         <v>2.0</v>
       </c>
-      <c r="M18" s="26">
+      <c r="M18" s="25">
         <f t="array" ref="M18">IF(L18&lt;&gt;"", SUMPRODUCT(LEFT(N18:Y18,1)*1), "")</f>
         <v>9</v>
       </c>
       <c r="N18" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="O18" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="O18" s="18" t="s">
+      <c r="P18" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="P18" s="18" t="s">
+      <c r="Q18" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="R18" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="S18" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="T18" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="U18" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="Q18" s="18" t="s">
+      <c r="V18" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="W18" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="R18" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="S18" s="18" t="s">
+      <c r="X18" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="T18" s="18" t="s">
+      <c r="Y18" s="18" t="s">
         <v>41</v>
-      </c>
-      <c r="U18" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="V18" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="W18" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="X18" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y18" s="18" t="s">
-        <v>42</v>
       </c>
       <c r="AD18" s="5"/>
     </row>
@@ -1887,8 +1887,8 @@
       <c r="B19" s="21">
         <v>2.0</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>78</v>
+      <c r="C19" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="D19" s="22">
         <v>46319.0</v>
@@ -1898,10 +1898,10 @@
       </c>
       <c r="F19" s="21"/>
       <c r="G19" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H19" s="21" t="s">
         <v>79</v>
-      </c>
-      <c r="H19" s="21" t="s">
-        <v>80</v>
       </c>
       <c r="I19" s="21" t="s">
         <v>37</v>
@@ -1910,52 +1910,52 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="K19" s="31">
+      <c r="K19" s="30">
         <f t="array" ref="K19">IF(L19&lt;&gt;"", SUMPRODUCT(MID(N19:Y19,5,1)*1), "")</f>
         <v>1</v>
       </c>
-      <c r="L19" s="30">
+      <c r="L19" s="27">
         <v>5.0</v>
       </c>
-      <c r="M19" s="26">
+      <c r="M19" s="25">
         <f t="array" ref="M19">IF(L19&lt;&gt;"", SUMPRODUCT(LEFT(N19:Y19,1)*1), "")</f>
         <v>10</v>
       </c>
       <c r="N19" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O19" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P19" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="P19" s="18" t="s">
-        <v>40</v>
-      </c>
       <c r="Q19" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R19" s="18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S19" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T19" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U19" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V19" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W19" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X19" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y19" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AD19" s="5"/>
     </row>
@@ -1966,8 +1966,8 @@
       <c r="B20" s="21">
         <v>2.0</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>78</v>
+      <c r="C20" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="D20" s="22">
         <v>46326.0</v>
@@ -1976,38 +1976,64 @@
         <v>0.375</v>
       </c>
       <c r="F20" s="21"/>
-      <c r="G20" s="30" t="s">
-        <v>81</v>
+      <c r="G20" s="27" t="s">
+        <v>80</v>
       </c>
       <c r="H20" s="21"/>
       <c r="I20" s="21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J20" s="20" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="31" t="str">
+        <v>L</v>
+      </c>
+      <c r="K20" s="30">
         <f t="array" ref="K20">IF(L20&lt;&gt;"", SUMPRODUCT(MID(N20:Y20,5,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="L20" s="30"/>
-      <c r="M20" s="26" t="str">
+        <v>1</v>
+      </c>
+      <c r="L20" s="27">
+        <v>6.0</v>
+      </c>
+      <c r="M20" s="25">
         <f t="array" ref="M20">IF(L20&lt;&gt;"", SUMPRODUCT(LEFT(N20:Y20,1)*1), "")</f>
-        <v/>
-      </c>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18"/>
-      <c r="P20" s="18"/>
-      <c r="Q20" s="18"/>
-      <c r="R20" s="18"/>
-      <c r="S20" s="18"/>
-      <c r="T20" s="18"/>
-      <c r="U20" s="18"/>
-      <c r="V20" s="18"/>
-      <c r="W20" s="18"/>
-      <c r="X20" s="18"/>
-      <c r="Y20" s="18"/>
+        <v>10</v>
+      </c>
+      <c r="N20" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="O20" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="P20" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q20" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="R20" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="S20" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="T20" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="U20" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="V20" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="W20" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="X20" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y20" s="18" t="s">
+        <v>41</v>
+      </c>
       <c r="AD20" s="5"/>
     </row>
     <row r="21">
@@ -2017,8 +2043,8 @@
       <c r="B21" s="21">
         <v>2.0</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>78</v>
+      <c r="C21" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="D21" s="22">
         <v>46333.0</v>
@@ -2027,25 +2053,25 @@
         <v>0.4895833333333333</v>
       </c>
       <c r="F21" s="21"/>
-      <c r="G21" s="30" t="s">
+      <c r="G21" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="H21" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="I21" s="30" t="s">
+      <c r="I21" s="27" t="s">
         <v>37</v>
       </c>
       <c r="J21" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K21" s="31" t="str">
+      <c r="K21" s="30" t="str">
         <f t="array" ref="K21">IF(L21&lt;&gt;"", SUMPRODUCT(MID(N21:Y21,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L21" s="30"/>
-      <c r="M21" s="26" t="str">
+      <c r="L21" s="27"/>
+      <c r="M21" s="25" t="str">
         <f t="array" ref="M21">IF(L21&lt;&gt;"", SUMPRODUCT(LEFT(N21:Y21,1)*1), "")</f>
         <v/>
       </c>
@@ -2070,8 +2096,8 @@
       <c r="B22" s="21">
         <v>2.0</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>78</v>
+      <c r="C22" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="D22" s="22">
         <v>46340.0</v>
@@ -2080,23 +2106,23 @@
         <v>0.375</v>
       </c>
       <c r="F22" s="21"/>
-      <c r="G22" s="30" t="s">
-        <v>86</v>
+      <c r="G22" s="27" t="s">
+        <v>83</v>
       </c>
       <c r="H22" s="21"/>
       <c r="I22" s="21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J22" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K22" s="31" t="str">
+      <c r="K22" s="30" t="str">
         <f t="array" ref="K22">IF(L22&lt;&gt;"", SUMPRODUCT(MID(N22:Y22,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L22" s="30"/>
-      <c r="M22" s="26" t="str">
+      <c r="L22" s="27"/>
+      <c r="M22" s="25" t="str">
         <f t="array" ref="M22">IF(L22&lt;&gt;"", SUMPRODUCT(LEFT(N22:Y22,1)*1), "")</f>
         <v/>
       </c>
@@ -2121,8 +2147,8 @@
       <c r="B23" s="21">
         <v>2.0</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>78</v>
+      <c r="C23" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="D23" s="22">
         <v>46347.0</v>
@@ -2131,25 +2157,25 @@
         <v>0.46875</v>
       </c>
       <c r="F23" s="21"/>
-      <c r="G23" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="H23" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="I23" s="30" t="s">
+      <c r="G23" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="H23" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="I23" s="27" t="s">
         <v>37</v>
       </c>
       <c r="J23" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K23" s="31" t="str">
+      <c r="K23" s="30" t="str">
         <f t="array" ref="K23">IF(L23&lt;&gt;"", SUMPRODUCT(MID(N23:Y23,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L23" s="30"/>
-      <c r="M23" s="26" t="str">
+      <c r="L23" s="27"/>
+      <c r="M23" s="25" t="str">
         <f t="array" ref="M23">IF(L23&lt;&gt;"", SUMPRODUCT(LEFT(N23:Y23,1)*1), "")</f>
         <v/>
       </c>
@@ -2174,8 +2200,8 @@
       <c r="B24" s="21">
         <v>2.0</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>78</v>
+      <c r="C24" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="D24" s="22">
         <v>46354.0</v>
@@ -2184,23 +2210,23 @@
         <v>0.375</v>
       </c>
       <c r="F24" s="21"/>
-      <c r="G24" s="30" t="s">
-        <v>89</v>
+      <c r="G24" s="27" t="s">
+        <v>86</v>
       </c>
       <c r="H24" s="21"/>
       <c r="I24" s="21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J24" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K24" s="31" t="str">
+      <c r="K24" s="30" t="str">
         <f t="array" ref="K24">IF(L24&lt;&gt;"", SUMPRODUCT(MID(N24:Y24,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L24" s="30"/>
-      <c r="M24" s="26" t="str">
+      <c r="L24" s="27"/>
+      <c r="M24" s="25" t="str">
         <f t="array" ref="M24">IF(L24&lt;&gt;"", SUMPRODUCT(LEFT(N24:Y24,1)*1), "")</f>
         <v/>
       </c>
@@ -2225,8 +2251,8 @@
       <c r="B25" s="21">
         <v>2.0</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>78</v>
+      <c r="C25" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="D25" s="22">
         <v>46361.0</v>
@@ -2235,25 +2261,25 @@
         <v>0.40625</v>
       </c>
       <c r="F25" s="21"/>
-      <c r="G25" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="H25" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="I25" s="30" t="s">
+      <c r="G25" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="H25" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I25" s="27" t="s">
         <v>37</v>
       </c>
       <c r="J25" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K25" s="31" t="str">
+      <c r="K25" s="30" t="str">
         <f t="array" ref="K25">IF(L25&lt;&gt;"", SUMPRODUCT(MID(N25:Y25,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L25" s="30"/>
-      <c r="M25" s="26" t="str">
+      <c r="L25" s="27"/>
+      <c r="M25" s="25" t="str">
         <f t="array" ref="M25">IF(L25&lt;&gt;"", SUMPRODUCT(LEFT(N25:Y25,1)*1), "")</f>
         <v/>
       </c>
@@ -2276,24 +2302,24 @@
         <f t="shared" ref="A26:A40" si="3">IF(ISBLANK(B26),"",A25+1)</f>
         <v/>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
       <c r="J26" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K26" s="26" t="str">
+      <c r="K26" s="25" t="str">
         <f t="array" ref="K26">IF(L26&lt;&gt;"", SUMPRODUCT(MID(N26:Y26,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L26" s="29"/>
-      <c r="M26" s="26" t="str">
+      <c r="L26" s="26"/>
+      <c r="M26" s="25" t="str">
         <f t="array" ref="M26">IF(L26&lt;&gt;"", SUMPRODUCT(LEFT(N26:Y26,1)*1), "")</f>
         <v/>
       </c>
@@ -2316,24 +2342,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
       <c r="J27" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K27" s="26" t="str">
+      <c r="K27" s="25" t="str">
         <f t="array" ref="K27">IF(L27&lt;&gt;"", SUMPRODUCT(MID(N27:Y27,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L27" s="21"/>
-      <c r="M27" s="26" t="str">
+      <c r="M27" s="25" t="str">
         <f t="array" ref="M27">IF(L27&lt;&gt;"", SUMPRODUCT(LEFT(N27:Y27,1)*1), "")</f>
         <v/>
       </c>
@@ -2356,24 +2382,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
       <c r="J28" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K28" s="26" t="str">
+      <c r="K28" s="25" t="str">
         <f t="array" ref="K28">IF(L28&lt;&gt;"", SUMPRODUCT(MID(N28:Y28,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L28" s="21"/>
-      <c r="M28" s="26" t="str">
+      <c r="M28" s="25" t="str">
         <f t="array" ref="M28">IF(L28&lt;&gt;"", SUMPRODUCT(LEFT(N28:Y28,1)*1), "")</f>
         <v/>
       </c>
@@ -2396,24 +2422,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
       <c r="J29" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K29" s="26" t="str">
+      <c r="K29" s="25" t="str">
         <f t="array" ref="K29">IF(L29&lt;&gt;"", SUMPRODUCT(MID(N29:Y29,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L29" s="21"/>
-      <c r="M29" s="26" t="str">
+      <c r="M29" s="25" t="str">
         <f t="array" ref="M29">IF(L29&lt;&gt;"", SUMPRODUCT(LEFT(N29:Y29,1)*1), "")</f>
         <v/>
       </c>
@@ -2436,24 +2462,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
       <c r="J30" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K30" s="26" t="str">
+      <c r="K30" s="25" t="str">
         <f t="array" ref="K30">IF(L30&lt;&gt;"", SUMPRODUCT(MID(N30:Y30,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L30" s="21"/>
-      <c r="M30" s="26" t="str">
+      <c r="M30" s="25" t="str">
         <f t="array" ref="M30">IF(L30&lt;&gt;"", SUMPRODUCT(LEFT(N30:Y30,1)*1), "")</f>
         <v/>
       </c>
@@ -2476,24 +2502,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
       <c r="J31" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K31" s="26" t="str">
+      <c r="K31" s="25" t="str">
         <f t="array" ref="K31">IF(L31&lt;&gt;"", SUMPRODUCT(MID(N31:Y31,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L31" s="21"/>
-      <c r="M31" s="26" t="str">
+      <c r="M31" s="25" t="str">
         <f t="array" ref="M31">IF(L31&lt;&gt;"", SUMPRODUCT(LEFT(N31:Y31,1)*1), "")</f>
         <v/>
       </c>
@@ -2516,24 +2542,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
       <c r="J32" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K32" s="26" t="str">
+      <c r="K32" s="25" t="str">
         <f t="array" ref="K32">IF(L32&lt;&gt;"", SUMPRODUCT(MID(N32:Y32,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L32" s="21"/>
-      <c r="M32" s="26" t="str">
+      <c r="M32" s="25" t="str">
         <f t="array" ref="M32">IF(L32&lt;&gt;"", SUMPRODUCT(LEFT(N32:Y32,1)*1), "")</f>
         <v/>
       </c>
@@ -2556,24 +2582,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
       <c r="J33" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K33" s="26" t="str">
+      <c r="K33" s="25" t="str">
         <f t="array" ref="K33">IF(L33&lt;&gt;"", SUMPRODUCT(MID(N33:Y33,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L33" s="21"/>
-      <c r="M33" s="26" t="str">
+      <c r="M33" s="25" t="str">
         <f t="array" ref="M33">IF(L33&lt;&gt;"", SUMPRODUCT(LEFT(N33:Y33,1)*1), "")</f>
         <v/>
       </c>
@@ -2596,24 +2622,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
       <c r="J34" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K34" s="26" t="str">
+      <c r="K34" s="25" t="str">
         <f t="array" ref="K34">IF(L34&lt;&gt;"", SUMPRODUCT(MID(N34:Y34,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L34" s="21"/>
-      <c r="M34" s="26" t="str">
+      <c r="M34" s="25" t="str">
         <f t="array" ref="M34">IF(L34&lt;&gt;"", SUMPRODUCT(LEFT(N34:Y34,1)*1), "")</f>
         <v/>
       </c>
@@ -2636,24 +2662,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
       <c r="J35" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K35" s="26" t="str">
+      <c r="K35" s="25" t="str">
         <f t="array" ref="K35">IF(L35&lt;&gt;"", SUMPRODUCT(MID(N35:Y35,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L35" s="21"/>
-      <c r="M35" s="26" t="str">
+      <c r="M35" s="25" t="str">
         <f t="array" ref="M35">IF(L35&lt;&gt;"", SUMPRODUCT(LEFT(N35:Y35,1)*1), "")</f>
         <v/>
       </c>
@@ -2676,24 +2702,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
       <c r="J36" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="26" t="str">
+      <c r="K36" s="25" t="str">
         <f t="array" ref="K36">IF(L36&lt;&gt;"", SUMPRODUCT(MID(N36:Y36,5,1)*1), "")</f>
         <v/>
       </c>
-      <c r="L36" s="29"/>
-      <c r="M36" s="26" t="str">
+      <c r="L36" s="26"/>
+      <c r="M36" s="25" t="str">
         <f t="array" ref="M36">IF(L36&lt;&gt;"", SUMPRODUCT(LEFT(N36:Y36,1)*1), "")</f>
         <v/>
       </c>
@@ -2716,24 +2742,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
       <c r="J37" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K37" s="26" t="str">
+      <c r="K37" s="25" t="str">
         <f t="array" ref="K37">IF(L37&lt;&gt;"", SUMPRODUCT(MID(N37:Y37,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L37" s="21"/>
-      <c r="M37" s="26" t="str">
+      <c r="M37" s="25" t="str">
         <f t="array" ref="M37">IF(L37&lt;&gt;"", SUMPRODUCT(LEFT(N37:Y37,1)*1), "")</f>
         <v/>
       </c>
@@ -2756,24 +2782,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
       <c r="J38" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K38" s="26" t="str">
+      <c r="K38" s="25" t="str">
         <f t="array" ref="K38">IF(L38&lt;&gt;"", SUMPRODUCT(MID(N38:Y38,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L38" s="21"/>
-      <c r="M38" s="26" t="str">
+      <c r="M38" s="25" t="str">
         <f t="array" ref="M38">IF(L38&lt;&gt;"", SUMPRODUCT(LEFT(N38:Y38,1)*1), "")</f>
         <v/>
       </c>
@@ -2796,24 +2822,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
       <c r="J39" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K39" s="26" t="str">
+      <c r="K39" s="25" t="str">
         <f t="array" ref="K39">IF(L39&lt;&gt;"", SUMPRODUCT(MID(N39:Y39,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L39" s="21"/>
-      <c r="M39" s="26" t="str">
+      <c r="M39" s="25" t="str">
         <f t="array" ref="M39">IF(L39&lt;&gt;"", SUMPRODUCT(LEFT(N39:Y39,1)*1), "")</f>
         <v/>
       </c>
@@ -2836,24 +2862,24 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
       <c r="J40" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K40" s="26" t="str">
+      <c r="K40" s="25" t="str">
         <f t="array" ref="K40">IF(L40&lt;&gt;"", SUMPRODUCT(MID(N40:Y40,5,1)*1), "")</f>
         <v/>
       </c>
       <c r="L40" s="21"/>
-      <c r="M40" s="26" t="str">
+      <c r="M40" s="25" t="str">
         <f t="array" ref="M40">IF(L40&lt;&gt;"", SUMPRODUCT(LEFT(N40:Y40,1)*1), "")</f>
         <v/>
       </c>
@@ -3006,7 +3032,7 @@
         <v>33</v>
       </c>
       <c r="N44" s="18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O44" s="5"/>
       <c r="T44" s="5"/>
@@ -3023,42 +3049,42 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B45" s="12">
+        <v>93</v>
+      </c>
+      <c r="B45" s="11">
         <v>1.0</v>
       </c>
-      <c r="C45" s="12">
+      <c r="C45" s="11">
         <v>1.0</v>
       </c>
-      <c r="D45" s="12">
+      <c r="D45" s="11">
         <v>1.0</v>
       </c>
-      <c r="E45" s="12">
+      <c r="E45" s="11">
         <v>1.0</v>
       </c>
-      <c r="F45" s="12">
+      <c r="F45" s="11">
         <v>1.0</v>
       </c>
-      <c r="G45" s="12">
+      <c r="G45" s="11">
         <v>1.0</v>
       </c>
-      <c r="H45" s="12">
+      <c r="H45" s="11">
+        <v>0.0</v>
+      </c>
+      <c r="I45" s="11">
         <v>1.0</v>
       </c>
-      <c r="I45" s="12">
+      <c r="J45" s="11">
         <v>1.0</v>
       </c>
-      <c r="J45" s="12">
+      <c r="K45" s="11">
         <v>1.0</v>
       </c>
-      <c r="K45" s="12">
-        <v>0.0</v>
-      </c>
-      <c r="L45" s="12">
+      <c r="L45" s="11">
         <v>1.0</v>
       </c>
-      <c r="M45" s="12">
+      <c r="M45" s="11">
         <v>0.0</v>
       </c>
       <c r="N45" s="5"/>
@@ -3080,48 +3106,48 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" s="12">
+        <v>72</v>
+      </c>
+      <c r="B46" s="11">
         <v>1.0</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C46" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="D46" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="E46" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="F46" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="G46" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="H46" s="11">
         <v>0.0</v>
       </c>
-      <c r="D46" s="12">
+      <c r="I46" s="11">
         <v>1.0</v>
       </c>
-      <c r="E46" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="F46" s="12">
+      <c r="J46" s="11">
         <v>0.0</v>
       </c>
-      <c r="G46" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="H46" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="I46" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="J46" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="K46" s="12">
+      <c r="K46" s="11">
         <v>0.0</v>
       </c>
-      <c r="L46" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="M46" s="12">
+      <c r="L46" s="11">
+        <v>0.0</v>
+      </c>
+      <c r="M46" s="11">
         <v>0.0</v>
       </c>
       <c r="N46" s="5"/>
       <c r="O46" s="34">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T46" s="5"/>
       <c r="U46" s="5"/>
@@ -3137,42 +3163,42 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B47" s="12">
+        <v>94</v>
+      </c>
+      <c r="B47" s="11">
         <v>0.0</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="11">
         <v>0.0</v>
       </c>
-      <c r="D47" s="12">
+      <c r="D47" s="11">
         <v>0.0</v>
       </c>
-      <c r="E47" s="12">
+      <c r="E47" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="F47" s="11">
         <v>0.0</v>
       </c>
-      <c r="F47" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="G47" s="12">
+      <c r="G47" s="11">
         <v>0.0</v>
       </c>
-      <c r="H47" s="12">
+      <c r="H47" s="11">
         <v>0.0</v>
       </c>
-      <c r="I47" s="12">
+      <c r="I47" s="11">
         <v>0.0</v>
       </c>
-      <c r="J47" s="12">
+      <c r="J47" s="11">
         <v>0.0</v>
       </c>
-      <c r="K47" s="12">
+      <c r="K47" s="11">
         <v>0.0</v>
       </c>
-      <c r="L47" s="12">
+      <c r="L47" s="11">
         <v>0.0</v>
       </c>
-      <c r="M47" s="12">
+      <c r="M47" s="11">
         <v>0.0</v>
       </c>
       <c r="N47" s="5"/>
@@ -3194,42 +3220,42 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B48" s="12">
+        <v>95</v>
+      </c>
+      <c r="B48" s="11">
         <v>0.0</v>
       </c>
-      <c r="C48" s="12">
+      <c r="C48" s="11">
         <v>0.0</v>
       </c>
-      <c r="D48" s="12">
+      <c r="D48" s="11">
         <v>0.0</v>
       </c>
-      <c r="E48" s="12">
+      <c r="E48" s="11">
         <v>0.0</v>
       </c>
-      <c r="F48" s="12">
+      <c r="F48" s="11">
         <v>0.0</v>
       </c>
-      <c r="G48" s="12">
+      <c r="G48" s="11">
         <v>0.0</v>
       </c>
-      <c r="H48" s="12">
+      <c r="H48" s="11">
         <v>0.0</v>
       </c>
-      <c r="I48" s="12">
+      <c r="I48" s="11">
         <v>0.0</v>
       </c>
-      <c r="J48" s="12">
+      <c r="J48" s="11">
         <v>0.0</v>
       </c>
-      <c r="K48" s="12">
+      <c r="K48" s="11">
         <v>0.0</v>
       </c>
-      <c r="L48" s="12">
+      <c r="L48" s="11">
         <v>0.0</v>
       </c>
-      <c r="M48" s="12">
+      <c r="M48" s="11">
         <v>0.0</v>
       </c>
       <c r="N48" s="5"/>
@@ -3257,7 +3283,7 @@
       </c>
       <c r="C49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>1,0,0,0</v>
+        <v>1,1,0,0</v>
       </c>
       <c r="D49" s="5" t="str">
         <f t="shared" si="5"/>
@@ -3265,11 +3291,11 @@
       </c>
       <c r="E49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,0,0</v>
+        <v>1,1,1,0</v>
       </c>
       <c r="F49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>1,0,1,0</v>
+        <v>1,1,0,0</v>
       </c>
       <c r="G49" s="5" t="str">
         <f t="shared" si="5"/>
@@ -3277,7 +3303,7 @@
       </c>
       <c r="H49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,0,0</v>
+        <v>0,0,0,0</v>
       </c>
       <c r="I49" s="5" t="str">
         <f t="shared" si="5"/>
@@ -3285,15 +3311,15 @@
       </c>
       <c r="J49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,0,0</v>
+        <v>1,0,0,0</v>
       </c>
       <c r="K49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>0,0,0,0</v>
+        <v>1,0,0,0</v>
       </c>
       <c r="L49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>1,1,0,0</v>
+        <v>1,0,0,0</v>
       </c>
       <c r="M49" s="5" t="str">
         <f t="shared" si="5"/>
@@ -33389,8 +33415,8 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3"/>
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
       <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
@@ -33436,41 +33462,41 @@
       <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="14">
         <f t="array" ref="C2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
+        <v>10</v>
+      </c>
+      <c r="D2" s="14">
+        <f t="array" ref="D2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z42, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
+        <v>10</v>
+      </c>
+      <c r="E2" s="14">
+        <f t="array" ref="E2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
+        <v>10</v>
+      </c>
+      <c r="F2" s="14">
+        <f t="array" ref="F2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <f t="array" ref="D2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z42, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>9</v>
-      </c>
-      <c r="E2" s="11">
-        <f t="array" ref="E2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>9</v>
-      </c>
-      <c r="F2" s="11">
-        <f t="array" ref="F2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>8</v>
-      </c>
-      <c r="G2" s="11">
+      <c r="G2" s="14">
         <f t="array" ref="G2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>9</v>
-      </c>
-      <c r="H2" s="11">
+        <v>10</v>
+      </c>
+      <c r="H2" s="14">
         <f t="array" ref="H2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>9</v>
-      </c>
-      <c r="I2" s="11">
+        <v>10</v>
+      </c>
+      <c r="I2" s="14">
         <f t="array" ref="I2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
         <v>7</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="14">
         <f t="array" ref="J2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>9</v>
-      </c>
-      <c r="K2" s="11">
+        <v>10</v>
+      </c>
+      <c r="K2" s="14">
         <f t="array" ref="K2">SUM(IF(LEFT(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 1)="1", 1, 0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -33484,43 +33510,43 @@
       <c r="U2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="25"/>
+      <c r="A3" s="28"/>
       <c r="B3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="27">
+        <v>63</v>
+      </c>
+      <c r="C3" s="29">
         <f>C2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="29">
         <f>D2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="29">
         <f>E2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="29">
         <f>F2/MatchesDB!$B$1</f>
-        <v>0.8888888889</v>
-      </c>
-      <c r="G3" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="G3" s="29">
         <f>G2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="H3" s="27">
+      <c r="H3" s="29">
         <f>H2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="I3" s="27">
+      <c r="I3" s="29">
         <f>I2/(MatchesDB!$B$1-4)</f>
-        <v>1.4</v>
-      </c>
-      <c r="J3" s="27">
+        <v>1.166666667</v>
+      </c>
+      <c r="J3" s="29">
         <f>J2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
-      <c r="K3" s="27">
+      <c r="K3" s="29">
         <f>K2/MatchesDB!$B$1</f>
         <v>1</v>
       </c>
@@ -33537,44 +33563,44 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="31">
         <f t="array" ref="C4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>7</v>
-      </c>
-      <c r="D4" s="28">
+        <v>8</v>
+      </c>
+      <c r="D4" s="31">
         <f t="array" ref="D4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
+        <v>9</v>
+      </c>
+      <c r="E4" s="31">
+        <f t="array" ref="E4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
+        <v>6</v>
+      </c>
+      <c r="F4" s="31">
+        <f t="array" ref="F4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>8</v>
       </c>
-      <c r="E4" s="28">
-        <f t="array" ref="E4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>5</v>
-      </c>
-      <c r="F4" s="28">
-        <f t="array" ref="F4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>7</v>
-      </c>
-      <c r="G4" s="28">
+      <c r="G4" s="31">
         <f t="array" ref="G4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>7</v>
-      </c>
-      <c r="H4" s="28">
+        <v>8</v>
+      </c>
+      <c r="H4" s="31">
         <f t="array" ref="H4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>9</v>
-      </c>
-      <c r="I4" s="28">
+        <v>10</v>
+      </c>
+      <c r="I4" s="31">
         <f t="array" ref="I4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>7</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="31">
         <f t="array" ref="J4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
-        <v>8</v>
-      </c>
-      <c r="K4" s="28">
+        <v>9</v>
+      </c>
+      <c r="K4" s="31">
         <f t="array" ref="K4">SUM(IF(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 3, 1)="1", 1, 0))</f>
         <v>9</v>
       </c>
@@ -33590,45 +33616,45 @@
       <c r="U4" s="5"/>
     </row>
     <row r="5">
-      <c r="A5" s="25"/>
+      <c r="A5" s="28"/>
       <c r="B5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="27">
+        <v>63</v>
+      </c>
+      <c r="C5" s="29">
         <f t="shared" ref="C5:K5" si="1">C4/C2</f>
-        <v>0.7777777778</v>
-      </c>
-      <c r="D5" s="27">
+        <v>0.8</v>
+      </c>
+      <c r="D5" s="29">
+        <f t="shared" si="1"/>
+        <v>0.9</v>
+      </c>
+      <c r="E5" s="29">
+        <f t="shared" si="1"/>
+        <v>0.6</v>
+      </c>
+      <c r="F5" s="29">
         <f t="shared" si="1"/>
         <v>0.8888888889</v>
       </c>
-      <c r="E5" s="27">
+      <c r="G5" s="29">
         <f t="shared" si="1"/>
-        <v>0.5555555556</v>
-      </c>
-      <c r="F5" s="27">
-        <f t="shared" si="1"/>
-        <v>0.875</v>
-      </c>
-      <c r="G5" s="27">
-        <f t="shared" si="1"/>
-        <v>0.7777777778</v>
-      </c>
-      <c r="H5" s="27">
+        <v>0.8</v>
+      </c>
+      <c r="H5" s="29">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="29">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J5" s="27">
+      <c r="J5" s="29">
         <f t="shared" si="1"/>
-        <v>0.8888888889</v>
-      </c>
-      <c r="K5" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="K5" s="29">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
@@ -33643,44 +33669,44 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="14">
         <f t="array" ref="C6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>1</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="14">
         <f t="array" ref="D6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>12</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="14">
         <f t="array" ref="E6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>6</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="14">
         <f t="array" ref="F6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
-        <v>2</v>
-      </c>
-      <c r="G6" s="11">
+        <v>3</v>
+      </c>
+      <c r="G6" s="14">
         <f t="array" ref="G6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>22</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="14">
         <f t="array" ref="H6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>4</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="14">
         <f t="array" ref="I6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>1</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="14">
         <f t="array" ref="J6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>11</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="14">
         <f t="array" ref="K6">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 5, 1)), 0))</f>
         <v>5</v>
       </c>
@@ -33696,33 +33722,33 @@
       <c r="U6" s="5"/>
     </row>
     <row r="7">
-      <c r="A7" s="25"/>
+      <c r="A7" s="28"/>
       <c r="B7" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C7" s="32">
         <f t="shared" ref="C7:K7" si="2">C6/C2</f>
-        <v>0.1111111111</v>
+        <v>0.1</v>
       </c>
       <c r="D7" s="32">
         <f t="shared" si="2"/>
-        <v>1.333333333</v>
+        <v>1.2</v>
       </c>
       <c r="E7" s="32">
         <f t="shared" si="2"/>
-        <v>0.6666666667</v>
+        <v>0.6</v>
       </c>
       <c r="F7" s="32">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.3333333333</v>
       </c>
       <c r="G7" s="32">
         <f t="shared" si="2"/>
-        <v>2.444444444</v>
+        <v>2.2</v>
       </c>
       <c r="H7" s="32">
         <f t="shared" si="2"/>
-        <v>0.4444444444</v>
+        <v>0.4</v>
       </c>
       <c r="I7" s="32">
         <f t="shared" si="2"/>
@@ -33730,11 +33756,11 @@
       </c>
       <c r="J7" s="32">
         <f t="shared" si="2"/>
-        <v>1.222222222</v>
+        <v>1.1</v>
       </c>
       <c r="K7" s="32">
         <f t="shared" si="2"/>
-        <v>0.5555555556</v>
+        <v>0.5</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
@@ -33749,44 +33775,44 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="31">
         <f t="array" ref="C8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(C$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>8</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="31">
         <f t="array" ref="D8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(D$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>10</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="31">
         <f t="array" ref="E8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(E$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>2</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="31">
         <f t="array" ref="F8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(F$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>2</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="31">
         <f t="array" ref="G8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(G$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>4</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="31">
         <f t="array" ref="H8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(H$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>2</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="31">
         <f t="array" ref="I8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(I$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>0</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="31">
         <f t="array" ref="J8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(J$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>5</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="31">
         <f t="array" ref="K8">SUM(IFERROR(VALUE(MID(INDEX(MatchesDB!$K$11:$Z40, 0, MATCH(K$1, MatchesDB!$K$10:$Z$10, 0)), 7, 1)), 0))</f>
         <v>4</v>
       </c>
@@ -33802,33 +33828,33 @@
       <c r="U8" s="5"/>
     </row>
     <row r="9">
-      <c r="A9" s="25"/>
+      <c r="A9" s="28"/>
       <c r="B9" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C9" s="32">
         <f t="shared" ref="C9:K9" si="3">C8/C2</f>
-        <v>0.8888888889</v>
+        <v>0.8</v>
       </c>
       <c r="D9" s="32">
         <f t="shared" si="3"/>
-        <v>1.111111111</v>
+        <v>1</v>
       </c>
       <c r="E9" s="32">
         <f t="shared" si="3"/>
-        <v>0.2222222222</v>
+        <v>0.2</v>
       </c>
       <c r="F9" s="32">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.2222222222</v>
       </c>
       <c r="G9" s="32">
         <f t="shared" si="3"/>
-        <v>0.4444444444</v>
+        <v>0.4</v>
       </c>
       <c r="H9" s="32">
         <f t="shared" si="3"/>
-        <v>0.2222222222</v>
+        <v>0.2</v>
       </c>
       <c r="I9" s="32">
         <f t="shared" si="3"/>
@@ -33836,11 +33862,11 @@
       </c>
       <c r="J9" s="32">
         <f t="shared" si="3"/>
-        <v>0.5555555556</v>
+        <v>0.5</v>
       </c>
       <c r="K9" s="32">
         <f t="shared" si="3"/>
-        <v>0.4444444444</v>
+        <v>0.4</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -33855,44 +33881,44 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="14">
         <f t="shared" ref="C10:K10" si="4">C6+C8</f>
         <v>9</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="14">
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="14">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="14">
         <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="G10" s="11">
+        <v>5</v>
+      </c>
+      <c r="G10" s="14">
         <f t="shared" si="4"/>
         <v>26</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="14">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="14">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="14">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="K10" s="11">
+      <c r="K10" s="14">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
@@ -33908,33 +33934,33 @@
       <c r="U10" s="5"/>
     </row>
     <row r="11">
-      <c r="A11" s="25"/>
+      <c r="A11" s="28"/>
       <c r="B11" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C11" s="32">
         <f t="shared" ref="C11:K11" si="5">C10/C2</f>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D11" s="32">
         <f t="shared" si="5"/>
-        <v>2.444444444</v>
+        <v>2.2</v>
       </c>
       <c r="E11" s="32">
         <f t="shared" si="5"/>
-        <v>0.8888888889</v>
+        <v>0.8</v>
       </c>
       <c r="F11" s="32">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0.5555555556</v>
       </c>
       <c r="G11" s="32">
         <f t="shared" si="5"/>
-        <v>2.888888889</v>
+        <v>2.6</v>
       </c>
       <c r="H11" s="32">
         <f t="shared" si="5"/>
-        <v>0.6666666667</v>
+        <v>0.6</v>
       </c>
       <c r="I11" s="32">
         <f t="shared" si="5"/>
@@ -33942,11 +33968,11 @@
       </c>
       <c r="J11" s="32">
         <f t="shared" si="5"/>
-        <v>1.777777778</v>
+        <v>1.6</v>
       </c>
       <c r="K11" s="32">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
